--- a/data/vendas-inadimplentes.xlsx
+++ b/data/vendas-inadimplentes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30030"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED432128-6B3D-4ED5-8D63-016E16EBE590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64F3D1F-70EF-49ED-9BD9-C615EABF3CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="883" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="149">
   <si>
     <t>Data vecto</t>
   </si>
@@ -456,6 +456,30 @@
   </si>
   <si>
     <t>10/03/2026</t>
+  </si>
+  <si>
+    <t>01/03/2026</t>
+  </si>
+  <si>
+    <t>30/04/2026</t>
+  </si>
+  <si>
+    <t>29/04/2026</t>
+  </si>
+  <si>
+    <t>20/04/2026</t>
+  </si>
+  <si>
+    <t>05/04/2026</t>
+  </si>
+  <si>
+    <t>21/04/2026</t>
+  </si>
+  <si>
+    <t>15/04/2026</t>
+  </si>
+  <si>
+    <t>10/04/2026</t>
   </si>
 </sst>
 </file>
@@ -11823,374 +11847,929 @@
       </c>
     </row>
     <row r="291" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A291" s="14"/>
-      <c r="B291" s="3"/>
-      <c r="C291" s="23"/>
-      <c r="D291" s="24"/>
-      <c r="E291" s="25"/>
-      <c r="F291" s="10"/>
-      <c r="G291" s="11"/>
-      <c r="H291" s="4"/>
-      <c r="I291" s="3"/>
-      <c r="J291" s="5"/>
-      <c r="K291" s="6"/>
-      <c r="L291" s="7"/>
-      <c r="M291" s="5"/>
+      <c r="A291" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B291" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C291" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="D291" s="26"/>
+      <c r="E291" s="26"/>
+      <c r="F291" s="15">
+        <v>1450</v>
+      </c>
+      <c r="G291" s="15">
+        <v>508</v>
+      </c>
+      <c r="H291" s="5">
+        <v>3515.6</v>
+      </c>
+      <c r="I291" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J291" s="17">
+        <v>4029.34</v>
+      </c>
+      <c r="K291" s="6">
+        <v>127</v>
+      </c>
+      <c r="L291" s="4">
+        <v>251.17</v>
+      </c>
+      <c r="M291" s="5">
+        <v>4280.51</v>
+      </c>
     </row>
     <row r="292" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A292" s="14"/>
-      <c r="B292" s="3"/>
-      <c r="C292" s="23"/>
-      <c r="D292" s="24"/>
-      <c r="E292" s="25"/>
-      <c r="F292" s="10"/>
-      <c r="G292" s="11"/>
-      <c r="H292" s="4"/>
-      <c r="I292" s="3"/>
-      <c r="J292" s="5"/>
-      <c r="K292" s="6"/>
-      <c r="L292" s="7"/>
-      <c r="M292" s="5"/>
+      <c r="A292" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B292" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C292" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D292" s="26"/>
+      <c r="E292" s="26"/>
+      <c r="F292" s="15">
+        <v>1508</v>
+      </c>
+      <c r="G292" s="15">
+        <v>1306</v>
+      </c>
+      <c r="H292" s="5">
+        <v>565.54999999999995</v>
+      </c>
+      <c r="I292" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J292" s="17">
+        <v>588.09</v>
+      </c>
+      <c r="K292" s="6">
+        <v>78</v>
+      </c>
+      <c r="L292" s="4">
+        <v>27.05</v>
+      </c>
+      <c r="M292" s="5">
+        <v>615.14</v>
+      </c>
     </row>
     <row r="293" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A293" s="14"/>
-      <c r="B293" s="3"/>
-      <c r="C293" s="23"/>
-      <c r="D293" s="24"/>
-      <c r="E293" s="25"/>
-      <c r="F293" s="10"/>
-      <c r="G293" s="11"/>
-      <c r="H293" s="4"/>
-      <c r="I293" s="3"/>
-      <c r="J293" s="5"/>
-      <c r="K293" s="6"/>
-      <c r="L293" s="7"/>
-      <c r="M293" s="5"/>
+      <c r="A293" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B293" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C293" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="D293" s="26"/>
+      <c r="E293" s="26"/>
+      <c r="F293" s="15">
+        <v>1479</v>
+      </c>
+      <c r="G293" s="15">
+        <v>803</v>
+      </c>
+      <c r="H293" s="5">
+        <v>1467.17</v>
+      </c>
+      <c r="I293" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J293" s="17">
+        <v>1677.04</v>
+      </c>
+      <c r="K293" s="6">
+        <v>45</v>
+      </c>
+      <c r="L293" s="4">
+        <v>58.7</v>
+      </c>
+      <c r="M293" s="5">
+        <v>1735.74</v>
+      </c>
     </row>
     <row r="294" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A294" s="14"/>
-      <c r="B294" s="3"/>
-      <c r="C294" s="23"/>
-      <c r="D294" s="24"/>
-      <c r="E294" s="25"/>
-      <c r="F294" s="10"/>
-      <c r="G294" s="11"/>
-      <c r="H294" s="4"/>
-      <c r="I294" s="3"/>
-      <c r="J294" s="5"/>
-      <c r="K294" s="6"/>
-      <c r="L294" s="7"/>
-      <c r="M294" s="5"/>
+      <c r="A294" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B294" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C294" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D294" s="26"/>
+      <c r="E294" s="26"/>
+      <c r="F294" s="15">
+        <v>1467</v>
+      </c>
+      <c r="G294" s="15">
+        <v>207</v>
+      </c>
+      <c r="H294" s="5">
+        <v>675.78</v>
+      </c>
+      <c r="I294" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J294" s="17">
+        <v>774.53</v>
+      </c>
+      <c r="K294" s="6">
+        <v>4</v>
+      </c>
+      <c r="L294" s="4">
+        <v>16.52</v>
+      </c>
+      <c r="M294" s="5">
+        <v>791.05</v>
+      </c>
     </row>
     <row r="295" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A295" s="14"/>
-      <c r="B295" s="3"/>
-      <c r="C295" s="23"/>
-      <c r="D295" s="24"/>
-      <c r="E295" s="25"/>
-      <c r="F295" s="10"/>
-      <c r="G295" s="11"/>
-      <c r="H295" s="4"/>
-      <c r="I295" s="3"/>
-      <c r="J295" s="5"/>
-      <c r="K295" s="6"/>
-      <c r="L295" s="7"/>
-      <c r="M295" s="5"/>
+      <c r="A295" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B295" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C295" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="D295" s="26"/>
+      <c r="E295" s="26"/>
+      <c r="F295" s="15">
+        <v>1571</v>
+      </c>
+      <c r="G295" s="15">
+        <v>101</v>
+      </c>
+      <c r="H295" s="5">
+        <v>736.79</v>
+      </c>
+      <c r="I295" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J295" s="17">
+        <v>834.4</v>
+      </c>
+      <c r="K295" s="6">
+        <v>5</v>
+      </c>
+      <c r="L295" s="4">
+        <v>18.079999999999998</v>
+      </c>
+      <c r="M295" s="5">
+        <v>852.48</v>
+      </c>
     </row>
     <row r="296" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A296" s="14"/>
-      <c r="B296" s="3"/>
-      <c r="C296" s="23"/>
-      <c r="D296" s="24"/>
-      <c r="E296" s="25"/>
-      <c r="F296" s="10"/>
-      <c r="G296" s="11"/>
-      <c r="H296" s="4"/>
-      <c r="I296" s="3"/>
-      <c r="J296" s="5"/>
-      <c r="K296" s="6"/>
-      <c r="L296" s="7"/>
-      <c r="M296" s="5"/>
+      <c r="A296" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B296" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C296" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D296" s="26"/>
+      <c r="E296" s="26"/>
+      <c r="F296" s="15">
+        <v>1613</v>
+      </c>
+      <c r="G296" s="15">
+        <v>1402</v>
+      </c>
+      <c r="H296" s="5">
+        <v>793.9</v>
+      </c>
+      <c r="I296" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J296" s="17">
+        <v>878.8</v>
+      </c>
+      <c r="K296" s="6">
+        <v>14</v>
+      </c>
+      <c r="L296" s="4">
+        <v>21.68</v>
+      </c>
+      <c r="M296" s="5">
+        <v>900.48</v>
+      </c>
     </row>
     <row r="297" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A297" s="14"/>
-      <c r="B297" s="3"/>
-      <c r="C297" s="23"/>
-      <c r="D297" s="24"/>
-      <c r="E297" s="25"/>
-      <c r="F297" s="10"/>
-      <c r="G297" s="11"/>
-      <c r="H297" s="4"/>
-      <c r="I297" s="3"/>
-      <c r="J297" s="5"/>
-      <c r="K297" s="6"/>
-      <c r="L297" s="7"/>
-      <c r="M297" s="5"/>
+      <c r="A297" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B297" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C297" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D297" s="26"/>
+      <c r="E297" s="26"/>
+      <c r="F297" s="15">
+        <v>1416</v>
+      </c>
+      <c r="G297" s="15">
+        <v>1304</v>
+      </c>
+      <c r="H297" s="5">
+        <v>600</v>
+      </c>
+      <c r="I297" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J297" s="17">
+        <v>689.81</v>
+      </c>
+      <c r="K297" s="6">
+        <v>14</v>
+      </c>
+      <c r="L297" s="4">
+        <v>17.02</v>
+      </c>
+      <c r="M297" s="5">
+        <v>706.83</v>
+      </c>
     </row>
     <row r="298" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A298" s="14"/>
-      <c r="B298" s="3"/>
-      <c r="C298" s="23"/>
-      <c r="D298" s="24"/>
-      <c r="E298" s="25"/>
-      <c r="F298" s="10"/>
-      <c r="G298" s="11"/>
-      <c r="H298" s="4"/>
-      <c r="I298" s="3"/>
-      <c r="J298" s="5"/>
-      <c r="K298" s="6"/>
-      <c r="L298" s="7"/>
-      <c r="M298" s="5"/>
+      <c r="A298" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B298" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C298" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="D298" s="26"/>
+      <c r="E298" s="26"/>
+      <c r="F298" s="15">
+        <v>1418</v>
+      </c>
+      <c r="G298" s="15">
+        <v>1204</v>
+      </c>
+      <c r="H298" s="5">
+        <v>762.74</v>
+      </c>
+      <c r="I298" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J298" s="17">
+        <v>876.91</v>
+      </c>
+      <c r="K298" s="6">
+        <v>5</v>
+      </c>
+      <c r="L298" s="4">
+        <v>19</v>
+      </c>
+      <c r="M298" s="5">
+        <v>895.91</v>
+      </c>
     </row>
     <row r="299" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A299" s="14"/>
-      <c r="B299" s="3"/>
-      <c r="C299" s="23"/>
-      <c r="D299" s="24"/>
-      <c r="E299" s="25"/>
-      <c r="F299" s="10"/>
-      <c r="G299" s="11"/>
-      <c r="H299" s="4"/>
-      <c r="I299" s="3"/>
-      <c r="J299" s="5"/>
-      <c r="K299" s="6"/>
-      <c r="L299" s="7"/>
-      <c r="M299" s="5"/>
+      <c r="A299" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B299" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C299" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="D299" s="26"/>
+      <c r="E299" s="26"/>
+      <c r="F299" s="15">
+        <v>1572</v>
+      </c>
+      <c r="G299" s="15">
+        <v>204</v>
+      </c>
+      <c r="H299" s="5">
+        <v>1000</v>
+      </c>
+      <c r="I299" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J299" s="17">
+        <v>1122.83</v>
+      </c>
+      <c r="K299" s="6">
+        <v>29</v>
+      </c>
+      <c r="L299" s="4">
+        <v>33.31</v>
+      </c>
+      <c r="M299" s="5">
+        <v>1156.1400000000001</v>
+      </c>
     </row>
     <row r="300" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A300" s="14"/>
-      <c r="B300" s="3"/>
-      <c r="C300" s="23"/>
-      <c r="D300" s="24"/>
-      <c r="E300" s="25"/>
-      <c r="F300" s="10"/>
-      <c r="G300" s="11"/>
-      <c r="H300" s="4"/>
-      <c r="I300" s="3"/>
-      <c r="J300" s="5"/>
-      <c r="K300" s="6"/>
-      <c r="L300" s="7"/>
-      <c r="M300" s="5"/>
+      <c r="A300" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B300" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C300" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D300" s="26"/>
+      <c r="E300" s="26"/>
+      <c r="F300" s="15">
+        <v>1470</v>
+      </c>
+      <c r="G300" s="15">
+        <v>602</v>
+      </c>
+      <c r="H300" s="5">
+        <v>763.85</v>
+      </c>
+      <c r="I300" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J300" s="17">
+        <v>875.47</v>
+      </c>
+      <c r="K300" s="6">
+        <v>13</v>
+      </c>
+      <c r="L300" s="4">
+        <v>21.3</v>
+      </c>
+      <c r="M300" s="5">
+        <v>896.77</v>
+      </c>
     </row>
     <row r="301" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A301" s="14"/>
-      <c r="B301" s="3"/>
-      <c r="C301" s="23"/>
-      <c r="D301" s="24"/>
-      <c r="E301" s="25"/>
-      <c r="F301" s="10"/>
-      <c r="G301" s="11"/>
-      <c r="H301" s="4"/>
-      <c r="I301" s="3"/>
-      <c r="J301" s="5"/>
-      <c r="K301" s="6"/>
-      <c r="L301" s="7"/>
-      <c r="M301" s="5"/>
+      <c r="A301" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B301" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C301" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="D301" s="26"/>
+      <c r="E301" s="26"/>
+      <c r="F301" s="15">
+        <v>1458</v>
+      </c>
+      <c r="G301" s="15">
+        <v>403</v>
+      </c>
+      <c r="H301" s="5">
+        <v>813.02</v>
+      </c>
+      <c r="I301" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J301" s="17">
+        <v>931.83</v>
+      </c>
+      <c r="K301" s="6">
+        <v>19</v>
+      </c>
+      <c r="L301" s="4">
+        <v>24.54</v>
+      </c>
+      <c r="M301" s="5">
+        <v>956.37</v>
+      </c>
     </row>
     <row r="302" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A302" s="14"/>
-      <c r="B302" s="3"/>
-      <c r="C302" s="23"/>
-      <c r="D302" s="24"/>
-      <c r="E302" s="25"/>
-      <c r="F302" s="10"/>
-      <c r="G302" s="11"/>
-      <c r="H302" s="4"/>
-      <c r="I302" s="3"/>
-      <c r="J302" s="5"/>
-      <c r="K302" s="6"/>
-      <c r="L302" s="7"/>
-      <c r="M302" s="5"/>
+      <c r="A302" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B302" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C302" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D302" s="26"/>
+      <c r="E302" s="26"/>
+      <c r="F302" s="15">
+        <v>1469</v>
+      </c>
+      <c r="G302" s="15">
+        <v>208</v>
+      </c>
+      <c r="H302" s="5">
+        <v>968.46</v>
+      </c>
+      <c r="I302" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J302" s="17">
+        <v>1109.98</v>
+      </c>
+      <c r="K302" s="6">
+        <v>45</v>
+      </c>
+      <c r="L302" s="4">
+        <v>38.85</v>
+      </c>
+      <c r="M302" s="5">
+        <v>1148.83</v>
+      </c>
     </row>
     <row r="303" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A303" s="14"/>
-      <c r="B303" s="3"/>
-      <c r="C303" s="23"/>
-      <c r="D303" s="24"/>
-      <c r="E303" s="25"/>
-      <c r="F303" s="10"/>
-      <c r="G303" s="11"/>
-      <c r="H303" s="4"/>
-      <c r="I303" s="3"/>
-      <c r="J303" s="5"/>
-      <c r="K303" s="6"/>
-      <c r="L303" s="7"/>
-      <c r="M303" s="5"/>
+      <c r="A303" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B303" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C303" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D303" s="26"/>
+      <c r="E303" s="26"/>
+      <c r="F303" s="15">
+        <v>1469</v>
+      </c>
+      <c r="G303" s="15">
+        <v>208</v>
+      </c>
+      <c r="H303" s="5">
+        <v>968.46</v>
+      </c>
+      <c r="I303" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J303" s="17">
+        <v>1109.98</v>
+      </c>
+      <c r="K303" s="6">
+        <v>14</v>
+      </c>
+      <c r="L303" s="4">
+        <v>27.38</v>
+      </c>
+      <c r="M303" s="5">
+        <v>1137.3599999999999</v>
+      </c>
     </row>
     <row r="304" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A304" s="14"/>
-      <c r="B304" s="3"/>
-      <c r="C304" s="23"/>
-      <c r="D304" s="24"/>
-      <c r="E304" s="25"/>
-      <c r="F304" s="10"/>
-      <c r="G304" s="11"/>
-      <c r="H304" s="4"/>
-      <c r="I304" s="3"/>
-      <c r="J304" s="5"/>
-      <c r="K304" s="6"/>
-      <c r="L304" s="7"/>
-      <c r="M304" s="5"/>
+      <c r="A304" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B304" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C304" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D304" s="26"/>
+      <c r="E304" s="26"/>
+      <c r="F304" s="15">
+        <v>1610</v>
+      </c>
+      <c r="G304" s="15">
+        <v>1003</v>
+      </c>
+      <c r="H304" s="5">
+        <v>1300</v>
+      </c>
+      <c r="I304" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J304" s="17">
+        <v>1252.07</v>
+      </c>
+      <c r="K304" s="6">
+        <v>76</v>
+      </c>
+      <c r="L304" s="4">
+        <v>56.76</v>
+      </c>
+      <c r="M304" s="5">
+        <v>1308.83</v>
+      </c>
     </row>
     <row r="305" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A305" s="14"/>
-      <c r="B305" s="3"/>
-      <c r="C305" s="23"/>
-      <c r="D305" s="24"/>
-      <c r="E305" s="25"/>
-      <c r="F305" s="10"/>
-      <c r="G305" s="11"/>
-      <c r="H305" s="4"/>
-      <c r="I305" s="3"/>
-      <c r="J305" s="5"/>
-      <c r="K305" s="6"/>
-      <c r="L305" s="7"/>
-      <c r="M305" s="5"/>
+      <c r="A305" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B305" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C305" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D305" s="26"/>
+      <c r="E305" s="26"/>
+      <c r="F305" s="15">
+        <v>1610</v>
+      </c>
+      <c r="G305" s="15">
+        <v>1003</v>
+      </c>
+      <c r="H305" s="5">
+        <v>1300</v>
+      </c>
+      <c r="I305" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J305" s="17">
+        <v>1439.02</v>
+      </c>
+      <c r="K305" s="6">
+        <v>48</v>
+      </c>
+      <c r="L305" s="4">
+        <v>51.8</v>
+      </c>
+      <c r="M305" s="5">
+        <v>1490.82</v>
+      </c>
     </row>
     <row r="306" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A306" s="14"/>
-      <c r="B306" s="3"/>
-      <c r="C306" s="23"/>
-      <c r="D306" s="24"/>
-      <c r="E306" s="25"/>
-      <c r="F306" s="10"/>
-      <c r="G306" s="11"/>
-      <c r="H306" s="4"/>
-      <c r="I306" s="3"/>
-      <c r="J306" s="5"/>
-      <c r="K306" s="6"/>
-      <c r="L306" s="7"/>
-      <c r="M306" s="5"/>
+      <c r="A306" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B306" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C306" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="D306" s="26"/>
+      <c r="E306" s="26"/>
+      <c r="F306" s="15">
+        <v>1499</v>
+      </c>
+      <c r="G306" s="15">
+        <v>606</v>
+      </c>
+      <c r="H306" s="5">
+        <v>1200</v>
+      </c>
+      <c r="I306" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J306" s="17">
+        <v>1371.65</v>
+      </c>
+      <c r="K306" s="6">
+        <v>29</v>
+      </c>
+      <c r="L306" s="4">
+        <v>40.69</v>
+      </c>
+      <c r="M306" s="5">
+        <v>1412.34</v>
+      </c>
     </row>
     <row r="307" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A307" s="14"/>
-      <c r="B307" s="3"/>
-      <c r="C307" s="23"/>
-      <c r="D307" s="24"/>
-      <c r="E307" s="25"/>
-      <c r="F307" s="10"/>
-      <c r="G307" s="11"/>
-      <c r="H307" s="4"/>
-      <c r="I307" s="3"/>
-      <c r="J307" s="5"/>
-      <c r="K307" s="6"/>
-      <c r="L307" s="7"/>
-      <c r="M307" s="5"/>
+      <c r="A307" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B307" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C307" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D307" s="26"/>
+      <c r="E307" s="26"/>
+      <c r="F307" s="15">
+        <v>1433</v>
+      </c>
+      <c r="G307" s="15">
+        <v>1406</v>
+      </c>
+      <c r="H307" s="5">
+        <v>3556.75</v>
+      </c>
+      <c r="I307" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J307" s="17">
+        <v>4076.5</v>
+      </c>
+      <c r="K307" s="6">
+        <v>231</v>
+      </c>
+      <c r="L307" s="4">
+        <v>395.42</v>
+      </c>
+      <c r="M307" s="5">
+        <v>4471.92</v>
+      </c>
     </row>
     <row r="308" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A308" s="14"/>
-      <c r="B308" s="3"/>
-      <c r="C308" s="23"/>
-      <c r="D308" s="24"/>
-      <c r="E308" s="25"/>
-      <c r="F308" s="10"/>
-      <c r="G308" s="11"/>
-      <c r="H308" s="4"/>
-      <c r="I308" s="3"/>
-      <c r="J308" s="5"/>
-      <c r="K308" s="6"/>
-      <c r="L308" s="7"/>
-      <c r="M308" s="5"/>
+      <c r="A308" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B308" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C308" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D308" s="26"/>
+      <c r="E308" s="26"/>
+      <c r="F308" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G308" s="15">
+        <v>506</v>
+      </c>
+      <c r="H308" s="5">
+        <v>688.62</v>
+      </c>
+      <c r="I308" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J308" s="17">
+        <v>786.1</v>
+      </c>
+      <c r="K308" s="6">
+        <v>145</v>
+      </c>
+      <c r="L308" s="4">
+        <v>53.71</v>
+      </c>
+      <c r="M308" s="5">
+        <v>839.81</v>
+      </c>
     </row>
     <row r="309" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A309" s="14"/>
-      <c r="B309" s="3"/>
-      <c r="C309" s="23"/>
-      <c r="D309" s="24"/>
-      <c r="E309" s="25"/>
-      <c r="F309" s="10"/>
-      <c r="G309" s="11"/>
-      <c r="H309" s="4"/>
-      <c r="I309" s="3"/>
-      <c r="J309" s="5"/>
-      <c r="K309" s="6"/>
-      <c r="L309" s="7"/>
-      <c r="M309" s="5"/>
+      <c r="A309" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B309" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C309" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D309" s="26"/>
+      <c r="E309" s="26"/>
+      <c r="F309" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G309" s="15">
+        <v>506</v>
+      </c>
+      <c r="H309" s="5">
+        <v>4340.6400000000003</v>
+      </c>
+      <c r="I309" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J309" s="17">
+        <v>4955.1000000000004</v>
+      </c>
+      <c r="K309" s="6">
+        <v>125</v>
+      </c>
+      <c r="L309" s="4">
+        <v>305.56</v>
+      </c>
+      <c r="M309" s="5">
+        <v>5260.66</v>
+      </c>
     </row>
     <row r="310" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A310" s="14"/>
-      <c r="B310" s="3"/>
-      <c r="C310" s="23"/>
-      <c r="D310" s="24"/>
-      <c r="E310" s="25"/>
-      <c r="F310" s="10"/>
-      <c r="G310" s="11"/>
-      <c r="H310" s="4"/>
-      <c r="I310" s="3"/>
-      <c r="J310" s="5"/>
-      <c r="K310" s="6"/>
-      <c r="L310" s="7"/>
-      <c r="M310" s="5"/>
+      <c r="A310" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B310" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C310" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D310" s="26"/>
+      <c r="E310" s="26"/>
+      <c r="F310" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G310" s="15">
+        <v>506</v>
+      </c>
+      <c r="H310" s="5">
+        <v>688.62</v>
+      </c>
+      <c r="I310" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J310" s="17">
+        <v>786.1</v>
+      </c>
+      <c r="K310" s="6">
+        <v>114</v>
+      </c>
+      <c r="L310" s="4">
+        <v>45.59</v>
+      </c>
+      <c r="M310" s="5">
+        <v>831.69</v>
+      </c>
     </row>
     <row r="311" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B311" s="3"/>
-      <c r="C311" s="23"/>
-      <c r="D311" s="24"/>
-      <c r="E311" s="25"/>
-      <c r="F311" s="10"/>
-      <c r="G311" s="11"/>
-      <c r="H311" s="4"/>
-      <c r="I311" s="3"/>
-      <c r="J311" s="5"/>
-      <c r="K311" s="6"/>
-      <c r="L311" s="7"/>
-      <c r="M311" s="5"/>
+      <c r="A311" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B311" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C311" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D311" s="26"/>
+      <c r="E311" s="26"/>
+      <c r="F311" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G311" s="15">
+        <v>506</v>
+      </c>
+      <c r="H311" s="5">
+        <v>688.62</v>
+      </c>
+      <c r="I311" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J311" s="17">
+        <v>786.1</v>
+      </c>
+      <c r="K311" s="6">
+        <v>83</v>
+      </c>
+      <c r="L311" s="4">
+        <v>37.47</v>
+      </c>
+      <c r="M311" s="5">
+        <v>823.57</v>
+      </c>
     </row>
     <row r="312" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B312" s="3"/>
-      <c r="C312" s="23"/>
-      <c r="D312" s="24"/>
-      <c r="E312" s="25"/>
-      <c r="F312" s="10"/>
-      <c r="G312" s="11"/>
-      <c r="H312" s="4"/>
-      <c r="I312" s="3"/>
-      <c r="J312" s="5"/>
-      <c r="K312" s="6"/>
-      <c r="L312" s="7"/>
-      <c r="M312" s="5"/>
+      <c r="A312" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B312" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C312" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D312" s="26"/>
+      <c r="E312" s="26"/>
+      <c r="F312" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G312" s="15">
+        <v>506</v>
+      </c>
+      <c r="H312" s="5">
+        <v>688.62</v>
+      </c>
+      <c r="I312" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J312" s="17">
+        <v>786.1</v>
+      </c>
+      <c r="K312" s="6">
+        <v>55</v>
+      </c>
+      <c r="L312" s="4">
+        <v>30.13</v>
+      </c>
+      <c r="M312" s="5">
+        <v>816.23</v>
+      </c>
     </row>
     <row r="313" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B313" s="3"/>
-      <c r="C313" s="23"/>
-      <c r="D313" s="24"/>
-      <c r="E313" s="25"/>
-      <c r="F313" s="10"/>
-      <c r="G313" s="11"/>
-      <c r="H313" s="4"/>
-      <c r="I313" s="3"/>
-      <c r="J313" s="5"/>
-      <c r="K313" s="6"/>
-      <c r="L313" s="7"/>
-      <c r="M313" s="5"/>
+      <c r="A313" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B313" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C313" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D313" s="26"/>
+      <c r="E313" s="26"/>
+      <c r="F313" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G313" s="15">
+        <v>506</v>
+      </c>
+      <c r="H313" s="5">
+        <v>688.62</v>
+      </c>
+      <c r="I313" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J313" s="17">
+        <v>786.1</v>
+      </c>
+      <c r="K313" s="6">
+        <v>24</v>
+      </c>
+      <c r="L313" s="4">
+        <v>22.01</v>
+      </c>
+      <c r="M313" s="5">
+        <v>808.11</v>
+      </c>
     </row>
     <row r="314" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B314" s="3"/>
-      <c r="C314" s="23"/>
-      <c r="D314" s="24"/>
-      <c r="E314" s="25"/>
-      <c r="F314" s="10"/>
-      <c r="G314" s="11"/>
-      <c r="H314" s="4"/>
-      <c r="I314" s="3"/>
-      <c r="J314" s="5"/>
-      <c r="K314" s="6"/>
-      <c r="L314" s="7"/>
-      <c r="M314" s="5"/>
+      <c r="A314" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B314" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C314" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D314" s="26"/>
+      <c r="E314" s="26"/>
+      <c r="F314" s="15">
+        <v>1641</v>
+      </c>
+      <c r="G314" s="15">
+        <v>1201</v>
+      </c>
+      <c r="H314" s="5">
+        <v>3383.42</v>
+      </c>
+      <c r="I314" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J314" s="17">
+        <v>3697.77</v>
+      </c>
+      <c r="K314" s="6">
+        <v>165</v>
+      </c>
+      <c r="L314" s="4">
+        <v>277.33999999999997</v>
+      </c>
+      <c r="M314" s="5">
+        <v>3975.11</v>
+      </c>
     </row>
     <row r="315" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B315" s="3"/>
-      <c r="C315" s="23"/>
-      <c r="D315" s="24"/>
-      <c r="E315" s="25"/>
-      <c r="F315" s="10"/>
-      <c r="G315" s="11"/>
-      <c r="H315" s="4"/>
-      <c r="I315" s="3"/>
-      <c r="J315" s="5"/>
-      <c r="K315" s="6"/>
-      <c r="L315" s="7"/>
-      <c r="M315" s="5"/>
+      <c r="A315" s="14">
+        <v>46113</v>
+      </c>
+      <c r="B315" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C315" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="D315" s="26"/>
+      <c r="E315" s="26"/>
+      <c r="F315" s="15">
+        <v>1641</v>
+      </c>
+      <c r="G315" s="15">
+        <v>1201</v>
+      </c>
+      <c r="H315" s="5">
+        <v>748.18</v>
+      </c>
+      <c r="I315" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J315" s="17">
+        <v>817.69</v>
+      </c>
+      <c r="K315" s="6">
+        <v>14</v>
+      </c>
+      <c r="L315" s="4">
+        <v>20.170000000000002</v>
+      </c>
+      <c r="M315" s="5">
+        <v>837.86</v>
+      </c>
     </row>
     <row r="316" spans="1:13" x14ac:dyDescent="0.25">
       <c r="B316" s="3"/>
@@ -12236,22 +12815,284 @@
     </row>
   </sheetData>
   <mergeCells count="318">
-    <mergeCell ref="C127:E127"/>
-    <mergeCell ref="C128:E128"/>
-    <mergeCell ref="C129:E129"/>
-    <mergeCell ref="C130:E130"/>
-    <mergeCell ref="C131:E131"/>
-    <mergeCell ref="C132:E132"/>
-    <mergeCell ref="C142:E142"/>
-    <mergeCell ref="C133:E133"/>
-    <mergeCell ref="C134:E134"/>
-    <mergeCell ref="C135:E135"/>
-    <mergeCell ref="C136:E136"/>
-    <mergeCell ref="C137:E137"/>
-    <mergeCell ref="C138:E138"/>
-    <mergeCell ref="C139:E139"/>
-    <mergeCell ref="C140:E140"/>
-    <mergeCell ref="C141:E141"/>
+    <mergeCell ref="C291:E291"/>
+    <mergeCell ref="C292:E292"/>
+    <mergeCell ref="C293:E293"/>
+    <mergeCell ref="C294:E294"/>
+    <mergeCell ref="C295:E295"/>
+    <mergeCell ref="C314:E314"/>
+    <mergeCell ref="C315:E315"/>
+    <mergeCell ref="C316:E316"/>
+    <mergeCell ref="C317:E317"/>
+    <mergeCell ref="C318:E318"/>
+    <mergeCell ref="C305:E305"/>
+    <mergeCell ref="C306:E306"/>
+    <mergeCell ref="C307:E307"/>
+    <mergeCell ref="C308:E308"/>
+    <mergeCell ref="C309:E309"/>
+    <mergeCell ref="C310:E310"/>
+    <mergeCell ref="C311:E311"/>
+    <mergeCell ref="C312:E312"/>
+    <mergeCell ref="C313:E313"/>
+    <mergeCell ref="C296:E296"/>
+    <mergeCell ref="C297:E297"/>
+    <mergeCell ref="C298:E298"/>
+    <mergeCell ref="C299:E299"/>
+    <mergeCell ref="C300:E300"/>
+    <mergeCell ref="C301:E301"/>
+    <mergeCell ref="C302:E302"/>
+    <mergeCell ref="C303:E303"/>
+    <mergeCell ref="C304:E304"/>
+    <mergeCell ref="C287:E287"/>
+    <mergeCell ref="C288:E288"/>
+    <mergeCell ref="C289:E289"/>
+    <mergeCell ref="C290:E290"/>
+    <mergeCell ref="C278:E278"/>
+    <mergeCell ref="C279:E279"/>
+    <mergeCell ref="C280:E280"/>
+    <mergeCell ref="C281:E281"/>
+    <mergeCell ref="C282:E282"/>
+    <mergeCell ref="C283:E283"/>
+    <mergeCell ref="C284:E284"/>
+    <mergeCell ref="C285:E285"/>
+    <mergeCell ref="C286:E286"/>
+    <mergeCell ref="C269:E269"/>
+    <mergeCell ref="C270:E270"/>
+    <mergeCell ref="C271:E271"/>
+    <mergeCell ref="C272:E272"/>
+    <mergeCell ref="C273:E273"/>
+    <mergeCell ref="C274:E274"/>
+    <mergeCell ref="C275:E275"/>
+    <mergeCell ref="C276:E276"/>
+    <mergeCell ref="C277:E277"/>
+    <mergeCell ref="C260:E260"/>
+    <mergeCell ref="C261:E261"/>
+    <mergeCell ref="C262:E262"/>
+    <mergeCell ref="C263:E263"/>
+    <mergeCell ref="C264:E264"/>
+    <mergeCell ref="C265:E265"/>
+    <mergeCell ref="C266:E266"/>
+    <mergeCell ref="C267:E267"/>
+    <mergeCell ref="C268:E268"/>
+    <mergeCell ref="C251:E251"/>
+    <mergeCell ref="C252:E252"/>
+    <mergeCell ref="C253:E253"/>
+    <mergeCell ref="C254:E254"/>
+    <mergeCell ref="C255:E255"/>
+    <mergeCell ref="C256:E256"/>
+    <mergeCell ref="C257:E257"/>
+    <mergeCell ref="C258:E258"/>
+    <mergeCell ref="C259:E259"/>
+    <mergeCell ref="C242:E242"/>
+    <mergeCell ref="C243:E243"/>
+    <mergeCell ref="C244:E244"/>
+    <mergeCell ref="C245:E245"/>
+    <mergeCell ref="C246:E246"/>
+    <mergeCell ref="C247:E247"/>
+    <mergeCell ref="C248:E248"/>
+    <mergeCell ref="C249:E249"/>
+    <mergeCell ref="C250:E250"/>
+    <mergeCell ref="C233:E233"/>
+    <mergeCell ref="C234:E234"/>
+    <mergeCell ref="C235:E235"/>
+    <mergeCell ref="C236:E236"/>
+    <mergeCell ref="C237:E237"/>
+    <mergeCell ref="C238:E238"/>
+    <mergeCell ref="C239:E239"/>
+    <mergeCell ref="C240:E240"/>
+    <mergeCell ref="C241:E241"/>
+    <mergeCell ref="C224:E224"/>
+    <mergeCell ref="C225:E225"/>
+    <mergeCell ref="C226:E226"/>
+    <mergeCell ref="C227:E227"/>
+    <mergeCell ref="C228:E228"/>
+    <mergeCell ref="C229:E229"/>
+    <mergeCell ref="C230:E230"/>
+    <mergeCell ref="C231:E231"/>
+    <mergeCell ref="C232:E232"/>
+    <mergeCell ref="C215:E215"/>
+    <mergeCell ref="C216:E216"/>
+    <mergeCell ref="C217:E217"/>
+    <mergeCell ref="C218:E218"/>
+    <mergeCell ref="C219:E219"/>
+    <mergeCell ref="C220:E220"/>
+    <mergeCell ref="C221:E221"/>
+    <mergeCell ref="C222:E222"/>
+    <mergeCell ref="C223:E223"/>
+    <mergeCell ref="C206:E206"/>
+    <mergeCell ref="C207:E207"/>
+    <mergeCell ref="C208:E208"/>
+    <mergeCell ref="C209:E209"/>
+    <mergeCell ref="C210:E210"/>
+    <mergeCell ref="C211:E211"/>
+    <mergeCell ref="C212:E212"/>
+    <mergeCell ref="C213:E213"/>
+    <mergeCell ref="C214:E214"/>
+    <mergeCell ref="C197:E197"/>
+    <mergeCell ref="C198:E198"/>
+    <mergeCell ref="C199:E199"/>
+    <mergeCell ref="C200:E200"/>
+    <mergeCell ref="C201:E201"/>
+    <mergeCell ref="C202:E202"/>
+    <mergeCell ref="C203:E203"/>
+    <mergeCell ref="C204:E204"/>
+    <mergeCell ref="C205:E205"/>
+    <mergeCell ref="C188:E188"/>
+    <mergeCell ref="C189:E189"/>
+    <mergeCell ref="C190:E190"/>
+    <mergeCell ref="C191:E191"/>
+    <mergeCell ref="C192:E192"/>
+    <mergeCell ref="C193:E193"/>
+    <mergeCell ref="C194:E194"/>
+    <mergeCell ref="C195:E195"/>
+    <mergeCell ref="C196:E196"/>
+    <mergeCell ref="C179:E179"/>
+    <mergeCell ref="C180:E180"/>
+    <mergeCell ref="C181:E181"/>
+    <mergeCell ref="C182:E182"/>
+    <mergeCell ref="C183:E183"/>
+    <mergeCell ref="C184:E184"/>
+    <mergeCell ref="C185:E185"/>
+    <mergeCell ref="C186:E186"/>
+    <mergeCell ref="C187:E187"/>
+    <mergeCell ref="C170:E170"/>
+    <mergeCell ref="C171:E171"/>
+    <mergeCell ref="C172:E172"/>
+    <mergeCell ref="C173:E173"/>
+    <mergeCell ref="C174:E174"/>
+    <mergeCell ref="C175:E175"/>
+    <mergeCell ref="C176:E176"/>
+    <mergeCell ref="C177:E177"/>
+    <mergeCell ref="C178:E178"/>
+    <mergeCell ref="C161:E161"/>
+    <mergeCell ref="C162:E162"/>
+    <mergeCell ref="C163:E163"/>
+    <mergeCell ref="C164:E164"/>
+    <mergeCell ref="C165:E165"/>
+    <mergeCell ref="C166:E166"/>
+    <mergeCell ref="C167:E167"/>
+    <mergeCell ref="C168:E168"/>
+    <mergeCell ref="C169:E169"/>
+    <mergeCell ref="C152:E152"/>
+    <mergeCell ref="C153:E153"/>
+    <mergeCell ref="C154:E154"/>
+    <mergeCell ref="C155:E155"/>
+    <mergeCell ref="C156:E156"/>
+    <mergeCell ref="C157:E157"/>
+    <mergeCell ref="C158:E158"/>
+    <mergeCell ref="C159:E159"/>
+    <mergeCell ref="C160:E160"/>
+    <mergeCell ref="C143:E143"/>
+    <mergeCell ref="C144:E144"/>
+    <mergeCell ref="C145:E145"/>
+    <mergeCell ref="C146:E146"/>
+    <mergeCell ref="C147:E147"/>
+    <mergeCell ref="C148:E148"/>
+    <mergeCell ref="C149:E149"/>
+    <mergeCell ref="C150:E150"/>
+    <mergeCell ref="C151:E151"/>
+    <mergeCell ref="C122:E122"/>
+    <mergeCell ref="C123:E123"/>
+    <mergeCell ref="C117:E117"/>
+    <mergeCell ref="C118:E118"/>
+    <mergeCell ref="C119:E119"/>
+    <mergeCell ref="C120:E120"/>
+    <mergeCell ref="C121:E121"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="C113:E113"/>
+    <mergeCell ref="C114:E114"/>
+    <mergeCell ref="C115:E115"/>
+    <mergeCell ref="C116:E116"/>
+    <mergeCell ref="C107:E107"/>
+    <mergeCell ref="C108:E108"/>
+    <mergeCell ref="C109:E109"/>
+    <mergeCell ref="C110:E110"/>
+    <mergeCell ref="C111:E111"/>
+    <mergeCell ref="C102:E102"/>
+    <mergeCell ref="C103:E103"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="C105:E105"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="C100:E100"/>
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="C13:E13"/>
@@ -12276,284 +13117,22 @@
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="C98:E98"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="C100:E100"/>
-    <mergeCell ref="C101:E101"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="C88:E88"/>
-    <mergeCell ref="C89:E89"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="C94:E94"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="C107:E107"/>
-    <mergeCell ref="C108:E108"/>
-    <mergeCell ref="C109:E109"/>
-    <mergeCell ref="C110:E110"/>
-    <mergeCell ref="C111:E111"/>
-    <mergeCell ref="C102:E102"/>
-    <mergeCell ref="C103:E103"/>
-    <mergeCell ref="C104:E104"/>
-    <mergeCell ref="C105:E105"/>
-    <mergeCell ref="C106:E106"/>
-    <mergeCell ref="C122:E122"/>
-    <mergeCell ref="C123:E123"/>
-    <mergeCell ref="C117:E117"/>
-    <mergeCell ref="C118:E118"/>
-    <mergeCell ref="C119:E119"/>
-    <mergeCell ref="C120:E120"/>
-    <mergeCell ref="C121:E121"/>
-    <mergeCell ref="C112:E112"/>
-    <mergeCell ref="C113:E113"/>
-    <mergeCell ref="C114:E114"/>
-    <mergeCell ref="C115:E115"/>
-    <mergeCell ref="C116:E116"/>
-    <mergeCell ref="C143:E143"/>
-    <mergeCell ref="C144:E144"/>
-    <mergeCell ref="C145:E145"/>
-    <mergeCell ref="C146:E146"/>
-    <mergeCell ref="C147:E147"/>
-    <mergeCell ref="C148:E148"/>
-    <mergeCell ref="C149:E149"/>
-    <mergeCell ref="C150:E150"/>
-    <mergeCell ref="C151:E151"/>
-    <mergeCell ref="C152:E152"/>
-    <mergeCell ref="C153:E153"/>
-    <mergeCell ref="C154:E154"/>
-    <mergeCell ref="C155:E155"/>
-    <mergeCell ref="C156:E156"/>
-    <mergeCell ref="C157:E157"/>
-    <mergeCell ref="C158:E158"/>
-    <mergeCell ref="C159:E159"/>
-    <mergeCell ref="C160:E160"/>
-    <mergeCell ref="C161:E161"/>
-    <mergeCell ref="C162:E162"/>
-    <mergeCell ref="C163:E163"/>
-    <mergeCell ref="C164:E164"/>
-    <mergeCell ref="C165:E165"/>
-    <mergeCell ref="C166:E166"/>
-    <mergeCell ref="C167:E167"/>
-    <mergeCell ref="C168:E168"/>
-    <mergeCell ref="C169:E169"/>
-    <mergeCell ref="C170:E170"/>
-    <mergeCell ref="C171:E171"/>
-    <mergeCell ref="C172:E172"/>
-    <mergeCell ref="C173:E173"/>
-    <mergeCell ref="C174:E174"/>
-    <mergeCell ref="C175:E175"/>
-    <mergeCell ref="C176:E176"/>
-    <mergeCell ref="C177:E177"/>
-    <mergeCell ref="C178:E178"/>
-    <mergeCell ref="C179:E179"/>
-    <mergeCell ref="C180:E180"/>
-    <mergeCell ref="C181:E181"/>
-    <mergeCell ref="C182:E182"/>
-    <mergeCell ref="C183:E183"/>
-    <mergeCell ref="C184:E184"/>
-    <mergeCell ref="C185:E185"/>
-    <mergeCell ref="C186:E186"/>
-    <mergeCell ref="C187:E187"/>
-    <mergeCell ref="C188:E188"/>
-    <mergeCell ref="C189:E189"/>
-    <mergeCell ref="C190:E190"/>
-    <mergeCell ref="C191:E191"/>
-    <mergeCell ref="C192:E192"/>
-    <mergeCell ref="C193:E193"/>
-    <mergeCell ref="C194:E194"/>
-    <mergeCell ref="C195:E195"/>
-    <mergeCell ref="C196:E196"/>
-    <mergeCell ref="C197:E197"/>
-    <mergeCell ref="C198:E198"/>
-    <mergeCell ref="C199:E199"/>
-    <mergeCell ref="C200:E200"/>
-    <mergeCell ref="C201:E201"/>
-    <mergeCell ref="C202:E202"/>
-    <mergeCell ref="C203:E203"/>
-    <mergeCell ref="C204:E204"/>
-    <mergeCell ref="C205:E205"/>
-    <mergeCell ref="C206:E206"/>
-    <mergeCell ref="C207:E207"/>
-    <mergeCell ref="C208:E208"/>
-    <mergeCell ref="C209:E209"/>
-    <mergeCell ref="C210:E210"/>
-    <mergeCell ref="C211:E211"/>
-    <mergeCell ref="C212:E212"/>
-    <mergeCell ref="C213:E213"/>
-    <mergeCell ref="C214:E214"/>
-    <mergeCell ref="C215:E215"/>
-    <mergeCell ref="C216:E216"/>
-    <mergeCell ref="C217:E217"/>
-    <mergeCell ref="C218:E218"/>
-    <mergeCell ref="C219:E219"/>
-    <mergeCell ref="C220:E220"/>
-    <mergeCell ref="C221:E221"/>
-    <mergeCell ref="C222:E222"/>
-    <mergeCell ref="C223:E223"/>
-    <mergeCell ref="C224:E224"/>
-    <mergeCell ref="C225:E225"/>
-    <mergeCell ref="C226:E226"/>
-    <mergeCell ref="C227:E227"/>
-    <mergeCell ref="C228:E228"/>
-    <mergeCell ref="C229:E229"/>
-    <mergeCell ref="C230:E230"/>
-    <mergeCell ref="C231:E231"/>
-    <mergeCell ref="C232:E232"/>
-    <mergeCell ref="C233:E233"/>
-    <mergeCell ref="C234:E234"/>
-    <mergeCell ref="C235:E235"/>
-    <mergeCell ref="C236:E236"/>
-    <mergeCell ref="C237:E237"/>
-    <mergeCell ref="C238:E238"/>
-    <mergeCell ref="C239:E239"/>
-    <mergeCell ref="C240:E240"/>
-    <mergeCell ref="C241:E241"/>
-    <mergeCell ref="C242:E242"/>
-    <mergeCell ref="C243:E243"/>
-    <mergeCell ref="C244:E244"/>
-    <mergeCell ref="C245:E245"/>
-    <mergeCell ref="C246:E246"/>
-    <mergeCell ref="C247:E247"/>
-    <mergeCell ref="C248:E248"/>
-    <mergeCell ref="C249:E249"/>
-    <mergeCell ref="C250:E250"/>
-    <mergeCell ref="C251:E251"/>
-    <mergeCell ref="C252:E252"/>
-    <mergeCell ref="C253:E253"/>
-    <mergeCell ref="C254:E254"/>
-    <mergeCell ref="C255:E255"/>
-    <mergeCell ref="C256:E256"/>
-    <mergeCell ref="C257:E257"/>
-    <mergeCell ref="C258:E258"/>
-    <mergeCell ref="C259:E259"/>
-    <mergeCell ref="C260:E260"/>
-    <mergeCell ref="C261:E261"/>
-    <mergeCell ref="C262:E262"/>
-    <mergeCell ref="C263:E263"/>
-    <mergeCell ref="C264:E264"/>
-    <mergeCell ref="C265:E265"/>
-    <mergeCell ref="C266:E266"/>
-    <mergeCell ref="C267:E267"/>
-    <mergeCell ref="C268:E268"/>
-    <mergeCell ref="C269:E269"/>
-    <mergeCell ref="C270:E270"/>
-    <mergeCell ref="C271:E271"/>
-    <mergeCell ref="C272:E272"/>
-    <mergeCell ref="C273:E273"/>
-    <mergeCell ref="C274:E274"/>
-    <mergeCell ref="C275:E275"/>
-    <mergeCell ref="C276:E276"/>
-    <mergeCell ref="C277:E277"/>
-    <mergeCell ref="C278:E278"/>
-    <mergeCell ref="C279:E279"/>
-    <mergeCell ref="C280:E280"/>
-    <mergeCell ref="C281:E281"/>
-    <mergeCell ref="C282:E282"/>
-    <mergeCell ref="C283:E283"/>
-    <mergeCell ref="C284:E284"/>
-    <mergeCell ref="C285:E285"/>
-    <mergeCell ref="C286:E286"/>
-    <mergeCell ref="C287:E287"/>
-    <mergeCell ref="C288:E288"/>
-    <mergeCell ref="C289:E289"/>
-    <mergeCell ref="C290:E290"/>
-    <mergeCell ref="C291:E291"/>
-    <mergeCell ref="C292:E292"/>
-    <mergeCell ref="C293:E293"/>
-    <mergeCell ref="C294:E294"/>
-    <mergeCell ref="C295:E295"/>
-    <mergeCell ref="C296:E296"/>
-    <mergeCell ref="C297:E297"/>
-    <mergeCell ref="C298:E298"/>
-    <mergeCell ref="C299:E299"/>
-    <mergeCell ref="C300:E300"/>
-    <mergeCell ref="C301:E301"/>
-    <mergeCell ref="C302:E302"/>
-    <mergeCell ref="C303:E303"/>
-    <mergeCell ref="C304:E304"/>
-    <mergeCell ref="C314:E314"/>
-    <mergeCell ref="C315:E315"/>
-    <mergeCell ref="C316:E316"/>
-    <mergeCell ref="C317:E317"/>
-    <mergeCell ref="C318:E318"/>
-    <mergeCell ref="C305:E305"/>
-    <mergeCell ref="C306:E306"/>
-    <mergeCell ref="C307:E307"/>
-    <mergeCell ref="C308:E308"/>
-    <mergeCell ref="C309:E309"/>
-    <mergeCell ref="C310:E310"/>
-    <mergeCell ref="C311:E311"/>
-    <mergeCell ref="C312:E312"/>
-    <mergeCell ref="C313:E313"/>
+    <mergeCell ref="C127:E127"/>
+    <mergeCell ref="C128:E128"/>
+    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="C130:E130"/>
+    <mergeCell ref="C131:E131"/>
+    <mergeCell ref="C132:E132"/>
+    <mergeCell ref="C142:E142"/>
+    <mergeCell ref="C133:E133"/>
+    <mergeCell ref="C134:E134"/>
+    <mergeCell ref="C135:E135"/>
+    <mergeCell ref="C136:E136"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="C138:E138"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="C141:E141"/>
   </mergeCells>
   <pageMargins left="0.52999994886203072" right="0.52999994886203072" top="0.52999994886203072" bottom="0.68999998212799307" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/data/vendas-inadimplentes.xlsx
+++ b/data/vendas-inadimplentes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30030"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30125"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64F3D1F-70EF-49ED-9BD9-C615EABF3CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B2307E-D3F8-4CAD-8301-522A51762F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="958" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="158">
   <si>
     <t>Data vecto</t>
   </si>
@@ -480,6 +480,33 @@
   </si>
   <si>
     <t>10/04/2026</t>
+  </si>
+  <si>
+    <t>01/04/2026</t>
+  </si>
+  <si>
+    <t>05/05/2026</t>
+  </si>
+  <si>
+    <t>10/05/2026</t>
+  </si>
+  <si>
+    <t>15/05/2026</t>
+  </si>
+  <si>
+    <t>PEDRO GABRIEL DINIZ MONTEIRO (333)</t>
+  </si>
+  <si>
+    <t>17/05/2026</t>
+  </si>
+  <si>
+    <t>20/05/2026</t>
+  </si>
+  <si>
+    <t>21/05/2026</t>
+  </si>
+  <si>
+    <t>30/05/2026</t>
   </si>
 </sst>
 </file>
@@ -666,6 +693,9 @@
     <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -673,9 +703,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1023,7 +1050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N318"/>
+  <dimension ref="A1:N369"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -1086,11 +1113,11 @@
       <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="26"/>
       <c r="F2" s="10">
         <v>1508</v>
       </c>
@@ -1123,11 +1150,11 @@
       <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
       <c r="F3" s="10">
         <v>1467</v>
       </c>
@@ -1160,11 +1187,11 @@
       <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
       <c r="F4" s="10">
         <v>1467</v>
       </c>
@@ -1197,11 +1224,11 @@
       <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
       <c r="F5" s="10">
         <v>1467</v>
       </c>
@@ -1234,11 +1261,11 @@
       <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="23"/>
       <c r="F6" s="10">
         <v>1467</v>
       </c>
@@ -1271,11 +1298,11 @@
       <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
       <c r="F7" s="10">
         <v>1613</v>
       </c>
@@ -1308,11 +1335,11 @@
       <c r="B8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="23"/>
       <c r="F8" s="10">
         <v>1613</v>
       </c>
@@ -1345,11 +1372,11 @@
       <c r="B9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
       <c r="F9" s="10">
         <v>1613</v>
       </c>
@@ -1382,11 +1409,11 @@
       <c r="B10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
       <c r="F10" s="10">
         <v>1613</v>
       </c>
@@ -1419,11 +1446,11 @@
       <c r="B11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
       <c r="F11" s="10">
         <v>1613</v>
       </c>
@@ -1456,11 +1483,11 @@
       <c r="B12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
       <c r="F12" s="10">
         <v>1613</v>
       </c>
@@ -1493,11 +1520,11 @@
       <c r="B13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
       <c r="F13" s="10">
         <v>1613</v>
       </c>
@@ -1530,11 +1557,11 @@
       <c r="B14" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
       <c r="F14" s="10">
         <v>1613</v>
       </c>
@@ -1567,11 +1594,11 @@
       <c r="B15" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
       <c r="F15" s="10">
         <v>1613</v>
       </c>
@@ -1604,11 +1631,11 @@
       <c r="B16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
       <c r="F16" s="10">
         <v>1416</v>
       </c>
@@ -1641,11 +1668,11 @@
       <c r="B17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="26"/>
-      <c r="E17" s="26"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
       <c r="F17" s="10">
         <v>1635</v>
       </c>
@@ -1678,11 +1705,11 @@
       <c r="B18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
       <c r="F18" s="10">
         <v>1635</v>
       </c>
@@ -1715,11 +1742,11 @@
       <c r="B19" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
       <c r="F19" s="10">
         <v>1635</v>
       </c>
@@ -1752,11 +1779,11 @@
       <c r="B20" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="26"/>
-      <c r="E20" s="26"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
       <c r="F20" s="10">
         <v>1635</v>
       </c>
@@ -1789,11 +1816,11 @@
       <c r="B21" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="26"/>
-      <c r="E21" s="26"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
       <c r="F21" s="10">
         <v>1549</v>
       </c>
@@ -1826,11 +1853,11 @@
       <c r="B22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
       <c r="F22" s="10">
         <v>1549</v>
       </c>
@@ -1863,11 +1890,11 @@
       <c r="B23" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
       <c r="F23" s="10">
         <v>1549</v>
       </c>
@@ -1900,11 +1927,11 @@
       <c r="B24" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="26"/>
-      <c r="E24" s="26"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
       <c r="F24" s="10">
         <v>1549</v>
       </c>
@@ -1937,11 +1964,11 @@
       <c r="B25" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
       <c r="F25" s="10">
         <v>1455</v>
       </c>
@@ -1974,11 +2001,11 @@
       <c r="B26" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="26"/>
-      <c r="E26" s="26"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
       <c r="F26" s="10">
         <v>1455</v>
       </c>
@@ -2011,11 +2038,11 @@
       <c r="B27" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="23" t="s">
         <v>34</v>
       </c>
-      <c r="D27" s="26"/>
-      <c r="E27" s="26"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
       <c r="F27" s="10">
         <v>1455</v>
       </c>
@@ -2048,11 +2075,11 @@
       <c r="B28" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
       <c r="F28" s="10">
         <v>1446</v>
       </c>
@@ -2085,11 +2112,11 @@
       <c r="B29" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C29" s="26" t="s">
+      <c r="C29" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
       <c r="F29" s="10">
         <v>1446</v>
       </c>
@@ -2122,11 +2149,11 @@
       <c r="B30" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="26"/>
-      <c r="E30" s="26"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
       <c r="F30" s="10">
         <v>1446</v>
       </c>
@@ -2159,11 +2186,11 @@
       <c r="B31" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="26" t="s">
+      <c r="C31" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="D31" s="26"/>
-      <c r="E31" s="26"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
       <c r="F31" s="10">
         <v>1461</v>
       </c>
@@ -2196,11 +2223,11 @@
       <c r="B32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="26" t="s">
+      <c r="C32" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="D32" s="26"/>
-      <c r="E32" s="26"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
       <c r="F32" s="10">
         <v>1461</v>
       </c>
@@ -2233,11 +2260,11 @@
       <c r="B33" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="26" t="s">
+      <c r="C33" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="D33" s="26"/>
-      <c r="E33" s="26"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
       <c r="F33" s="10">
         <v>1461</v>
       </c>
@@ -2270,11 +2297,11 @@
       <c r="B34" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C34" s="26" t="s">
+      <c r="C34" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D34" s="26"/>
-      <c r="E34" s="26"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
       <c r="F34" s="10">
         <v>1453</v>
       </c>
@@ -2307,11 +2334,11 @@
       <c r="B35" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
       <c r="F35" s="10">
         <v>1453</v>
       </c>
@@ -2344,11 +2371,11 @@
       <c r="B36" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="26" t="s">
+      <c r="C36" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
       <c r="F36" s="10">
         <v>1425</v>
       </c>
@@ -2381,11 +2408,11 @@
       <c r="B37" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="26" t="s">
+      <c r="C37" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D37" s="26"/>
-      <c r="E37" s="26"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
       <c r="F37" s="10">
         <v>1425</v>
       </c>
@@ -2418,11 +2445,11 @@
       <c r="B38" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="26" t="s">
+      <c r="C38" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D38" s="26"/>
-      <c r="E38" s="26"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
       <c r="F38" s="10">
         <v>1425</v>
       </c>
@@ -2455,11 +2482,11 @@
       <c r="B39" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C39" s="26" t="s">
+      <c r="C39" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D39" s="26"/>
-      <c r="E39" s="26"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
       <c r="F39" s="10">
         <v>1425</v>
       </c>
@@ -2492,11 +2519,11 @@
       <c r="B40" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C40" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D40" s="26"/>
-      <c r="E40" s="26"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
       <c r="F40" s="10">
         <v>1425</v>
       </c>
@@ -2529,11 +2556,11 @@
       <c r="B41" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C41" s="26" t="s">
+      <c r="C41" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
       <c r="F41" s="10">
         <v>1425</v>
       </c>
@@ -2566,11 +2593,11 @@
       <c r="B42" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C42" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
       <c r="F42" s="10">
         <v>1425</v>
       </c>
@@ -2603,11 +2630,11 @@
       <c r="B43" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C43" s="26" t="s">
+      <c r="C43" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
       <c r="F43" s="10">
         <v>1641</v>
       </c>
@@ -2640,11 +2667,11 @@
       <c r="B44" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C44" s="26" t="s">
+      <c r="C44" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D44" s="26"/>
-      <c r="E44" s="26"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
       <c r="F44" s="10">
         <v>1641</v>
       </c>
@@ -2677,11 +2704,11 @@
       <c r="B45" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C45" s="23" t="s">
+      <c r="C45" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="D45" s="24"/>
-      <c r="E45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="26"/>
       <c r="F45" s="10">
         <v>1477</v>
       </c>
@@ -2714,11 +2741,11 @@
       <c r="B46" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C46" s="23" t="s">
+      <c r="C46" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="D46" s="24"/>
-      <c r="E46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="26"/>
       <c r="F46" s="10">
         <v>1508</v>
       </c>
@@ -2751,11 +2778,11 @@
       <c r="B47" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C47" s="23" t="s">
+      <c r="C47" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="D47" s="24"/>
-      <c r="E47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="26"/>
       <c r="F47" s="10">
         <v>1508</v>
       </c>
@@ -2788,11 +2815,11 @@
       <c r="B48" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C48" s="23" t="s">
+      <c r="C48" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D48" s="24"/>
-      <c r="E48" s="25"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="26"/>
       <c r="F48" s="10">
         <v>1467</v>
       </c>
@@ -2825,11 +2852,11 @@
       <c r="B49" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="23" t="s">
+      <c r="C49" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D49" s="24"/>
-      <c r="E49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="26"/>
       <c r="F49" s="10">
         <v>1467</v>
       </c>
@@ -2862,11 +2889,11 @@
       <c r="B50" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="23" t="s">
+      <c r="C50" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D50" s="24"/>
-      <c r="E50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="26"/>
       <c r="F50" s="10">
         <v>1467</v>
       </c>
@@ -2899,11 +2926,11 @@
       <c r="B51" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="23" t="s">
+      <c r="C51" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D51" s="24"/>
-      <c r="E51" s="25"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="26"/>
       <c r="F51" s="10">
         <v>1467</v>
       </c>
@@ -2936,11 +2963,11 @@
       <c r="B52" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C52" s="23" t="s">
+      <c r="C52" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D52" s="24"/>
-      <c r="E52" s="25"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="26"/>
       <c r="F52" s="10">
         <v>1467</v>
       </c>
@@ -2973,11 +3000,11 @@
       <c r="B53" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="23" t="s">
+      <c r="C53" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D53" s="24"/>
-      <c r="E53" s="25"/>
+      <c r="D53" s="25"/>
+      <c r="E53" s="26"/>
       <c r="F53" s="10">
         <v>1613</v>
       </c>
@@ -3010,11 +3037,11 @@
       <c r="B54" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="23" t="s">
+      <c r="C54" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D54" s="24"/>
-      <c r="E54" s="25"/>
+      <c r="D54" s="25"/>
+      <c r="E54" s="26"/>
       <c r="F54" s="10">
         <v>1613</v>
       </c>
@@ -3048,11 +3075,11 @@
       <c r="B55" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C55" s="23" t="s">
+      <c r="C55" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D55" s="24"/>
-      <c r="E55" s="25"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="26"/>
       <c r="F55" s="10">
         <v>1613</v>
       </c>
@@ -3085,11 +3112,11 @@
       <c r="B56" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C56" s="23" t="s">
+      <c r="C56" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D56" s="24"/>
-      <c r="E56" s="25"/>
+      <c r="D56" s="25"/>
+      <c r="E56" s="26"/>
       <c r="F56" s="10">
         <v>1613</v>
       </c>
@@ -3122,11 +3149,11 @@
       <c r="B57" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C57" s="23" t="s">
+      <c r="C57" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D57" s="24"/>
-      <c r="E57" s="25"/>
+      <c r="D57" s="25"/>
+      <c r="E57" s="26"/>
       <c r="F57" s="10">
         <v>1613</v>
       </c>
@@ -3159,11 +3186,11 @@
       <c r="B58" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D58" s="24"/>
-      <c r="E58" s="25"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="26"/>
       <c r="F58" s="10">
         <v>1613</v>
       </c>
@@ -3196,11 +3223,11 @@
       <c r="B59" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C59" s="23" t="s">
+      <c r="C59" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D59" s="24"/>
-      <c r="E59" s="25"/>
+      <c r="D59" s="25"/>
+      <c r="E59" s="26"/>
       <c r="F59" s="10">
         <v>1613</v>
       </c>
@@ -3233,11 +3260,11 @@
       <c r="B60" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D60" s="24"/>
-      <c r="E60" s="25"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="26"/>
       <c r="F60" s="10">
         <v>1613</v>
       </c>
@@ -3270,11 +3297,11 @@
       <c r="B61" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C61" s="23" t="s">
+      <c r="C61" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D61" s="24"/>
-      <c r="E61" s="25"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="26"/>
       <c r="F61" s="10">
         <v>1613</v>
       </c>
@@ -3307,11 +3334,11 @@
       <c r="B62" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D62" s="24"/>
-      <c r="E62" s="25"/>
+      <c r="D62" s="25"/>
+      <c r="E62" s="26"/>
       <c r="F62" s="10">
         <v>1613</v>
       </c>
@@ -3344,11 +3371,11 @@
       <c r="B63" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="D63" s="24"/>
-      <c r="E63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="26"/>
       <c r="F63" s="10">
         <v>1558</v>
       </c>
@@ -3381,11 +3408,11 @@
       <c r="B64" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D64" s="24"/>
-      <c r="E64" s="25"/>
+      <c r="D64" s="25"/>
+      <c r="E64" s="26"/>
       <c r="F64" s="10">
         <v>1416</v>
       </c>
@@ -3418,11 +3445,11 @@
       <c r="B65" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C65" s="23" t="s">
+      <c r="C65" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D65" s="24"/>
-      <c r="E65" s="25"/>
+      <c r="D65" s="25"/>
+      <c r="E65" s="26"/>
       <c r="F65" s="10">
         <v>1416</v>
       </c>
@@ -3455,11 +3482,11 @@
       <c r="B66" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C66" s="23" t="s">
+      <c r="C66" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D66" s="24"/>
-      <c r="E66" s="25"/>
+      <c r="D66" s="25"/>
+      <c r="E66" s="26"/>
       <c r="F66" s="10">
         <v>1416</v>
       </c>
@@ -3492,11 +3519,11 @@
       <c r="B67" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C67" s="23" t="s">
+      <c r="C67" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D67" s="24"/>
-      <c r="E67" s="25"/>
+      <c r="D67" s="25"/>
+      <c r="E67" s="26"/>
       <c r="F67" s="10">
         <v>1635</v>
       </c>
@@ -3529,11 +3556,11 @@
       <c r="B68" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C68" s="23" t="s">
+      <c r="C68" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D68" s="24"/>
-      <c r="E68" s="25"/>
+      <c r="D68" s="25"/>
+      <c r="E68" s="26"/>
       <c r="F68" s="10">
         <v>1635</v>
       </c>
@@ -3566,11 +3593,11 @@
       <c r="B69" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C69" s="23" t="s">
+      <c r="C69" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D69" s="24"/>
-      <c r="E69" s="25"/>
+      <c r="D69" s="25"/>
+      <c r="E69" s="26"/>
       <c r="F69" s="10">
         <v>1635</v>
       </c>
@@ -3603,11 +3630,11 @@
       <c r="B70" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C70" s="23" t="s">
+      <c r="C70" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D70" s="24"/>
-      <c r="E70" s="25"/>
+      <c r="D70" s="25"/>
+      <c r="E70" s="26"/>
       <c r="F70" s="10">
         <v>1635</v>
       </c>
@@ -3640,11 +3667,11 @@
       <c r="B71" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C71" s="23" t="s">
+      <c r="C71" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D71" s="24"/>
-      <c r="E71" s="25"/>
+      <c r="D71" s="25"/>
+      <c r="E71" s="26"/>
       <c r="F71" s="10">
         <v>1635</v>
       </c>
@@ -3677,11 +3704,11 @@
       <c r="B72" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C72" s="23" t="s">
+      <c r="C72" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D72" s="24"/>
-      <c r="E72" s="25"/>
+      <c r="D72" s="25"/>
+      <c r="E72" s="26"/>
       <c r="F72" s="10">
         <v>1549</v>
       </c>
@@ -3714,11 +3741,11 @@
       <c r="B73" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C73" s="23" t="s">
+      <c r="C73" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D73" s="24"/>
-      <c r="E73" s="25"/>
+      <c r="D73" s="25"/>
+      <c r="E73" s="26"/>
       <c r="F73" s="10">
         <v>1549</v>
       </c>
@@ -3751,11 +3778,11 @@
       <c r="B74" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C74" s="23" t="s">
+      <c r="C74" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D74" s="24"/>
-      <c r="E74" s="25"/>
+      <c r="D74" s="25"/>
+      <c r="E74" s="26"/>
       <c r="F74" s="10">
         <v>1549</v>
       </c>
@@ -3788,11 +3815,11 @@
       <c r="B75" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C75" s="23" t="s">
+      <c r="C75" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D75" s="24"/>
-      <c r="E75" s="25"/>
+      <c r="D75" s="25"/>
+      <c r="E75" s="26"/>
       <c r="F75" s="10">
         <v>1549</v>
       </c>
@@ -3825,11 +3852,11 @@
       <c r="B76" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C76" s="23" t="s">
+      <c r="C76" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D76" s="24"/>
-      <c r="E76" s="25"/>
+      <c r="D76" s="25"/>
+      <c r="E76" s="26"/>
       <c r="F76" s="10">
         <v>1549</v>
       </c>
@@ -3862,11 +3889,11 @@
       <c r="B77" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C77" s="23" t="s">
+      <c r="C77" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="D77" s="24"/>
-      <c r="E77" s="25"/>
+      <c r="D77" s="25"/>
+      <c r="E77" s="26"/>
       <c r="F77" s="10">
         <v>1461</v>
       </c>
@@ -3899,11 +3926,11 @@
       <c r="B78" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C78" s="23" t="s">
+      <c r="C78" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="D78" s="24"/>
-      <c r="E78" s="25"/>
+      <c r="D78" s="25"/>
+      <c r="E78" s="26"/>
       <c r="F78" s="10">
         <v>1461</v>
       </c>
@@ -3936,11 +3963,11 @@
       <c r="B79" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="23" t="s">
+      <c r="C79" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="D79" s="24"/>
-      <c r="E79" s="25"/>
+      <c r="D79" s="25"/>
+      <c r="E79" s="26"/>
       <c r="F79" s="10">
         <v>1461</v>
       </c>
@@ -3973,11 +4000,11 @@
       <c r="B80" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C80" s="23" t="s">
+      <c r="C80" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="D80" s="24"/>
-      <c r="E80" s="25"/>
+      <c r="D80" s="25"/>
+      <c r="E80" s="26"/>
       <c r="F80" s="10">
         <v>1461</v>
       </c>
@@ -4010,11 +4037,11 @@
       <c r="B81" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C81" s="23" t="s">
+      <c r="C81" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="D81" s="24"/>
-      <c r="E81" s="25"/>
+      <c r="D81" s="25"/>
+      <c r="E81" s="26"/>
       <c r="F81" s="10">
         <v>1458</v>
       </c>
@@ -4047,11 +4074,11 @@
       <c r="B82" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C82" s="23" t="s">
+      <c r="C82" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="D82" s="24"/>
-      <c r="E82" s="25"/>
+      <c r="D82" s="25"/>
+      <c r="E82" s="26"/>
       <c r="F82" s="10">
         <v>1469</v>
       </c>
@@ -4084,11 +4111,11 @@
       <c r="B83" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C83" s="23" t="s">
+      <c r="C83" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D83" s="24"/>
-      <c r="E83" s="25"/>
+      <c r="D83" s="25"/>
+      <c r="E83" s="26"/>
       <c r="F83" s="10">
         <v>1610</v>
       </c>
@@ -4121,11 +4148,11 @@
       <c r="B84" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C84" s="23" t="s">
+      <c r="C84" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="D84" s="24"/>
-      <c r="E84" s="25"/>
+      <c r="D84" s="25"/>
+      <c r="E84" s="26"/>
       <c r="F84" s="10">
         <v>1499</v>
       </c>
@@ -4158,11 +4185,11 @@
       <c r="B85" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C85" s="23" t="s">
+      <c r="C85" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D85" s="24"/>
-      <c r="E85" s="25"/>
+      <c r="D85" s="25"/>
+      <c r="E85" s="26"/>
       <c r="F85" s="10">
         <v>1453</v>
       </c>
@@ -4195,11 +4222,11 @@
       <c r="B86" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C86" s="23" t="s">
+      <c r="C86" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D86" s="24"/>
-      <c r="E86" s="25"/>
+      <c r="D86" s="25"/>
+      <c r="E86" s="26"/>
       <c r="F86" s="10">
         <v>1453</v>
       </c>
@@ -4232,11 +4259,11 @@
       <c r="B87" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C87" s="23" t="s">
+      <c r="C87" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="D87" s="24"/>
-      <c r="E87" s="25"/>
+      <c r="D87" s="25"/>
+      <c r="E87" s="26"/>
       <c r="F87" s="10">
         <v>1433</v>
       </c>
@@ -4269,11 +4296,11 @@
       <c r="B88" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C88" s="23" t="s">
+      <c r="C88" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D88" s="24"/>
-      <c r="E88" s="25"/>
+      <c r="D88" s="25"/>
+      <c r="E88" s="26"/>
       <c r="F88" s="10">
         <v>1425</v>
       </c>
@@ -4306,11 +4333,11 @@
       <c r="B89" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C89" s="23" t="s">
+      <c r="C89" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D89" s="24"/>
-      <c r="E89" s="25"/>
+      <c r="D89" s="25"/>
+      <c r="E89" s="26"/>
       <c r="F89" s="10">
         <v>1425</v>
       </c>
@@ -4343,11 +4370,11 @@
       <c r="B90" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C90" s="23" t="s">
+      <c r="C90" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D90" s="24"/>
-      <c r="E90" s="25"/>
+      <c r="D90" s="25"/>
+      <c r="E90" s="26"/>
       <c r="F90" s="10">
         <v>1425</v>
       </c>
@@ -4380,11 +4407,11 @@
       <c r="B91" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C91" s="23" t="s">
+      <c r="C91" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D91" s="24"/>
-      <c r="E91" s="25"/>
+      <c r="D91" s="25"/>
+      <c r="E91" s="26"/>
       <c r="F91" s="10">
         <v>1425</v>
       </c>
@@ -4417,11 +4444,11 @@
       <c r="B92" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C92" s="23" t="s">
+      <c r="C92" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D92" s="24"/>
-      <c r="E92" s="25"/>
+      <c r="D92" s="25"/>
+      <c r="E92" s="26"/>
       <c r="F92" s="10">
         <v>1425</v>
       </c>
@@ -4454,11 +4481,11 @@
       <c r="B93" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C93" s="23" t="s">
+      <c r="C93" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D93" s="24"/>
-      <c r="E93" s="25"/>
+      <c r="D93" s="25"/>
+      <c r="E93" s="26"/>
       <c r="F93" s="10">
         <v>1425</v>
       </c>
@@ -4491,11 +4518,11 @@
       <c r="B94" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C94" s="23" t="s">
+      <c r="C94" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D94" s="24"/>
-      <c r="E94" s="25"/>
+      <c r="D94" s="25"/>
+      <c r="E94" s="26"/>
       <c r="F94" s="10">
         <v>1425</v>
       </c>
@@ -4528,11 +4555,11 @@
       <c r="B95" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C95" s="23" t="s">
+      <c r="C95" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D95" s="24"/>
-      <c r="E95" s="25"/>
+      <c r="D95" s="25"/>
+      <c r="E95" s="26"/>
       <c r="F95" s="10">
         <v>1425</v>
       </c>
@@ -4565,11 +4592,11 @@
       <c r="B96" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C96" s="23" t="s">
+      <c r="C96" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D96" s="24"/>
-      <c r="E96" s="25"/>
+      <c r="D96" s="25"/>
+      <c r="E96" s="26"/>
       <c r="F96" s="10">
         <v>1641</v>
       </c>
@@ -4602,11 +4629,11 @@
       <c r="B97" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C97" s="23" t="s">
+      <c r="C97" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D97" s="24"/>
-      <c r="E97" s="25"/>
+      <c r="D97" s="25"/>
+      <c r="E97" s="26"/>
       <c r="F97" s="10">
         <v>1467</v>
       </c>
@@ -4639,11 +4666,11 @@
       <c r="B98" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C98" s="23" t="s">
+      <c r="C98" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D98" s="24"/>
-      <c r="E98" s="25"/>
+      <c r="D98" s="25"/>
+      <c r="E98" s="26"/>
       <c r="F98" s="10">
         <v>1613</v>
       </c>
@@ -4676,11 +4703,11 @@
       <c r="B99" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C99" s="23" t="s">
+      <c r="C99" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D99" s="24"/>
-      <c r="E99" s="25"/>
+      <c r="D99" s="25"/>
+      <c r="E99" s="26"/>
       <c r="F99" s="10">
         <v>1613</v>
       </c>
@@ -4713,11 +4740,11 @@
       <c r="B100" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C100" s="23" t="s">
+      <c r="C100" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D100" s="24"/>
-      <c r="E100" s="25"/>
+      <c r="D100" s="25"/>
+      <c r="E100" s="26"/>
       <c r="F100" s="10">
         <v>1635</v>
       </c>
@@ -4750,11 +4777,11 @@
       <c r="B101" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C101" s="23" t="s">
+      <c r="C101" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D101" s="24"/>
-      <c r="E101" s="25"/>
+      <c r="D101" s="25"/>
+      <c r="E101" s="26"/>
       <c r="F101" s="10">
         <v>1635</v>
       </c>
@@ -4787,11 +4814,11 @@
       <c r="B102" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C102" s="23" t="s">
+      <c r="C102" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D102" s="24"/>
-      <c r="E102" s="25"/>
+      <c r="D102" s="25"/>
+      <c r="E102" s="26"/>
       <c r="F102" s="10">
         <v>1635</v>
       </c>
@@ -4824,11 +4851,11 @@
       <c r="B103" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C103" s="23" t="s">
+      <c r="C103" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D103" s="24"/>
-      <c r="E103" s="25"/>
+      <c r="D103" s="25"/>
+      <c r="E103" s="26"/>
       <c r="F103" s="10">
         <v>1549</v>
       </c>
@@ -4861,11 +4888,11 @@
       <c r="B104" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C104" s="23" t="s">
+      <c r="C104" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D104" s="24"/>
-      <c r="E104" s="25"/>
+      <c r="D104" s="25"/>
+      <c r="E104" s="26"/>
       <c r="F104" s="10">
         <v>1635</v>
       </c>
@@ -4898,11 +4925,11 @@
       <c r="B105" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C105" s="23" t="s">
+      <c r="C105" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D105" s="24"/>
-      <c r="E105" s="25"/>
+      <c r="D105" s="25"/>
+      <c r="E105" s="26"/>
       <c r="F105" s="10">
         <v>1549</v>
       </c>
@@ -4935,11 +4962,11 @@
       <c r="B106" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C106" s="23" t="s">
+      <c r="C106" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D106" s="24"/>
-      <c r="E106" s="25"/>
+      <c r="D106" s="25"/>
+      <c r="E106" s="26"/>
       <c r="F106" s="10">
         <v>1467</v>
       </c>
@@ -4972,11 +4999,11 @@
       <c r="B107" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C107" s="23" t="s">
+      <c r="C107" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="D107" s="24"/>
-      <c r="E107" s="25"/>
+      <c r="D107" s="25"/>
+      <c r="E107" s="26"/>
       <c r="F107" s="10">
         <v>1458</v>
       </c>
@@ -5009,11 +5036,11 @@
       <c r="B108" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C108" s="23" t="s">
+      <c r="C108" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D108" s="24"/>
-      <c r="E108" s="25"/>
+      <c r="D108" s="25"/>
+      <c r="E108" s="26"/>
       <c r="F108" s="10">
         <v>1610</v>
       </c>
@@ -5046,11 +5073,11 @@
       <c r="B109" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C109" s="23" t="s">
+      <c r="C109" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D109" s="24"/>
-      <c r="E109" s="25"/>
+      <c r="D109" s="25"/>
+      <c r="E109" s="26"/>
       <c r="F109" s="10">
         <v>1635</v>
       </c>
@@ -5083,11 +5110,11 @@
       <c r="B110" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C110" s="23" t="s">
+      <c r="C110" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D110" s="24"/>
-      <c r="E110" s="25"/>
+      <c r="D110" s="25"/>
+      <c r="E110" s="26"/>
       <c r="F110" s="10">
         <v>1641</v>
       </c>
@@ -5120,11 +5147,11 @@
       <c r="B111" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C111" s="23" t="s">
+      <c r="C111" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D111" s="24"/>
-      <c r="E111" s="25"/>
+      <c r="D111" s="25"/>
+      <c r="E111" s="26"/>
       <c r="F111" s="10">
         <v>1549</v>
       </c>
@@ -5157,11 +5184,11 @@
       <c r="B112" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C112" s="23" t="s">
+      <c r="C112" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D112" s="24"/>
-      <c r="E112" s="25"/>
+      <c r="D112" s="25"/>
+      <c r="E112" s="26"/>
       <c r="F112" s="10">
         <v>1467</v>
       </c>
@@ -5194,11 +5221,11 @@
       <c r="B113" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C113" s="23" t="s">
+      <c r="C113" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D113" s="24"/>
-      <c r="E113" s="25"/>
+      <c r="D113" s="25"/>
+      <c r="E113" s="26"/>
       <c r="F113" s="10">
         <v>1416</v>
       </c>
@@ -5231,11 +5258,11 @@
       <c r="B114" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C114" s="23" t="s">
+      <c r="C114" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="D114" s="24"/>
-      <c r="E114" s="25"/>
+      <c r="D114" s="25"/>
+      <c r="E114" s="26"/>
       <c r="F114" s="10">
         <v>1358</v>
       </c>
@@ -5268,11 +5295,11 @@
       <c r="B115" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C115" s="23" t="s">
+      <c r="C115" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D115" s="24"/>
-      <c r="E115" s="25"/>
+      <c r="D115" s="25"/>
+      <c r="E115" s="26"/>
       <c r="F115" s="10">
         <v>1610</v>
       </c>
@@ -5305,11 +5332,11 @@
       <c r="B116" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C116" s="23" t="s">
+      <c r="C116" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="D116" s="24"/>
-      <c r="E116" s="25"/>
+      <c r="D116" s="25"/>
+      <c r="E116" s="26"/>
       <c r="F116" s="10">
         <v>1416</v>
       </c>
@@ -5342,11 +5369,11 @@
       <c r="B117" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C117" s="23" t="s">
+      <c r="C117" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D117" s="24"/>
-      <c r="E117" s="25"/>
+      <c r="D117" s="25"/>
+      <c r="E117" s="26"/>
       <c r="F117" s="10">
         <v>1635</v>
       </c>
@@ -5379,11 +5406,11 @@
       <c r="B118" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C118" s="23" t="s">
+      <c r="C118" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="D118" s="24"/>
-      <c r="E118" s="25"/>
+      <c r="D118" s="25"/>
+      <c r="E118" s="26"/>
       <c r="F118" s="10">
         <v>1469</v>
       </c>
@@ -5416,11 +5443,11 @@
       <c r="B119" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C119" s="23" t="s">
+      <c r="C119" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D119" s="24"/>
-      <c r="E119" s="25"/>
+      <c r="D119" s="25"/>
+      <c r="E119" s="26"/>
       <c r="F119" s="10">
         <v>1453</v>
       </c>
@@ -5453,11 +5480,11 @@
       <c r="B120" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C120" s="23" t="s">
+      <c r="C120" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="D120" s="24"/>
-      <c r="E120" s="25"/>
+      <c r="D120" s="25"/>
+      <c r="E120" s="26"/>
       <c r="F120" s="10">
         <v>1457</v>
       </c>
@@ -5490,11 +5517,11 @@
       <c r="B121" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C121" s="23" t="s">
+      <c r="C121" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D121" s="24"/>
-      <c r="E121" s="25"/>
+      <c r="D121" s="25"/>
+      <c r="E121" s="26"/>
       <c r="F121" s="10">
         <v>1641</v>
       </c>
@@ -5527,11 +5554,11 @@
       <c r="B122" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C122" s="23" t="s">
+      <c r="C122" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="D122" s="24"/>
-      <c r="E122" s="25"/>
+      <c r="D122" s="25"/>
+      <c r="E122" s="26"/>
       <c r="F122" s="10">
         <v>1470</v>
       </c>
@@ -5564,11 +5591,11 @@
       <c r="B123" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C123" s="23" t="s">
+      <c r="C123" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D123" s="24"/>
-      <c r="E123" s="25"/>
+      <c r="D123" s="25"/>
+      <c r="E123" s="26"/>
       <c r="F123" s="10">
         <v>1467</v>
       </c>
@@ -5601,11 +5628,11 @@
       <c r="B124" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C124" s="23" t="s">
+      <c r="C124" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D124" s="24"/>
-      <c r="E124" s="25"/>
+      <c r="D124" s="25"/>
+      <c r="E124" s="26"/>
       <c r="F124" s="10">
         <v>1467</v>
       </c>
@@ -5638,11 +5665,11 @@
       <c r="B125" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C125" s="23" t="s">
+      <c r="C125" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D125" s="24"/>
-      <c r="E125" s="25"/>
+      <c r="D125" s="25"/>
+      <c r="E125" s="26"/>
       <c r="F125" s="10">
         <v>1467</v>
       </c>
@@ -5675,11 +5702,11 @@
       <c r="B126" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C126" s="23" t="s">
+      <c r="C126" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D126" s="24"/>
-      <c r="E126" s="25"/>
+      <c r="D126" s="25"/>
+      <c r="E126" s="26"/>
       <c r="F126" s="10">
         <v>1467</v>
       </c>
@@ -5712,11 +5739,11 @@
       <c r="B127" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C127" s="23" t="s">
+      <c r="C127" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D127" s="24"/>
-      <c r="E127" s="25"/>
+      <c r="D127" s="25"/>
+      <c r="E127" s="26"/>
       <c r="F127" s="10">
         <v>1467</v>
       </c>
@@ -5749,11 +5776,11 @@
       <c r="B128" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C128" s="23" t="s">
+      <c r="C128" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D128" s="24"/>
-      <c r="E128" s="25"/>
+      <c r="D128" s="25"/>
+      <c r="E128" s="26"/>
       <c r="F128" s="10">
         <v>1467</v>
       </c>
@@ -5786,11 +5813,11 @@
       <c r="B129" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C129" s="23" t="s">
+      <c r="C129" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D129" s="24"/>
-      <c r="E129" s="25"/>
+      <c r="D129" s="25"/>
+      <c r="E129" s="26"/>
       <c r="F129" s="10">
         <v>1613</v>
       </c>
@@ -5823,11 +5850,11 @@
       <c r="B130" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C130" s="23" t="s">
+      <c r="C130" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D130" s="24"/>
-      <c r="E130" s="25"/>
+      <c r="D130" s="25"/>
+      <c r="E130" s="26"/>
       <c r="F130" s="10">
         <v>1549</v>
       </c>
@@ -5860,11 +5887,11 @@
       <c r="B131" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C131" s="23" t="s">
+      <c r="C131" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D131" s="24"/>
-      <c r="E131" s="25"/>
+      <c r="D131" s="25"/>
+      <c r="E131" s="26"/>
       <c r="F131" s="10">
         <v>1549</v>
       </c>
@@ -5897,11 +5924,11 @@
       <c r="B132" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C132" s="23" t="s">
+      <c r="C132" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D132" s="24"/>
-      <c r="E132" s="25"/>
+      <c r="D132" s="25"/>
+      <c r="E132" s="26"/>
       <c r="F132" s="10">
         <v>1549</v>
       </c>
@@ -5934,11 +5961,11 @@
       <c r="B133" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C133" s="23" t="s">
+      <c r="C133" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D133" s="24"/>
-      <c r="E133" s="25"/>
+      <c r="D133" s="25"/>
+      <c r="E133" s="26"/>
       <c r="F133" s="10">
         <v>1549</v>
       </c>
@@ -5971,11 +5998,11 @@
       <c r="B134" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C134" s="23" t="s">
+      <c r="C134" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="D134" s="24"/>
-      <c r="E134" s="25"/>
+      <c r="D134" s="25"/>
+      <c r="E134" s="26"/>
       <c r="F134" s="10">
         <v>1469</v>
       </c>
@@ -6008,11 +6035,11 @@
       <c r="B135" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C135" s="23" t="s">
+      <c r="C135" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="D135" s="24"/>
-      <c r="E135" s="25"/>
+      <c r="D135" s="25"/>
+      <c r="E135" s="26"/>
       <c r="F135" s="10">
         <v>1469</v>
       </c>
@@ -6045,11 +6072,11 @@
       <c r="B136" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C136" s="23" t="s">
+      <c r="C136" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D136" s="24"/>
-      <c r="E136" s="25"/>
+      <c r="D136" s="25"/>
+      <c r="E136" s="26"/>
       <c r="F136" s="10">
         <v>1610</v>
       </c>
@@ -6082,11 +6109,11 @@
       <c r="B137" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C137" s="23" t="s">
+      <c r="C137" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="D137" s="24"/>
-      <c r="E137" s="25"/>
+      <c r="D137" s="25"/>
+      <c r="E137" s="26"/>
       <c r="F137" s="10">
         <v>1610</v>
       </c>
@@ -6119,11 +6146,11 @@
       <c r="B138" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C138" s="23" t="s">
+      <c r="C138" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="D138" s="24"/>
-      <c r="E138" s="25"/>
+      <c r="D138" s="25"/>
+      <c r="E138" s="26"/>
       <c r="F138" s="10">
         <v>1475</v>
       </c>
@@ -6156,11 +6183,11 @@
       <c r="B139" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C139" s="23" t="s">
+      <c r="C139" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="D139" s="24"/>
-      <c r="E139" s="25"/>
+      <c r="D139" s="25"/>
+      <c r="E139" s="26"/>
       <c r="F139" s="10">
         <v>1433</v>
       </c>
@@ -6193,11 +6220,11 @@
       <c r="B140" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C140" s="23" t="s">
+      <c r="C140" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D140" s="24"/>
-      <c r="E140" s="25"/>
+      <c r="D140" s="25"/>
+      <c r="E140" s="26"/>
       <c r="F140" s="10">
         <v>1641</v>
       </c>
@@ -6230,11 +6257,11 @@
       <c r="B141" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C141" s="23" t="s">
+      <c r="C141" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D141" s="24"/>
-      <c r="E141" s="25"/>
+      <c r="D141" s="25"/>
+      <c r="E141" s="26"/>
       <c r="F141" s="10">
         <v>1641</v>
       </c>
@@ -6267,11 +6294,11 @@
       <c r="B142" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C142" s="23" t="s">
+      <c r="C142" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="D142" s="24"/>
-      <c r="E142" s="25"/>
+      <c r="D142" s="25"/>
+      <c r="E142" s="26"/>
       <c r="F142" s="10">
         <v>1641</v>
       </c>
@@ -6304,11 +6331,11 @@
       <c r="B143" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C143" s="26" t="s">
+      <c r="C143" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D143" s="26"/>
-      <c r="E143" s="26"/>
+      <c r="D143" s="23"/>
+      <c r="E143" s="23"/>
       <c r="F143" s="15">
         <v>1477</v>
       </c>
@@ -6341,11 +6368,11 @@
       <c r="B144" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C144" s="26" t="s">
+      <c r="C144" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="D144" s="26"/>
-      <c r="E144" s="26"/>
+      <c r="D144" s="23"/>
+      <c r="E144" s="23"/>
       <c r="F144" s="15">
         <v>1358</v>
       </c>
@@ -6378,11 +6405,11 @@
       <c r="B145" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C145" s="26" t="s">
+      <c r="C145" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D145" s="26"/>
-      <c r="E145" s="26"/>
+      <c r="D145" s="23"/>
+      <c r="E145" s="23"/>
       <c r="F145" s="15">
         <v>1467</v>
       </c>
@@ -6415,11 +6442,11 @@
       <c r="B146" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C146" s="26" t="s">
+      <c r="C146" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D146" s="26"/>
-      <c r="E146" s="26"/>
+      <c r="D146" s="23"/>
+      <c r="E146" s="23"/>
       <c r="F146" s="15">
         <v>1467</v>
       </c>
@@ -6452,11 +6479,11 @@
       <c r="B147" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C147" s="26" t="s">
+      <c r="C147" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D147" s="26"/>
-      <c r="E147" s="26"/>
+      <c r="D147" s="23"/>
+      <c r="E147" s="23"/>
       <c r="F147" s="15">
         <v>1467</v>
       </c>
@@ -6489,11 +6516,11 @@
       <c r="B148" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C148" s="26" t="s">
+      <c r="C148" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D148" s="26"/>
-      <c r="E148" s="26"/>
+      <c r="D148" s="23"/>
+      <c r="E148" s="23"/>
       <c r="F148" s="15">
         <v>1467</v>
       </c>
@@ -6526,11 +6553,11 @@
       <c r="B149" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C149" s="26" t="s">
+      <c r="C149" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D149" s="26"/>
-      <c r="E149" s="26"/>
+      <c r="D149" s="23"/>
+      <c r="E149" s="23"/>
       <c r="F149" s="15">
         <v>1467</v>
       </c>
@@ -6563,11 +6590,11 @@
       <c r="B150" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C150" s="26" t="s">
+      <c r="C150" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D150" s="26"/>
-      <c r="E150" s="26"/>
+      <c r="D150" s="23"/>
+      <c r="E150" s="23"/>
       <c r="F150" s="15">
         <v>1467</v>
       </c>
@@ -6600,11 +6627,11 @@
       <c r="B151" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C151" s="26" t="s">
+      <c r="C151" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D151" s="26"/>
-      <c r="E151" s="26"/>
+      <c r="D151" s="23"/>
+      <c r="E151" s="23"/>
       <c r="F151" s="15">
         <v>1549</v>
       </c>
@@ -6637,11 +6664,11 @@
       <c r="B152" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C152" s="26" t="s">
+      <c r="C152" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D152" s="26"/>
-      <c r="E152" s="26"/>
+      <c r="D152" s="23"/>
+      <c r="E152" s="23"/>
       <c r="F152" s="15">
         <v>1549</v>
       </c>
@@ -6674,11 +6701,11 @@
       <c r="B153" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C153" s="26" t="s">
+      <c r="C153" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D153" s="26"/>
-      <c r="E153" s="26"/>
+      <c r="D153" s="23"/>
+      <c r="E153" s="23"/>
       <c r="F153" s="15">
         <v>1549</v>
       </c>
@@ -6711,11 +6738,11 @@
       <c r="B154" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="C154" s="26" t="s">
+      <c r="C154" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D154" s="26"/>
-      <c r="E154" s="26"/>
+      <c r="D154" s="23"/>
+      <c r="E154" s="23"/>
       <c r="F154" s="15">
         <v>1549</v>
       </c>
@@ -6748,11 +6775,11 @@
       <c r="B155" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C155" s="26" t="s">
+      <c r="C155" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D155" s="26"/>
-      <c r="E155" s="26"/>
+      <c r="D155" s="23"/>
+      <c r="E155" s="23"/>
       <c r="F155" s="15">
         <v>1549</v>
       </c>
@@ -6785,11 +6812,11 @@
       <c r="B156" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C156" s="26" t="s">
+      <c r="C156" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="D156" s="26"/>
-      <c r="E156" s="26"/>
+      <c r="D156" s="23"/>
+      <c r="E156" s="23"/>
       <c r="F156" s="15">
         <v>1549</v>
       </c>
@@ -6822,11 +6849,11 @@
       <c r="B157" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C157" s="26" t="s">
+      <c r="C157" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="D157" s="26"/>
-      <c r="E157" s="26"/>
+      <c r="D157" s="23"/>
+      <c r="E157" s="23"/>
       <c r="F157" s="15">
         <v>1417</v>
       </c>
@@ -6859,11 +6886,11 @@
       <c r="B158" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C158" s="26" t="s">
+      <c r="C158" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D158" s="26"/>
-      <c r="E158" s="26"/>
+      <c r="D158" s="23"/>
+      <c r="E158" s="23"/>
       <c r="F158" s="15">
         <v>1470</v>
       </c>
@@ -6896,11 +6923,11 @@
       <c r="B159" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C159" s="26" t="s">
+      <c r="C159" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D159" s="26"/>
-      <c r="E159" s="26"/>
+      <c r="D159" s="23"/>
+      <c r="E159" s="23"/>
       <c r="F159" s="15">
         <v>1469</v>
       </c>
@@ -6933,11 +6960,11 @@
       <c r="B160" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C160" s="26" t="s">
+      <c r="C160" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D160" s="26"/>
-      <c r="E160" s="26"/>
+      <c r="D160" s="23"/>
+      <c r="E160" s="23"/>
       <c r="F160" s="15">
         <v>1469</v>
       </c>
@@ -6970,11 +6997,11 @@
       <c r="B161" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C161" s="26" t="s">
+      <c r="C161" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D161" s="26"/>
-      <c r="E161" s="26"/>
+      <c r="D161" s="23"/>
+      <c r="E161" s="23"/>
       <c r="F161" s="15">
         <v>1469</v>
       </c>
@@ -7007,11 +7034,11 @@
       <c r="B162" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C162" s="26" t="s">
+      <c r="C162" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="D162" s="26"/>
-      <c r="E162" s="26"/>
+      <c r="D162" s="23"/>
+      <c r="E162" s="23"/>
       <c r="F162" s="15">
         <v>1472</v>
       </c>
@@ -7044,11 +7071,11 @@
       <c r="B163" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="C163" s="26" t="s">
+      <c r="C163" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D163" s="26"/>
-      <c r="E163" s="26"/>
+      <c r="D163" s="23"/>
+      <c r="E163" s="23"/>
       <c r="F163" s="15">
         <v>1610</v>
       </c>
@@ -7081,11 +7108,11 @@
       <c r="B164" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C164" s="26" t="s">
+      <c r="C164" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="D164" s="26"/>
-      <c r="E164" s="26"/>
+      <c r="D164" s="23"/>
+      <c r="E164" s="23"/>
       <c r="F164" s="15">
         <v>1453</v>
       </c>
@@ -7118,11 +7145,11 @@
       <c r="B165" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C165" s="26" t="s">
+      <c r="C165" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="D165" s="26"/>
-      <c r="E165" s="26"/>
+      <c r="D165" s="23"/>
+      <c r="E165" s="23"/>
       <c r="F165" s="15">
         <v>1433</v>
       </c>
@@ -7155,11 +7182,11 @@
       <c r="B166" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C166" s="26" t="s">
+      <c r="C166" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="D166" s="26"/>
-      <c r="E166" s="26"/>
+      <c r="D166" s="23"/>
+      <c r="E166" s="23"/>
       <c r="F166" s="15">
         <v>1457</v>
       </c>
@@ -7192,11 +7219,11 @@
       <c r="B167" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C167" s="26" t="s">
+      <c r="C167" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D167" s="26"/>
-      <c r="E167" s="26"/>
+      <c r="D167" s="23"/>
+      <c r="E167" s="23"/>
       <c r="F167" s="15">
         <v>1466</v>
       </c>
@@ -7229,11 +7256,11 @@
       <c r="B168" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C168" s="26" t="s">
+      <c r="C168" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D168" s="26"/>
-      <c r="E168" s="26"/>
+      <c r="D168" s="23"/>
+      <c r="E168" s="23"/>
       <c r="F168" s="15">
         <v>1641</v>
       </c>
@@ -7266,11 +7293,11 @@
       <c r="B169" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C169" s="26" t="s">
+      <c r="C169" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D169" s="26"/>
-      <c r="E169" s="26"/>
+      <c r="D169" s="23"/>
+      <c r="E169" s="23"/>
       <c r="F169" s="15">
         <v>1641</v>
       </c>
@@ -7303,11 +7330,11 @@
       <c r="B170" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C170" s="26" t="s">
+      <c r="C170" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D170" s="26"/>
-      <c r="E170" s="26"/>
+      <c r="D170" s="23"/>
+      <c r="E170" s="23"/>
       <c r="F170" s="15">
         <v>1414</v>
       </c>
@@ -7341,11 +7368,11 @@
       <c r="B171" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C171" s="26" t="s">
+      <c r="C171" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="D171" s="26"/>
-      <c r="E171" s="26"/>
+      <c r="D171" s="23"/>
+      <c r="E171" s="23"/>
       <c r="F171" s="15">
         <v>1477</v>
       </c>
@@ -7379,11 +7406,11 @@
       <c r="B172" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C172" s="26" t="s">
+      <c r="C172" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="D172" s="26"/>
-      <c r="E172" s="26"/>
+      <c r="D172" s="23"/>
+      <c r="E172" s="23"/>
       <c r="F172" s="15">
         <v>1358</v>
       </c>
@@ -7417,11 +7444,11 @@
       <c r="B173" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C173" s="26" t="s">
+      <c r="C173" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="D173" s="26"/>
-      <c r="E173" s="26"/>
+      <c r="D173" s="23"/>
+      <c r="E173" s="23"/>
       <c r="F173" s="15">
         <v>1358</v>
       </c>
@@ -7455,11 +7482,11 @@
       <c r="B174" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C174" s="26" t="s">
+      <c r="C174" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D174" s="26"/>
-      <c r="E174" s="26"/>
+      <c r="D174" s="23"/>
+      <c r="E174" s="23"/>
       <c r="F174" s="15">
         <v>1467</v>
       </c>
@@ -7493,11 +7520,11 @@
       <c r="B175" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C175" s="26" t="s">
+      <c r="C175" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D175" s="26"/>
-      <c r="E175" s="26"/>
+      <c r="D175" s="23"/>
+      <c r="E175" s="23"/>
       <c r="F175" s="15">
         <v>1467</v>
       </c>
@@ -7531,11 +7558,11 @@
       <c r="B176" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C176" s="26" t="s">
+      <c r="C176" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D176" s="26"/>
-      <c r="E176" s="26"/>
+      <c r="D176" s="23"/>
+      <c r="E176" s="23"/>
       <c r="F176" s="15">
         <v>1467</v>
       </c>
@@ -7569,11 +7596,11 @@
       <c r="B177" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C177" s="26" t="s">
+      <c r="C177" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D177" s="26"/>
-      <c r="E177" s="26"/>
+      <c r="D177" s="23"/>
+      <c r="E177" s="23"/>
       <c r="F177" s="15">
         <v>1467</v>
       </c>
@@ -7607,11 +7634,11 @@
       <c r="B178" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C178" s="26" t="s">
+      <c r="C178" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D178" s="26"/>
-      <c r="E178" s="26"/>
+      <c r="D178" s="23"/>
+      <c r="E178" s="23"/>
       <c r="F178" s="15">
         <v>1467</v>
       </c>
@@ -7645,11 +7672,11 @@
       <c r="B179" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C179" s="26" t="s">
+      <c r="C179" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D179" s="26"/>
-      <c r="E179" s="26"/>
+      <c r="D179" s="23"/>
+      <c r="E179" s="23"/>
       <c r="F179" s="15">
         <v>1467</v>
       </c>
@@ -7683,11 +7710,11 @@
       <c r="B180" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C180" s="26" t="s">
+      <c r="C180" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D180" s="26"/>
-      <c r="E180" s="26"/>
+      <c r="D180" s="23"/>
+      <c r="E180" s="23"/>
       <c r="F180" s="15">
         <v>1467</v>
       </c>
@@ -7721,11 +7748,11 @@
       <c r="B181" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C181" s="26" t="s">
+      <c r="C181" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D181" s="26"/>
-      <c r="E181" s="26"/>
+      <c r="D181" s="23"/>
+      <c r="E181" s="23"/>
       <c r="F181" s="15">
         <v>1416</v>
       </c>
@@ -7759,11 +7786,11 @@
       <c r="B182" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C182" s="26" t="s">
+      <c r="C182" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D182" s="26"/>
-      <c r="E182" s="26"/>
+      <c r="D182" s="23"/>
+      <c r="E182" s="23"/>
       <c r="F182" s="15">
         <v>1635</v>
       </c>
@@ -7797,11 +7824,11 @@
       <c r="B183" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C183" s="26" t="s">
+      <c r="C183" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D183" s="26"/>
-      <c r="E183" s="26"/>
+      <c r="D183" s="23"/>
+      <c r="E183" s="23"/>
       <c r="F183" s="15">
         <v>1635</v>
       </c>
@@ -7835,11 +7862,11 @@
       <c r="B184" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C184" s="26" t="s">
+      <c r="C184" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="D184" s="26"/>
-      <c r="E184" s="26"/>
+      <c r="D184" s="23"/>
+      <c r="E184" s="23"/>
       <c r="F184" s="15">
         <v>1417</v>
       </c>
@@ -7873,11 +7900,11 @@
       <c r="B185" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C185" s="26" t="s">
+      <c r="C185" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D185" s="26"/>
-      <c r="E185" s="26"/>
+      <c r="D185" s="23"/>
+      <c r="E185" s="23"/>
       <c r="F185" s="15">
         <v>1470</v>
       </c>
@@ -7911,11 +7938,11 @@
       <c r="B186" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C186" s="26" t="s">
+      <c r="C186" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D186" s="26"/>
-      <c r="E186" s="26"/>
+      <c r="D186" s="23"/>
+      <c r="E186" s="23"/>
       <c r="F186" s="15">
         <v>1469</v>
       </c>
@@ -7949,11 +7976,11 @@
       <c r="B187" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C187" s="26" t="s">
+      <c r="C187" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D187" s="26"/>
-      <c r="E187" s="26"/>
+      <c r="D187" s="23"/>
+      <c r="E187" s="23"/>
       <c r="F187" s="15">
         <v>1469</v>
       </c>
@@ -7987,11 +8014,11 @@
       <c r="B188" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C188" s="26" t="s">
+      <c r="C188" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D188" s="26"/>
-      <c r="E188" s="26"/>
+      <c r="D188" s="23"/>
+      <c r="E188" s="23"/>
       <c r="F188" s="15">
         <v>1469</v>
       </c>
@@ -8025,11 +8052,11 @@
       <c r="B189" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C189" s="26" t="s">
+      <c r="C189" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D189" s="26"/>
-      <c r="E189" s="26"/>
+      <c r="D189" s="23"/>
+      <c r="E189" s="23"/>
       <c r="F189" s="15">
         <v>1469</v>
       </c>
@@ -8063,11 +8090,11 @@
       <c r="B190" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C190" s="26" t="s">
+      <c r="C190" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D190" s="26"/>
-      <c r="E190" s="26"/>
+      <c r="D190" s="23"/>
+      <c r="E190" s="23"/>
       <c r="F190" s="15">
         <v>1610</v>
       </c>
@@ -8101,11 +8128,11 @@
       <c r="B191" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C191" s="26" t="s">
+      <c r="C191" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="D191" s="26"/>
-      <c r="E191" s="26"/>
+      <c r="D191" s="23"/>
+      <c r="E191" s="23"/>
       <c r="F191" s="15">
         <v>1433</v>
       </c>
@@ -8139,11 +8166,11 @@
       <c r="B192" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C192" s="26" t="s">
+      <c r="C192" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="D192" s="26"/>
-      <c r="E192" s="26"/>
+      <c r="D192" s="23"/>
+      <c r="E192" s="23"/>
       <c r="F192" s="15">
         <v>1433</v>
       </c>
@@ -8177,11 +8204,11 @@
       <c r="B193" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C193" s="26" t="s">
+      <c r="C193" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D193" s="26"/>
-      <c r="E193" s="26"/>
+      <c r="D193" s="23"/>
+      <c r="E193" s="23"/>
       <c r="F193" s="15">
         <v>1466</v>
       </c>
@@ -8215,11 +8242,11 @@
       <c r="B194" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C194" s="26" t="s">
+      <c r="C194" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D194" s="26"/>
-      <c r="E194" s="26"/>
+      <c r="D194" s="23"/>
+      <c r="E194" s="23"/>
       <c r="F194" s="15">
         <v>1641</v>
       </c>
@@ -8253,11 +8280,11 @@
       <c r="B195" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C195" s="26" t="s">
+      <c r="C195" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D195" s="26"/>
-      <c r="E195" s="26"/>
+      <c r="D195" s="23"/>
+      <c r="E195" s="23"/>
       <c r="F195" s="15">
         <v>1641</v>
       </c>
@@ -8291,11 +8318,11 @@
       <c r="B196" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C196" s="26" t="s">
+      <c r="C196" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D196" s="26"/>
-      <c r="E196" s="26"/>
+      <c r="D196" s="23"/>
+      <c r="E196" s="23"/>
       <c r="F196" s="15">
         <v>1641</v>
       </c>
@@ -8329,11 +8356,11 @@
       <c r="B197" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C197" s="26" t="s">
+      <c r="C197" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D197" s="26"/>
-      <c r="E197" s="26"/>
+      <c r="D197" s="23"/>
+      <c r="E197" s="23"/>
       <c r="F197" s="15">
         <v>1641</v>
       </c>
@@ -8367,11 +8394,11 @@
       <c r="B198" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C198" s="26" t="s">
+      <c r="C198" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="D198" s="26"/>
-      <c r="E198" s="26"/>
+      <c r="D198" s="23"/>
+      <c r="E198" s="23"/>
       <c r="F198" s="15">
         <v>1450</v>
       </c>
@@ -8405,11 +8432,11 @@
       <c r="B199" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C199" s="26" t="s">
+      <c r="C199" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D199" s="26"/>
-      <c r="E199" s="26"/>
+      <c r="D199" s="23"/>
+      <c r="E199" s="23"/>
       <c r="F199" s="15">
         <v>1414</v>
       </c>
@@ -8443,11 +8470,11 @@
       <c r="B200" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C200" s="26" t="s">
+      <c r="C200" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D200" s="26"/>
-      <c r="E200" s="26"/>
+      <c r="D200" s="23"/>
+      <c r="E200" s="23"/>
       <c r="F200" s="15">
         <v>1414</v>
       </c>
@@ -8481,11 +8508,11 @@
       <c r="B201" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C201" s="26" t="s">
+      <c r="C201" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D201" s="26"/>
-      <c r="E201" s="26"/>
+      <c r="D201" s="23"/>
+      <c r="E201" s="23"/>
       <c r="F201" s="15">
         <v>1414</v>
       </c>
@@ -8519,11 +8546,11 @@
       <c r="B202" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C202" s="26" t="s">
+      <c r="C202" s="23" t="s">
         <v>110</v>
       </c>
-      <c r="D202" s="26"/>
-      <c r="E202" s="26"/>
+      <c r="D202" s="23"/>
+      <c r="E202" s="23"/>
       <c r="F202" s="15">
         <v>1750</v>
       </c>
@@ -8557,11 +8584,11 @@
       <c r="B203" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C203" s="26" t="s">
+      <c r="C203" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D203" s="26"/>
-      <c r="E203" s="26"/>
+      <c r="D203" s="23"/>
+      <c r="E203" s="23"/>
       <c r="F203" s="15">
         <v>1613</v>
       </c>
@@ -8595,11 +8622,11 @@
       <c r="B204" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C204" s="26" t="s">
+      <c r="C204" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D204" s="26"/>
-      <c r="E204" s="26"/>
+      <c r="D204" s="23"/>
+      <c r="E204" s="23"/>
       <c r="F204" s="15">
         <v>1416</v>
       </c>
@@ -8633,11 +8660,11 @@
       <c r="B205" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C205" s="26" t="s">
+      <c r="C205" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D205" s="26"/>
-      <c r="E205" s="26"/>
+      <c r="D205" s="23"/>
+      <c r="E205" s="23"/>
       <c r="F205" s="15">
         <v>1416</v>
       </c>
@@ -8671,11 +8698,11 @@
       <c r="B206" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C206" s="26" t="s">
+      <c r="C206" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="D206" s="26"/>
-      <c r="E206" s="26"/>
+      <c r="D206" s="23"/>
+      <c r="E206" s="23"/>
       <c r="F206" s="15">
         <v>1572</v>
       </c>
@@ -8709,11 +8736,11 @@
       <c r="B207" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C207" s="26" t="s">
+      <c r="C207" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D207" s="26"/>
-      <c r="E207" s="26"/>
+      <c r="D207" s="23"/>
+      <c r="E207" s="23"/>
       <c r="F207" s="15">
         <v>1470</v>
       </c>
@@ -8747,11 +8774,11 @@
       <c r="B208" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C208" s="26" t="s">
+      <c r="C208" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D208" s="26"/>
-      <c r="E208" s="26"/>
+      <c r="D208" s="23"/>
+      <c r="E208" s="23"/>
       <c r="F208" s="15">
         <v>1470</v>
       </c>
@@ -8785,11 +8812,11 @@
       <c r="B209" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C209" s="26" t="s">
+      <c r="C209" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D209" s="26"/>
-      <c r="E209" s="26"/>
+      <c r="D209" s="23"/>
+      <c r="E209" s="23"/>
       <c r="F209" s="15">
         <v>1469</v>
       </c>
@@ -8823,11 +8850,11 @@
       <c r="B210" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C210" s="26" t="s">
+      <c r="C210" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="D210" s="26"/>
-      <c r="E210" s="26"/>
+      <c r="D210" s="23"/>
+      <c r="E210" s="23"/>
       <c r="F210" s="15">
         <v>1472</v>
       </c>
@@ -8861,11 +8888,11 @@
       <c r="B211" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C211" s="26" t="s">
+      <c r="C211" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="D211" s="26"/>
-      <c r="E211" s="26"/>
+      <c r="D211" s="23"/>
+      <c r="E211" s="23"/>
       <c r="F211" s="15">
         <v>1472</v>
       </c>
@@ -8899,11 +8926,11 @@
       <c r="B212" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C212" s="26" t="s">
+      <c r="C212" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D212" s="26"/>
-      <c r="E212" s="26"/>
+      <c r="D212" s="23"/>
+      <c r="E212" s="23"/>
       <c r="F212" s="15">
         <v>1610</v>
       </c>
@@ -8937,11 +8964,11 @@
       <c r="B213" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C213" s="26" t="s">
+      <c r="C213" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D213" s="26"/>
-      <c r="E213" s="26"/>
+      <c r="D213" s="23"/>
+      <c r="E213" s="23"/>
       <c r="F213" s="15">
         <v>1610</v>
       </c>
@@ -8975,11 +9002,11 @@
       <c r="B214" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C214" s="26" t="s">
+      <c r="C214" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="D214" s="26"/>
-      <c r="E214" s="26"/>
+      <c r="D214" s="23"/>
+      <c r="E214" s="23"/>
       <c r="F214" s="15">
         <v>1433</v>
       </c>
@@ -9013,11 +9040,11 @@
       <c r="B215" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C215" s="26" t="s">
+      <c r="C215" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="D215" s="26"/>
-      <c r="E215" s="26"/>
+      <c r="D215" s="23"/>
+      <c r="E215" s="23"/>
       <c r="F215" s="15">
         <v>1457</v>
       </c>
@@ -9051,11 +9078,11 @@
       <c r="B216" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C216" s="26" t="s">
+      <c r="C216" s="23" t="s">
         <v>72</v>
       </c>
-      <c r="D216" s="26"/>
-      <c r="E216" s="26"/>
+      <c r="D216" s="23"/>
+      <c r="E216" s="23"/>
       <c r="F216" s="15">
         <v>1457</v>
       </c>
@@ -9089,11 +9116,11 @@
       <c r="B217" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C217" s="26" t="s">
+      <c r="C217" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D217" s="26"/>
-      <c r="E217" s="26"/>
+      <c r="D217" s="23"/>
+      <c r="E217" s="23"/>
       <c r="F217" s="15">
         <v>1533</v>
       </c>
@@ -9127,11 +9154,11 @@
       <c r="B218" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C218" s="26" t="s">
+      <c r="C218" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D218" s="26"/>
-      <c r="E218" s="26"/>
+      <c r="D218" s="23"/>
+      <c r="E218" s="23"/>
       <c r="F218" s="15">
         <v>1533</v>
       </c>
@@ -9165,11 +9192,11 @@
       <c r="B219" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C219" s="26" t="s">
+      <c r="C219" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D219" s="26"/>
-      <c r="E219" s="26"/>
+      <c r="D219" s="23"/>
+      <c r="E219" s="23"/>
       <c r="F219" s="15">
         <v>1641</v>
       </c>
@@ -9203,11 +9230,11 @@
       <c r="B220" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C220" s="26" t="s">
+      <c r="C220" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D220" s="26"/>
-      <c r="E220" s="26"/>
+      <c r="D220" s="23"/>
+      <c r="E220" s="23"/>
       <c r="F220" s="15">
         <v>1641</v>
       </c>
@@ -9241,11 +9268,11 @@
       <c r="B221" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C221" s="26" t="s">
+      <c r="C221" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D221" s="26"/>
-      <c r="E221" s="26"/>
+      <c r="D221" s="23"/>
+      <c r="E221" s="23"/>
       <c r="F221" s="15">
         <v>1641</v>
       </c>
@@ -9279,11 +9306,11 @@
       <c r="B222" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C222" s="26" t="s">
+      <c r="C222" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="D222" s="26"/>
-      <c r="E222" s="26"/>
+      <c r="D222" s="23"/>
+      <c r="E222" s="23"/>
       <c r="F222" s="15">
         <v>1450</v>
       </c>
@@ -9317,11 +9344,11 @@
       <c r="B223" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C223" s="26" t="s">
+      <c r="C223" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D223" s="26"/>
-      <c r="E223" s="26"/>
+      <c r="D223" s="23"/>
+      <c r="E223" s="23"/>
       <c r="F223" s="15">
         <v>1414</v>
       </c>
@@ -9355,11 +9382,11 @@
       <c r="B224" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C224" s="26" t="s">
+      <c r="C224" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D224" s="26"/>
-      <c r="E224" s="26"/>
+      <c r="D224" s="23"/>
+      <c r="E224" s="23"/>
       <c r="F224" s="15">
         <v>1414</v>
       </c>
@@ -9393,11 +9420,11 @@
       <c r="B225" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C225" s="26" t="s">
+      <c r="C225" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D225" s="26"/>
-      <c r="E225" s="26"/>
+      <c r="D225" s="23"/>
+      <c r="E225" s="23"/>
       <c r="F225" s="15">
         <v>1414</v>
       </c>
@@ -9431,11 +9458,11 @@
       <c r="B226" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C226" s="26" t="s">
+      <c r="C226" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D226" s="26"/>
-      <c r="E226" s="26"/>
+      <c r="D226" s="23"/>
+      <c r="E226" s="23"/>
       <c r="F226" s="15">
         <v>1414</v>
       </c>
@@ -9469,11 +9496,11 @@
       <c r="B227" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C227" s="26" t="s">
+      <c r="C227" s="23" t="s">
         <v>118</v>
       </c>
-      <c r="D227" s="26"/>
-      <c r="E227" s="26"/>
+      <c r="D227" s="23"/>
+      <c r="E227" s="23"/>
       <c r="F227" s="15">
         <v>1782</v>
       </c>
@@ -9507,11 +9534,11 @@
       <c r="B228" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C228" s="26" t="s">
+      <c r="C228" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="D228" s="26"/>
-      <c r="E228" s="26"/>
+      <c r="D228" s="23"/>
+      <c r="E228" s="23"/>
       <c r="F228" s="15">
         <v>1542</v>
       </c>
@@ -9545,11 +9572,11 @@
       <c r="B229" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C229" s="26" t="s">
+      <c r="C229" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D229" s="26"/>
-      <c r="E229" s="26"/>
+      <c r="D229" s="23"/>
+      <c r="E229" s="23"/>
       <c r="F229" s="15">
         <v>1470</v>
       </c>
@@ -9583,11 +9610,11 @@
       <c r="B230" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C230" s="26" t="s">
+      <c r="C230" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D230" s="26"/>
-      <c r="E230" s="26"/>
+      <c r="D230" s="23"/>
+      <c r="E230" s="23"/>
       <c r="F230" s="15">
         <v>1470</v>
       </c>
@@ -9621,11 +9648,11 @@
       <c r="B231" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C231" s="26" t="s">
+      <c r="C231" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D231" s="26"/>
-      <c r="E231" s="26"/>
+      <c r="D231" s="23"/>
+      <c r="E231" s="23"/>
       <c r="F231" s="15">
         <v>1470</v>
       </c>
@@ -9659,11 +9686,11 @@
       <c r="B232" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C232" s="26" t="s">
+      <c r="C232" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D232" s="26"/>
-      <c r="E232" s="26"/>
+      <c r="D232" s="23"/>
+      <c r="E232" s="23"/>
       <c r="F232" s="15">
         <v>1469</v>
       </c>
@@ -9697,11 +9724,11 @@
       <c r="B233" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C233" s="26" t="s">
+      <c r="C233" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D233" s="26"/>
-      <c r="E233" s="26"/>
+      <c r="D233" s="23"/>
+      <c r="E233" s="23"/>
       <c r="F233" s="15">
         <v>1469</v>
       </c>
@@ -9735,11 +9762,11 @@
       <c r="B234" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C234" s="26" t="s">
+      <c r="C234" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="D234" s="26"/>
-      <c r="E234" s="26"/>
+      <c r="D234" s="23"/>
+      <c r="E234" s="23"/>
       <c r="F234" s="15">
         <v>1472</v>
       </c>
@@ -9773,11 +9800,11 @@
       <c r="B235" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C235" s="26" t="s">
+      <c r="C235" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D235" s="26"/>
-      <c r="E235" s="26"/>
+      <c r="D235" s="23"/>
+      <c r="E235" s="23"/>
       <c r="F235" s="15">
         <v>1610</v>
       </c>
@@ -9811,11 +9838,11 @@
       <c r="B236" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C236" s="26" t="s">
+      <c r="C236" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D236" s="26"/>
-      <c r="E236" s="26"/>
+      <c r="D236" s="23"/>
+      <c r="E236" s="23"/>
       <c r="F236" s="15">
         <v>1610</v>
       </c>
@@ -9849,11 +9876,11 @@
       <c r="B237" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C237" s="26" t="s">
+      <c r="C237" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D237" s="26"/>
-      <c r="E237" s="26"/>
+      <c r="D237" s="23"/>
+      <c r="E237" s="23"/>
       <c r="F237" s="15">
         <v>1610</v>
       </c>
@@ -9887,11 +9914,11 @@
       <c r="B238" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C238" s="26" t="s">
+      <c r="C238" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="D238" s="26"/>
-      <c r="E238" s="26"/>
+      <c r="D238" s="23"/>
+      <c r="E238" s="23"/>
       <c r="F238" s="15">
         <v>1433</v>
       </c>
@@ -9925,11 +9952,11 @@
       <c r="B239" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C239" s="26" t="s">
+      <c r="C239" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D239" s="26"/>
-      <c r="E239" s="26"/>
+      <c r="D239" s="23"/>
+      <c r="E239" s="23"/>
       <c r="F239" s="15">
         <v>1533</v>
       </c>
@@ -9963,11 +9990,11 @@
       <c r="B240" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C240" s="26" t="s">
+      <c r="C240" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D240" s="26"/>
-      <c r="E240" s="26"/>
+      <c r="D240" s="23"/>
+      <c r="E240" s="23"/>
       <c r="F240" s="15">
         <v>1533</v>
       </c>
@@ -10001,11 +10028,11 @@
       <c r="B241" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C241" s="26" t="s">
+      <c r="C241" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D241" s="26"/>
-      <c r="E241" s="26"/>
+      <c r="D241" s="23"/>
+      <c r="E241" s="23"/>
       <c r="F241" s="15">
         <v>1533</v>
       </c>
@@ -10039,11 +10066,11 @@
       <c r="B242" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C242" s="26" t="s">
+      <c r="C242" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D242" s="26"/>
-      <c r="E242" s="26"/>
+      <c r="D242" s="23"/>
+      <c r="E242" s="23"/>
       <c r="F242" s="15">
         <v>1641</v>
       </c>
@@ -10077,11 +10104,11 @@
       <c r="B243" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C243" s="26" t="s">
+      <c r="C243" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="D243" s="26"/>
-      <c r="E243" s="26"/>
+      <c r="D243" s="23"/>
+      <c r="E243" s="23"/>
       <c r="F243" s="15">
         <v>1450</v>
       </c>
@@ -10114,11 +10141,11 @@
       <c r="B244" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C244" s="26" t="s">
+      <c r="C244" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D244" s="26"/>
-      <c r="E244" s="26"/>
+      <c r="D244" s="23"/>
+      <c r="E244" s="23"/>
       <c r="F244" s="15">
         <v>1414</v>
       </c>
@@ -10151,11 +10178,11 @@
       <c r="B245" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C245" s="26" t="s">
+      <c r="C245" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D245" s="26"/>
-      <c r="E245" s="26"/>
+      <c r="D245" s="23"/>
+      <c r="E245" s="23"/>
       <c r="F245" s="15">
         <v>1414</v>
       </c>
@@ -10188,11 +10215,11 @@
       <c r="B246" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C246" s="26" t="s">
+      <c r="C246" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D246" s="26"/>
-      <c r="E246" s="26"/>
+      <c r="D246" s="23"/>
+      <c r="E246" s="23"/>
       <c r="F246" s="15">
         <v>1414</v>
       </c>
@@ -10225,11 +10252,11 @@
       <c r="B247" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C247" s="26" t="s">
+      <c r="C247" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D247" s="26"/>
-      <c r="E247" s="26"/>
+      <c r="D247" s="23"/>
+      <c r="E247" s="23"/>
       <c r="F247" s="15">
         <v>1414</v>
       </c>
@@ -10262,11 +10289,11 @@
       <c r="B248" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C248" s="26" t="s">
+      <c r="C248" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D248" s="26"/>
-      <c r="E248" s="26"/>
+      <c r="D248" s="23"/>
+      <c r="E248" s="23"/>
       <c r="F248" s="15">
         <v>1414</v>
       </c>
@@ -10299,11 +10326,11 @@
       <c r="B249" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C249" s="26" t="s">
+      <c r="C249" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D249" s="26"/>
-      <c r="E249" s="26"/>
+      <c r="D249" s="23"/>
+      <c r="E249" s="23"/>
       <c r="F249" s="15">
         <v>1508</v>
       </c>
@@ -10336,11 +10363,11 @@
       <c r="B250" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C250" s="26" t="s">
+      <c r="C250" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D250" s="26"/>
-      <c r="E250" s="26"/>
+      <c r="D250" s="23"/>
+      <c r="E250" s="23"/>
       <c r="F250" s="15">
         <v>1467</v>
       </c>
@@ -10373,11 +10400,11 @@
       <c r="B251" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C251" s="26" t="s">
+      <c r="C251" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="D251" s="26"/>
-      <c r="E251" s="26"/>
+      <c r="D251" s="23"/>
+      <c r="E251" s="23"/>
       <c r="F251" s="15">
         <v>1571</v>
       </c>
@@ -10410,11 +10437,11 @@
       <c r="B252" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C252" s="26" t="s">
+      <c r="C252" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="D252" s="26"/>
-      <c r="E252" s="26"/>
+      <c r="D252" s="23"/>
+      <c r="E252" s="23"/>
       <c r="F252" s="15">
         <v>1418</v>
       </c>
@@ -10447,11 +10474,11 @@
       <c r="B253" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C253" s="26" t="s">
+      <c r="C253" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="D253" s="26"/>
-      <c r="E253" s="26"/>
+      <c r="D253" s="23"/>
+      <c r="E253" s="23"/>
       <c r="F253" s="15">
         <v>1417</v>
       </c>
@@ -10484,11 +10511,11 @@
       <c r="B254" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C254" s="26" t="s">
+      <c r="C254" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="D254" s="26"/>
-      <c r="E254" s="26"/>
+      <c r="D254" s="23"/>
+      <c r="E254" s="23"/>
       <c r="F254" s="15">
         <v>1572</v>
       </c>
@@ -10521,11 +10548,11 @@
       <c r="B255" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C255" s="26" t="s">
+      <c r="C255" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D255" s="26"/>
-      <c r="E255" s="26"/>
+      <c r="D255" s="23"/>
+      <c r="E255" s="23"/>
       <c r="F255" s="15">
         <v>1470</v>
       </c>
@@ -10558,11 +10585,11 @@
       <c r="B256" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C256" s="26" t="s">
+      <c r="C256" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D256" s="26"/>
-      <c r="E256" s="26"/>
+      <c r="D256" s="23"/>
+      <c r="E256" s="23"/>
       <c r="F256" s="15">
         <v>1470</v>
       </c>
@@ -10595,11 +10622,11 @@
       <c r="B257" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C257" s="26" t="s">
+      <c r="C257" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="D257" s="26"/>
-      <c r="E257" s="26"/>
+      <c r="D257" s="23"/>
+      <c r="E257" s="23"/>
       <c r="F257" s="15">
         <v>1458</v>
       </c>
@@ -10632,11 +10659,11 @@
       <c r="B258" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C258" s="26" t="s">
+      <c r="C258" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="D258" s="26"/>
-      <c r="E258" s="26"/>
+      <c r="D258" s="23"/>
+      <c r="E258" s="23"/>
       <c r="F258" s="15">
         <v>1472</v>
       </c>
@@ -10669,11 +10696,11 @@
       <c r="B259" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C259" s="26" t="s">
+      <c r="C259" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="D259" s="26"/>
-      <c r="E259" s="26"/>
+      <c r="D259" s="23"/>
+      <c r="E259" s="23"/>
       <c r="F259" s="15">
         <v>1472</v>
       </c>
@@ -10706,11 +10733,11 @@
       <c r="B260" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C260" s="26" t="s">
+      <c r="C260" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D260" s="26"/>
-      <c r="E260" s="26"/>
+      <c r="D260" s="23"/>
+      <c r="E260" s="23"/>
       <c r="F260" s="15">
         <v>1610</v>
       </c>
@@ -10743,11 +10770,11 @@
       <c r="B261" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C261" s="26" t="s">
+      <c r="C261" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D261" s="26"/>
-      <c r="E261" s="26"/>
+      <c r="D261" s="23"/>
+      <c r="E261" s="23"/>
       <c r="F261" s="15">
         <v>1610</v>
       </c>
@@ -10780,11 +10807,11 @@
       <c r="B262" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C262" s="26" t="s">
+      <c r="C262" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D262" s="26"/>
-      <c r="E262" s="26"/>
+      <c r="D262" s="23"/>
+      <c r="E262" s="23"/>
       <c r="F262" s="15">
         <v>1610</v>
       </c>
@@ -10817,11 +10844,11 @@
       <c r="B263" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C263" s="26" t="s">
+      <c r="C263" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="D263" s="26"/>
-      <c r="E263" s="26"/>
+      <c r="D263" s="23"/>
+      <c r="E263" s="23"/>
       <c r="F263" s="15">
         <v>1433</v>
       </c>
@@ -10854,11 +10881,11 @@
       <c r="B264" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C264" s="26" t="s">
+      <c r="C264" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D264" s="26"/>
-      <c r="E264" s="26"/>
+      <c r="D264" s="23"/>
+      <c r="E264" s="23"/>
       <c r="F264" s="15">
         <v>1533</v>
       </c>
@@ -10891,11 +10918,11 @@
       <c r="B265" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C265" s="26" t="s">
+      <c r="C265" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D265" s="26"/>
-      <c r="E265" s="26"/>
+      <c r="D265" s="23"/>
+      <c r="E265" s="23"/>
       <c r="F265" s="15">
         <v>1533</v>
       </c>
@@ -10928,11 +10955,11 @@
       <c r="B266" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C266" s="26" t="s">
+      <c r="C266" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D266" s="26"/>
-      <c r="E266" s="26"/>
+      <c r="D266" s="23"/>
+      <c r="E266" s="23"/>
       <c r="F266" s="15">
         <v>1533</v>
       </c>
@@ -10965,11 +10992,11 @@
       <c r="B267" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C267" s="26" t="s">
+      <c r="C267" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D267" s="26"/>
-      <c r="E267" s="26"/>
+      <c r="D267" s="23"/>
+      <c r="E267" s="23"/>
       <c r="F267" s="15">
         <v>1533</v>
       </c>
@@ -11002,11 +11029,11 @@
       <c r="B268" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C268" s="26" t="s">
+      <c r="C268" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D268" s="26"/>
-      <c r="E268" s="26"/>
+      <c r="D268" s="23"/>
+      <c r="E268" s="23"/>
       <c r="F268" s="15">
         <v>1466</v>
       </c>
@@ -11039,11 +11066,11 @@
       <c r="B269" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C269" s="26" t="s">
+      <c r="C269" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D269" s="26"/>
-      <c r="E269" s="26"/>
+      <c r="D269" s="23"/>
+      <c r="E269" s="23"/>
       <c r="F269" s="15">
         <v>1641</v>
       </c>
@@ -11076,11 +11103,11 @@
       <c r="B270" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C270" s="26" t="s">
+      <c r="C270" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D270" s="26"/>
-      <c r="E270" s="26"/>
+      <c r="D270" s="23"/>
+      <c r="E270" s="23"/>
       <c r="F270" s="15">
         <v>1641</v>
       </c>
@@ -11113,11 +11140,11 @@
       <c r="B271" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C271" s="26" t="s">
+      <c r="C271" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="D271" s="26"/>
-      <c r="E271" s="26"/>
+      <c r="D271" s="23"/>
+      <c r="E271" s="23"/>
       <c r="F271" s="15">
         <v>1450</v>
       </c>
@@ -11150,11 +11177,11 @@
       <c r="B272" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C272" s="26" t="s">
+      <c r="C272" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D272" s="26"/>
-      <c r="E272" s="26"/>
+      <c r="D272" s="23"/>
+      <c r="E272" s="23"/>
       <c r="F272" s="15">
         <v>1508</v>
       </c>
@@ -11187,11 +11214,11 @@
       <c r="B273" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C273" s="26" t="s">
+      <c r="C273" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="D273" s="26"/>
-      <c r="E273" s="26"/>
+      <c r="D273" s="23"/>
+      <c r="E273" s="23"/>
       <c r="F273" s="15">
         <v>1479</v>
       </c>
@@ -11224,11 +11251,11 @@
       <c r="B274" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C274" s="26" t="s">
+      <c r="C274" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D274" s="26"/>
-      <c r="E274" s="26"/>
+      <c r="D274" s="23"/>
+      <c r="E274" s="23"/>
       <c r="F274" s="15">
         <v>1613</v>
       </c>
@@ -11261,11 +11288,11 @@
       <c r="B275" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C275" s="26" t="s">
+      <c r="C275" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D275" s="26"/>
-      <c r="E275" s="26"/>
+      <c r="D275" s="23"/>
+      <c r="E275" s="23"/>
       <c r="F275" s="15">
         <v>1613</v>
       </c>
@@ -11298,11 +11325,11 @@
       <c r="B276" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C276" s="26" t="s">
+      <c r="C276" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="D276" s="26"/>
-      <c r="E276" s="26"/>
+      <c r="D276" s="23"/>
+      <c r="E276" s="23"/>
       <c r="F276" s="15">
         <v>1417</v>
       </c>
@@ -11335,11 +11362,11 @@
       <c r="B277" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C277" s="26" t="s">
+      <c r="C277" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="D277" s="26"/>
-      <c r="E277" s="26"/>
+      <c r="D277" s="23"/>
+      <c r="E277" s="23"/>
       <c r="F277" s="15">
         <v>1572</v>
       </c>
@@ -11372,11 +11399,11 @@
       <c r="B278" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C278" s="26" t="s">
+      <c r="C278" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D278" s="26"/>
-      <c r="E278" s="26"/>
+      <c r="D278" s="23"/>
+      <c r="E278" s="23"/>
       <c r="F278" s="15">
         <v>1470</v>
       </c>
@@ -11409,11 +11436,11 @@
       <c r="B279" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C279" s="26" t="s">
+      <c r="C279" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D279" s="26"/>
-      <c r="E279" s="26"/>
+      <c r="D279" s="23"/>
+      <c r="E279" s="23"/>
       <c r="F279" s="15">
         <v>1470</v>
       </c>
@@ -11446,11 +11473,11 @@
       <c r="B280" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C280" s="26" t="s">
+      <c r="C280" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D280" s="26"/>
-      <c r="E280" s="26"/>
+      <c r="D280" s="23"/>
+      <c r="E280" s="23"/>
       <c r="F280" s="15">
         <v>1469</v>
       </c>
@@ -11483,11 +11510,11 @@
       <c r="B281" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C281" s="26" t="s">
+      <c r="C281" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="D281" s="26"/>
-      <c r="E281" s="26"/>
+      <c r="D281" s="23"/>
+      <c r="E281" s="23"/>
       <c r="F281" s="15">
         <v>1472</v>
       </c>
@@ -11520,11 +11547,11 @@
       <c r="B282" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C282" s="26" t="s">
+      <c r="C282" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D282" s="26"/>
-      <c r="E282" s="26"/>
+      <c r="D282" s="23"/>
+      <c r="E282" s="23"/>
       <c r="F282" s="15">
         <v>1610</v>
       </c>
@@ -11557,11 +11584,11 @@
       <c r="B283" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C283" s="26" t="s">
+      <c r="C283" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D283" s="26"/>
-      <c r="E283" s="26"/>
+      <c r="D283" s="23"/>
+      <c r="E283" s="23"/>
       <c r="F283" s="15">
         <v>1610</v>
       </c>
@@ -11594,11 +11621,11 @@
       <c r="B284" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C284" s="26" t="s">
+      <c r="C284" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="D284" s="26"/>
-      <c r="E284" s="26"/>
+      <c r="D284" s="23"/>
+      <c r="E284" s="23"/>
       <c r="F284" s="15">
         <v>1433</v>
       </c>
@@ -11631,11 +11658,11 @@
       <c r="B285" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C285" s="26" t="s">
+      <c r="C285" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D285" s="26"/>
-      <c r="E285" s="26"/>
+      <c r="D285" s="23"/>
+      <c r="E285" s="23"/>
       <c r="F285" s="15">
         <v>1533</v>
       </c>
@@ -11668,11 +11695,11 @@
       <c r="B286" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C286" s="26" t="s">
+      <c r="C286" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D286" s="26"/>
-      <c r="E286" s="26"/>
+      <c r="D286" s="23"/>
+      <c r="E286" s="23"/>
       <c r="F286" s="15">
         <v>1533</v>
       </c>
@@ -11705,11 +11732,11 @@
       <c r="B287" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C287" s="26" t="s">
+      <c r="C287" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D287" s="26"/>
-      <c r="E287" s="26"/>
+      <c r="D287" s="23"/>
+      <c r="E287" s="23"/>
       <c r="F287" s="15">
         <v>1533</v>
       </c>
@@ -11742,11 +11769,11 @@
       <c r="B288" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C288" s="26" t="s">
+      <c r="C288" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D288" s="26"/>
-      <c r="E288" s="26"/>
+      <c r="D288" s="23"/>
+      <c r="E288" s="23"/>
       <c r="F288" s="15">
         <v>1533</v>
       </c>
@@ -11779,11 +11806,11 @@
       <c r="B289" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C289" s="26" t="s">
+      <c r="C289" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D289" s="26"/>
-      <c r="E289" s="26"/>
+      <c r="D289" s="23"/>
+      <c r="E289" s="23"/>
       <c r="F289" s="15">
         <v>1533</v>
       </c>
@@ -11816,11 +11843,11 @@
       <c r="B290" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C290" s="26" t="s">
+      <c r="C290" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D290" s="26"/>
-      <c r="E290" s="26"/>
+      <c r="D290" s="23"/>
+      <c r="E290" s="23"/>
       <c r="F290" s="15">
         <v>1641</v>
       </c>
@@ -11853,11 +11880,11 @@
       <c r="B291" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C291" s="26" t="s">
+      <c r="C291" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="D291" s="26"/>
-      <c r="E291" s="26"/>
+      <c r="D291" s="23"/>
+      <c r="E291" s="23"/>
       <c r="F291" s="15">
         <v>1450</v>
       </c>
@@ -11890,11 +11917,11 @@
       <c r="B292" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C292" s="26" t="s">
+      <c r="C292" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="D292" s="26"/>
-      <c r="E292" s="26"/>
+      <c r="D292" s="23"/>
+      <c r="E292" s="23"/>
       <c r="F292" s="15">
         <v>1508</v>
       </c>
@@ -11927,11 +11954,11 @@
       <c r="B293" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C293" s="26" t="s">
+      <c r="C293" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="D293" s="26"/>
-      <c r="E293" s="26"/>
+      <c r="D293" s="23"/>
+      <c r="E293" s="23"/>
       <c r="F293" s="15">
         <v>1479</v>
       </c>
@@ -11964,11 +11991,11 @@
       <c r="B294" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="C294" s="26" t="s">
+      <c r="C294" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="D294" s="26"/>
-      <c r="E294" s="26"/>
+      <c r="D294" s="23"/>
+      <c r="E294" s="23"/>
       <c r="F294" s="15">
         <v>1467</v>
       </c>
@@ -12001,11 +12028,11 @@
       <c r="B295" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C295" s="26" t="s">
+      <c r="C295" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="D295" s="26"/>
-      <c r="E295" s="26"/>
+      <c r="D295" s="23"/>
+      <c r="E295" s="23"/>
       <c r="F295" s="15">
         <v>1571</v>
       </c>
@@ -12038,11 +12065,11 @@
       <c r="B296" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C296" s="26" t="s">
+      <c r="C296" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="D296" s="26"/>
-      <c r="E296" s="26"/>
+      <c r="D296" s="23"/>
+      <c r="E296" s="23"/>
       <c r="F296" s="15">
         <v>1613</v>
       </c>
@@ -12075,11 +12102,11 @@
       <c r="B297" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C297" s="26" t="s">
+      <c r="C297" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D297" s="26"/>
-      <c r="E297" s="26"/>
+      <c r="D297" s="23"/>
+      <c r="E297" s="23"/>
       <c r="F297" s="15">
         <v>1416</v>
       </c>
@@ -12112,11 +12139,11 @@
       <c r="B298" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C298" s="26" t="s">
+      <c r="C298" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="D298" s="26"/>
-      <c r="E298" s="26"/>
+      <c r="D298" s="23"/>
+      <c r="E298" s="23"/>
       <c r="F298" s="15">
         <v>1418</v>
       </c>
@@ -12149,11 +12176,11 @@
       <c r="B299" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C299" s="26" t="s">
+      <c r="C299" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="D299" s="26"/>
-      <c r="E299" s="26"/>
+      <c r="D299" s="23"/>
+      <c r="E299" s="23"/>
       <c r="F299" s="15">
         <v>1572</v>
       </c>
@@ -12186,11 +12213,11 @@
       <c r="B300" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C300" s="26" t="s">
+      <c r="C300" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D300" s="26"/>
-      <c r="E300" s="26"/>
+      <c r="D300" s="23"/>
+      <c r="E300" s="23"/>
       <c r="F300" s="15">
         <v>1470</v>
       </c>
@@ -12223,11 +12250,11 @@
       <c r="B301" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C301" s="26" t="s">
+      <c r="C301" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="D301" s="26"/>
-      <c r="E301" s="26"/>
+      <c r="D301" s="23"/>
+      <c r="E301" s="23"/>
       <c r="F301" s="15">
         <v>1458</v>
       </c>
@@ -12260,11 +12287,11 @@
       <c r="B302" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C302" s="26" t="s">
+      <c r="C302" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D302" s="26"/>
-      <c r="E302" s="26"/>
+      <c r="D302" s="23"/>
+      <c r="E302" s="23"/>
       <c r="F302" s="15">
         <v>1469</v>
       </c>
@@ -12297,11 +12324,11 @@
       <c r="B303" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C303" s="26" t="s">
+      <c r="C303" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="D303" s="26"/>
-      <c r="E303" s="26"/>
+      <c r="D303" s="23"/>
+      <c r="E303" s="23"/>
       <c r="F303" s="15">
         <v>1469</v>
       </c>
@@ -12334,11 +12361,11 @@
       <c r="B304" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C304" s="26" t="s">
+      <c r="C304" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D304" s="26"/>
-      <c r="E304" s="26"/>
+      <c r="D304" s="23"/>
+      <c r="E304" s="23"/>
       <c r="F304" s="15">
         <v>1610</v>
       </c>
@@ -12371,11 +12398,11 @@
       <c r="B305" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C305" s="26" t="s">
+      <c r="C305" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D305" s="26"/>
-      <c r="E305" s="26"/>
+      <c r="D305" s="23"/>
+      <c r="E305" s="23"/>
       <c r="F305" s="15">
         <v>1610</v>
       </c>
@@ -12408,11 +12435,11 @@
       <c r="B306" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C306" s="26" t="s">
+      <c r="C306" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="D306" s="26"/>
-      <c r="E306" s="26"/>
+      <c r="D306" s="23"/>
+      <c r="E306" s="23"/>
       <c r="F306" s="15">
         <v>1499</v>
       </c>
@@ -12445,11 +12472,11 @@
       <c r="B307" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C307" s="26" t="s">
+      <c r="C307" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="D307" s="26"/>
-      <c r="E307" s="26"/>
+      <c r="D307" s="23"/>
+      <c r="E307" s="23"/>
       <c r="F307" s="15">
         <v>1433</v>
       </c>
@@ -12482,11 +12509,11 @@
       <c r="B308" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C308" s="26" t="s">
+      <c r="C308" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D308" s="26"/>
-      <c r="E308" s="26"/>
+      <c r="D308" s="23"/>
+      <c r="E308" s="23"/>
       <c r="F308" s="15">
         <v>1533</v>
       </c>
@@ -12519,11 +12546,11 @@
       <c r="B309" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C309" s="26" t="s">
+      <c r="C309" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D309" s="26"/>
-      <c r="E309" s="26"/>
+      <c r="D309" s="23"/>
+      <c r="E309" s="23"/>
       <c r="F309" s="15">
         <v>1533</v>
       </c>
@@ -12556,11 +12583,11 @@
       <c r="B310" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C310" s="26" t="s">
+      <c r="C310" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D310" s="26"/>
-      <c r="E310" s="26"/>
+      <c r="D310" s="23"/>
+      <c r="E310" s="23"/>
       <c r="F310" s="15">
         <v>1533</v>
       </c>
@@ -12593,11 +12620,11 @@
       <c r="B311" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C311" s="26" t="s">
+      <c r="C311" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D311" s="26"/>
-      <c r="E311" s="26"/>
+      <c r="D311" s="23"/>
+      <c r="E311" s="23"/>
       <c r="F311" s="15">
         <v>1533</v>
       </c>
@@ -12630,11 +12657,11 @@
       <c r="B312" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C312" s="26" t="s">
+      <c r="C312" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D312" s="26"/>
-      <c r="E312" s="26"/>
+      <c r="D312" s="23"/>
+      <c r="E312" s="23"/>
       <c r="F312" s="15">
         <v>1533</v>
       </c>
@@ -12667,11 +12694,11 @@
       <c r="B313" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C313" s="26" t="s">
+      <c r="C313" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="D313" s="26"/>
-      <c r="E313" s="26"/>
+      <c r="D313" s="23"/>
+      <c r="E313" s="23"/>
       <c r="F313" s="15">
         <v>1533</v>
       </c>
@@ -12704,11 +12731,11 @@
       <c r="B314" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C314" s="26" t="s">
+      <c r="C314" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D314" s="26"/>
-      <c r="E314" s="26"/>
+      <c r="D314" s="23"/>
+      <c r="E314" s="23"/>
       <c r="F314" s="15">
         <v>1641</v>
       </c>
@@ -12741,11 +12768,11 @@
       <c r="B315" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C315" s="26" t="s">
+      <c r="C315" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="D315" s="26"/>
-      <c r="E315" s="26"/>
+      <c r="D315" s="23"/>
+      <c r="E315" s="23"/>
       <c r="F315" s="15">
         <v>1641</v>
       </c>
@@ -12771,328 +12798,1131 @@
         <v>837.86</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B316" s="3"/>
-      <c r="C316" s="23"/>
-      <c r="D316" s="24"/>
-      <c r="E316" s="25"/>
-      <c r="F316" s="10"/>
-      <c r="G316" s="11"/>
-      <c r="H316" s="4"/>
-      <c r="I316" s="3"/>
-      <c r="J316" s="5"/>
-      <c r="K316" s="6"/>
-      <c r="L316" s="7"/>
-      <c r="M316" s="5"/>
-    </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B317" s="3"/>
-      <c r="C317" s="23"/>
-      <c r="D317" s="24"/>
-      <c r="E317" s="25"/>
-      <c r="F317" s="10"/>
-      <c r="G317" s="11"/>
-      <c r="H317" s="4"/>
-      <c r="I317" s="3"/>
-      <c r="J317" s="5"/>
-      <c r="K317" s="6"/>
-      <c r="L317" s="7"/>
-      <c r="M317" s="5"/>
-    </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="B318" s="3"/>
-      <c r="C318" s="23"/>
-      <c r="D318" s="24"/>
-      <c r="E318" s="25"/>
-      <c r="F318" s="10"/>
-      <c r="G318" s="11"/>
-      <c r="H318" s="4"/>
-      <c r="I318" s="3"/>
-      <c r="J318" s="5"/>
-      <c r="K318" s="6"/>
-      <c r="L318" s="7"/>
-      <c r="M318" s="5"/>
+    <row r="316" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A316" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B316" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C316" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D316" s="23"/>
+      <c r="E316" s="23"/>
+      <c r="F316" s="15">
+        <v>1641</v>
+      </c>
+      <c r="G316" s="15">
+        <v>1201</v>
+      </c>
+      <c r="H316" s="5">
+        <v>3383.42</v>
+      </c>
+      <c r="I316" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J316" s="17">
+        <v>3734.74</v>
+      </c>
+      <c r="K316" s="9">
+        <v>194</v>
+      </c>
+      <c r="L316" s="4">
+        <v>316.2</v>
+      </c>
+      <c r="M316" s="5">
+        <v>4050.94</v>
+      </c>
+    </row>
+    <row r="317" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A317" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B317" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C317" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D317" s="23"/>
+      <c r="E317" s="23"/>
+      <c r="F317" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G317" s="16">
+        <v>506</v>
+      </c>
+      <c r="H317" s="4">
+        <v>688.62</v>
+      </c>
+      <c r="I317" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J317" s="18">
+        <v>793.96</v>
+      </c>
+      <c r="K317" s="9">
+        <v>174</v>
+      </c>
+      <c r="L317" s="7">
+        <v>61.93</v>
+      </c>
+      <c r="M317" s="4">
+        <v>855.89</v>
+      </c>
+    </row>
+    <row r="318" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A318" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B318" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C318" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D318" s="23"/>
+      <c r="E318" s="23"/>
+      <c r="F318" s="15">
+        <v>1450</v>
+      </c>
+      <c r="G318" s="16">
+        <v>508</v>
+      </c>
+      <c r="H318" s="5">
+        <v>3515.6</v>
+      </c>
+      <c r="I318" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J318" s="17">
+        <v>4069.63</v>
+      </c>
+      <c r="K318" s="9">
+        <v>156</v>
+      </c>
+      <c r="L318" s="4">
+        <v>293.01</v>
+      </c>
+      <c r="M318" s="5">
+        <v>4362.6400000000003</v>
+      </c>
+    </row>
+    <row r="319" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A319" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B319" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C319" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D319" s="23"/>
+      <c r="E319" s="23"/>
+      <c r="F319" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G319" s="16">
+        <v>506</v>
+      </c>
+      <c r="H319" s="5">
+        <v>4340.6400000000003</v>
+      </c>
+      <c r="I319" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J319" s="17">
+        <v>5004.6499999999996</v>
+      </c>
+      <c r="K319" s="9">
+        <v>154</v>
+      </c>
+      <c r="L319" s="4">
+        <v>357</v>
+      </c>
+      <c r="M319" s="5">
+        <v>5361.65</v>
+      </c>
+    </row>
+    <row r="320" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A320" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B320" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C320" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D320" s="23"/>
+      <c r="E320" s="23"/>
+      <c r="F320" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G320" s="16">
+        <v>506</v>
+      </c>
+      <c r="H320" s="4">
+        <v>688.62</v>
+      </c>
+      <c r="I320" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J320" s="18">
+        <v>793.96</v>
+      </c>
+      <c r="K320" s="9">
+        <v>143</v>
+      </c>
+      <c r="L320" s="7">
+        <v>53.73</v>
+      </c>
+      <c r="M320" s="4">
+        <v>847.69</v>
+      </c>
+    </row>
+    <row r="321" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A321" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B321" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C321" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D321" s="23"/>
+      <c r="E321" s="23"/>
+      <c r="F321" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G321" s="16">
+        <v>506</v>
+      </c>
+      <c r="H321" s="4">
+        <v>688.62</v>
+      </c>
+      <c r="I321" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J321" s="18">
+        <v>793.96</v>
+      </c>
+      <c r="K321" s="9">
+        <v>112</v>
+      </c>
+      <c r="L321" s="7">
+        <v>45.52</v>
+      </c>
+      <c r="M321" s="4">
+        <v>839.48</v>
+      </c>
+    </row>
+    <row r="322" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A322" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B322" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C322" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D322" s="23"/>
+      <c r="E322" s="23"/>
+      <c r="F322" s="15">
+        <v>1508</v>
+      </c>
+      <c r="G322" s="15">
+        <v>1306</v>
+      </c>
+      <c r="H322" s="4">
+        <v>565.54999999999995</v>
+      </c>
+      <c r="I322" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J322" s="18">
+        <v>593.98</v>
+      </c>
+      <c r="K322" s="9">
+        <v>107</v>
+      </c>
+      <c r="L322" s="7">
+        <v>33.07</v>
+      </c>
+      <c r="M322" s="4">
+        <v>627.04999999999995</v>
+      </c>
+    </row>
+    <row r="323" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A323" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B323" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C323" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D323" s="23"/>
+      <c r="E323" s="23"/>
+      <c r="F323" s="15">
+        <v>1610</v>
+      </c>
+      <c r="G323" s="15">
+        <v>1003</v>
+      </c>
+      <c r="H323" s="5">
+        <v>1300</v>
+      </c>
+      <c r="I323" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J323" s="17">
+        <v>1264.5899999999999</v>
+      </c>
+      <c r="K323" s="9">
+        <v>105</v>
+      </c>
+      <c r="L323" s="7">
+        <v>69.55</v>
+      </c>
+      <c r="M323" s="5">
+        <v>1334.14</v>
+      </c>
+    </row>
+    <row r="324" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A324" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B324" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C324" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D324" s="23"/>
+      <c r="E324" s="23"/>
+      <c r="F324" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G324" s="16">
+        <v>506</v>
+      </c>
+      <c r="H324" s="4">
+        <v>688.62</v>
+      </c>
+      <c r="I324" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J324" s="18">
+        <v>793.96</v>
+      </c>
+      <c r="K324" s="6">
+        <v>84</v>
+      </c>
+      <c r="L324" s="7">
+        <v>38.11</v>
+      </c>
+      <c r="M324" s="4">
+        <v>832.07</v>
+      </c>
+    </row>
+    <row r="325" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A325" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B325" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C325" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D325" s="23"/>
+      <c r="E325" s="23"/>
+      <c r="F325" s="15">
+        <v>1610</v>
+      </c>
+      <c r="G325" s="15">
+        <v>1003</v>
+      </c>
+      <c r="H325" s="5">
+        <v>1300</v>
+      </c>
+      <c r="I325" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J325" s="17">
+        <v>1453.41</v>
+      </c>
+      <c r="K325" s="6">
+        <v>77</v>
+      </c>
+      <c r="L325" s="7">
+        <v>66.37</v>
+      </c>
+      <c r="M325" s="5">
+        <v>1519.78</v>
+      </c>
+    </row>
+    <row r="326" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A326" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B326" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C326" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="D326" s="23"/>
+      <c r="E326" s="23"/>
+      <c r="F326" s="15">
+        <v>1479</v>
+      </c>
+      <c r="G326" s="16">
+        <v>803</v>
+      </c>
+      <c r="H326" s="5">
+        <v>1467.17</v>
+      </c>
+      <c r="I326" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J326" s="17">
+        <v>1693.81</v>
+      </c>
+      <c r="K326" s="6">
+        <v>74</v>
+      </c>
+      <c r="L326" s="7">
+        <v>75.66</v>
+      </c>
+      <c r="M326" s="5">
+        <v>1769.47</v>
+      </c>
+    </row>
+    <row r="327" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A327" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B327" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C327" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D327" s="23"/>
+      <c r="E327" s="23"/>
+      <c r="F327" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G327" s="16">
+        <v>506</v>
+      </c>
+      <c r="H327" s="4">
+        <v>688.62</v>
+      </c>
+      <c r="I327" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J327" s="18">
+        <v>793.96</v>
+      </c>
+      <c r="K327" s="6">
+        <v>53</v>
+      </c>
+      <c r="L327" s="7">
+        <v>29.91</v>
+      </c>
+      <c r="M327" s="4">
+        <v>823.87</v>
+      </c>
+    </row>
+    <row r="328" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A328" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B328" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C328" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D328" s="23"/>
+      <c r="E328" s="23"/>
+      <c r="F328" s="15">
+        <v>1458</v>
+      </c>
+      <c r="G328" s="16">
+        <v>403</v>
+      </c>
+      <c r="H328" s="4">
+        <v>813.02</v>
+      </c>
+      <c r="I328" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J328" s="18">
+        <v>941.15</v>
+      </c>
+      <c r="K328" s="6">
+        <v>48</v>
+      </c>
+      <c r="L328" s="7">
+        <v>33.880000000000003</v>
+      </c>
+      <c r="M328" s="4">
+        <v>975.03</v>
+      </c>
+    </row>
+    <row r="329" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A329" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B329" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C329" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D329" s="23"/>
+      <c r="E329" s="23"/>
+      <c r="F329" s="15">
+        <v>1613</v>
+      </c>
+      <c r="G329" s="15">
+        <v>1402</v>
+      </c>
+      <c r="H329" s="4">
+        <v>793.9</v>
+      </c>
+      <c r="I329" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J329" s="18">
+        <v>887.59</v>
+      </c>
+      <c r="K329" s="6">
+        <v>43</v>
+      </c>
+      <c r="L329" s="7">
+        <v>30.47</v>
+      </c>
+      <c r="M329" s="4">
+        <v>918.06</v>
+      </c>
+    </row>
+    <row r="330" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A330" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B330" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C330" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D330" s="23"/>
+      <c r="E330" s="23"/>
+      <c r="F330" s="15">
+        <v>1469</v>
+      </c>
+      <c r="G330" s="16">
+        <v>208</v>
+      </c>
+      <c r="H330" s="4">
+        <v>968.46</v>
+      </c>
+      <c r="I330" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J330" s="17">
+        <v>1121.08</v>
+      </c>
+      <c r="K330" s="6">
+        <v>43</v>
+      </c>
+      <c r="L330" s="7">
+        <v>38.49</v>
+      </c>
+      <c r="M330" s="5">
+        <v>1159.57</v>
+      </c>
+    </row>
+    <row r="331" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A331" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B331" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C331" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D331" s="23"/>
+      <c r="E331" s="23"/>
+      <c r="F331" s="15">
+        <v>1572</v>
+      </c>
+      <c r="G331" s="16">
+        <v>204</v>
+      </c>
+      <c r="H331" s="5">
+        <v>1000</v>
+      </c>
+      <c r="I331" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J331" s="17">
+        <v>1134.06</v>
+      </c>
+      <c r="K331" s="6">
+        <v>28</v>
+      </c>
+      <c r="L331" s="7">
+        <v>33.26</v>
+      </c>
+      <c r="M331" s="5">
+        <v>1167.32</v>
+      </c>
+    </row>
+    <row r="332" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A332" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C332" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D332" s="23"/>
+      <c r="E332" s="23"/>
+      <c r="F332" s="15">
+        <v>1499</v>
+      </c>
+      <c r="G332" s="16">
+        <v>606</v>
+      </c>
+      <c r="H332" s="5">
+        <v>1200</v>
+      </c>
+      <c r="I332" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J332" s="17">
+        <v>1385.37</v>
+      </c>
+      <c r="K332" s="6">
+        <v>28</v>
+      </c>
+      <c r="L332" s="7">
+        <v>40.64</v>
+      </c>
+      <c r="M332" s="5">
+        <v>1426.01</v>
+      </c>
+    </row>
+    <row r="333" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A333" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B333" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C333" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D333" s="23"/>
+      <c r="E333" s="23"/>
+      <c r="F333" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G333" s="16">
+        <v>506</v>
+      </c>
+      <c r="H333" s="4">
+        <v>688.62</v>
+      </c>
+      <c r="I333" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J333" s="18">
+        <v>793.96</v>
+      </c>
+      <c r="K333" s="6">
+        <v>23</v>
+      </c>
+      <c r="L333" s="7">
+        <v>21.97</v>
+      </c>
+      <c r="M333" s="4">
+        <v>815.93</v>
+      </c>
+    </row>
+    <row r="334" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A334" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B334" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C334" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D334" s="23"/>
+      <c r="E334" s="23"/>
+      <c r="F334" s="15">
+        <v>1419</v>
+      </c>
+      <c r="G334" s="16">
+        <v>607</v>
+      </c>
+      <c r="H334" s="5">
+        <v>1116.46</v>
+      </c>
+      <c r="I334" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J334" s="17">
+        <v>1296.4100000000001</v>
+      </c>
+      <c r="K334" s="6">
+        <v>18</v>
+      </c>
+      <c r="L334" s="7">
+        <v>33.71</v>
+      </c>
+      <c r="M334" s="5">
+        <v>1330.12</v>
+      </c>
+    </row>
+    <row r="335" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A335" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B335" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C335" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D335" s="23"/>
+      <c r="E335" s="23"/>
+      <c r="F335" s="15">
+        <v>1610</v>
+      </c>
+      <c r="G335" s="15">
+        <v>1003</v>
+      </c>
+      <c r="H335" s="5">
+        <v>1300</v>
+      </c>
+      <c r="I335" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J335" s="17">
+        <v>1453.41</v>
+      </c>
+      <c r="K335" s="6">
+        <v>16</v>
+      </c>
+      <c r="L335" s="7">
+        <v>36.82</v>
+      </c>
+      <c r="M335" s="5">
+        <v>1490.23</v>
+      </c>
+    </row>
+    <row r="336" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A336" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B336" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C336" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D336" s="23"/>
+      <c r="E336" s="23"/>
+      <c r="F336" s="15">
+        <v>1613</v>
+      </c>
+      <c r="G336" s="15">
+        <v>1402</v>
+      </c>
+      <c r="H336" s="4">
+        <v>793.9</v>
+      </c>
+      <c r="I336" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J336" s="18">
+        <v>887.59</v>
+      </c>
+      <c r="K336" s="6">
+        <v>13</v>
+      </c>
+      <c r="L336" s="7">
+        <v>21.6</v>
+      </c>
+      <c r="M336" s="4">
+        <v>909.19</v>
+      </c>
+    </row>
+    <row r="337" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A337" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B337" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C337" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D337" s="23"/>
+      <c r="E337" s="23"/>
+      <c r="F337" s="15">
+        <v>1469</v>
+      </c>
+      <c r="G337" s="16">
+        <v>208</v>
+      </c>
+      <c r="H337" s="4">
+        <v>968.46</v>
+      </c>
+      <c r="I337" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J337" s="17">
+        <v>1121.08</v>
+      </c>
+      <c r="K337" s="6">
+        <v>13</v>
+      </c>
+      <c r="L337" s="7">
+        <v>27.28</v>
+      </c>
+      <c r="M337" s="5">
+        <v>1148.3599999999999</v>
+      </c>
+    </row>
+    <row r="338" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A338" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B338" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C338" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="D338" s="23"/>
+      <c r="E338" s="23"/>
+      <c r="F338" s="15">
+        <v>1472</v>
+      </c>
+      <c r="G338" s="16">
+        <v>502</v>
+      </c>
+      <c r="H338" s="4">
+        <v>677.17</v>
+      </c>
+      <c r="I338" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J338" s="18">
+        <v>783.89</v>
+      </c>
+      <c r="K338" s="6">
+        <v>13</v>
+      </c>
+      <c r="L338" s="7">
+        <v>19.079999999999998</v>
+      </c>
+      <c r="M338" s="4">
+        <v>802.97</v>
+      </c>
+    </row>
+    <row r="339" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A339" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B339" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C339" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D339" s="23"/>
+      <c r="E339" s="23"/>
+      <c r="F339" s="15">
+        <v>1457</v>
+      </c>
+      <c r="G339" s="16">
+        <v>507</v>
+      </c>
+      <c r="H339" s="4">
+        <v>632.9</v>
+      </c>
+      <c r="I339" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J339" s="18">
+        <v>732.64</v>
+      </c>
+      <c r="K339" s="6">
+        <v>13</v>
+      </c>
+      <c r="L339" s="7">
+        <v>17.82</v>
+      </c>
+      <c r="M339" s="4">
+        <v>750.46</v>
+      </c>
+    </row>
+    <row r="340" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A340" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B340" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C340" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D340" s="23"/>
+      <c r="E340" s="23"/>
+      <c r="F340" s="15">
+        <v>1641</v>
+      </c>
+      <c r="G340" s="15">
+        <v>1201</v>
+      </c>
+      <c r="H340" s="5">
+        <v>3383.42</v>
+      </c>
+      <c r="I340" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J340" s="17">
+        <v>3734.74</v>
+      </c>
+      <c r="K340" s="6">
+        <v>13</v>
+      </c>
+      <c r="L340" s="7">
+        <v>90.87</v>
+      </c>
+      <c r="M340" s="5">
+        <v>3825.61</v>
+      </c>
+    </row>
+    <row r="341" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A341" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B341" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C341" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D341" s="23"/>
+      <c r="E341" s="23"/>
+      <c r="F341" s="15">
+        <v>1470</v>
+      </c>
+      <c r="G341" s="16">
+        <v>602</v>
+      </c>
+      <c r="H341" s="4">
+        <v>763.85</v>
+      </c>
+      <c r="I341" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J341" s="18">
+        <v>884.23</v>
+      </c>
+      <c r="K341" s="6">
+        <v>12</v>
+      </c>
+      <c r="L341" s="7">
+        <v>21.22</v>
+      </c>
+      <c r="M341" s="4">
+        <v>905.45</v>
+      </c>
+    </row>
+    <row r="342" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A342" s="14">
+        <v>46143</v>
+      </c>
+      <c r="B342" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C342" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D342" s="23"/>
+      <c r="E342" s="23"/>
+      <c r="F342" s="15">
+        <v>1467</v>
+      </c>
+      <c r="G342" s="16">
+        <v>207</v>
+      </c>
+      <c r="H342" s="4">
+        <v>675.78</v>
+      </c>
+      <c r="I342" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J342" s="18">
+        <v>782.28</v>
+      </c>
+      <c r="K342" s="19">
+        <v>3</v>
+      </c>
+      <c r="L342" s="7">
+        <v>16.43</v>
+      </c>
+      <c r="M342" s="4">
+        <v>798.71</v>
+      </c>
+    </row>
+    <row r="343" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A343" s="14"/>
+    </row>
+    <row r="344" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A344" s="14"/>
+    </row>
+    <row r="345" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A345" s="14"/>
+    </row>
+    <row r="346" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A346" s="14"/>
+    </row>
+    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A347" s="14"/>
+    </row>
+    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A348" s="14"/>
+    </row>
+    <row r="349" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A349" s="14"/>
+    </row>
+    <row r="350" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A350" s="14"/>
+    </row>
+    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A351" s="14"/>
+    </row>
+    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A352" s="14"/>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A353" s="14"/>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A354" s="14"/>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A355" s="14"/>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A356" s="14"/>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A357" s="14"/>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A358" s="14"/>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A359" s="14"/>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A360" s="14"/>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A361" s="14"/>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A362" s="14"/>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A363" s="14"/>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A364" s="14"/>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A365" s="14"/>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A366" s="14"/>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A367" s="14"/>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A368" s="14"/>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A369" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="318">
-    <mergeCell ref="C291:E291"/>
-    <mergeCell ref="C292:E292"/>
-    <mergeCell ref="C293:E293"/>
-    <mergeCell ref="C294:E294"/>
-    <mergeCell ref="C295:E295"/>
-    <mergeCell ref="C314:E314"/>
-    <mergeCell ref="C315:E315"/>
+  <mergeCells count="342">
+    <mergeCell ref="C340:E340"/>
+    <mergeCell ref="C341:E341"/>
+    <mergeCell ref="C342:E342"/>
+    <mergeCell ref="C337:E337"/>
+    <mergeCell ref="C338:E338"/>
+    <mergeCell ref="C339:E339"/>
+    <mergeCell ref="C334:E334"/>
+    <mergeCell ref="C335:E335"/>
+    <mergeCell ref="C336:E336"/>
+    <mergeCell ref="C331:E331"/>
+    <mergeCell ref="C332:E332"/>
+    <mergeCell ref="C333:E333"/>
+    <mergeCell ref="C328:E328"/>
+    <mergeCell ref="C329:E329"/>
+    <mergeCell ref="C330:E330"/>
+    <mergeCell ref="C325:E325"/>
+    <mergeCell ref="C326:E326"/>
+    <mergeCell ref="C327:E327"/>
+    <mergeCell ref="C322:E322"/>
+    <mergeCell ref="C323:E323"/>
+    <mergeCell ref="C324:E324"/>
+    <mergeCell ref="C319:E319"/>
+    <mergeCell ref="C320:E320"/>
+    <mergeCell ref="C321:E321"/>
     <mergeCell ref="C316:E316"/>
     <mergeCell ref="C317:E317"/>
     <mergeCell ref="C318:E318"/>
-    <mergeCell ref="C305:E305"/>
-    <mergeCell ref="C306:E306"/>
-    <mergeCell ref="C307:E307"/>
-    <mergeCell ref="C308:E308"/>
-    <mergeCell ref="C309:E309"/>
-    <mergeCell ref="C310:E310"/>
-    <mergeCell ref="C311:E311"/>
-    <mergeCell ref="C312:E312"/>
-    <mergeCell ref="C313:E313"/>
-    <mergeCell ref="C296:E296"/>
-    <mergeCell ref="C297:E297"/>
-    <mergeCell ref="C298:E298"/>
-    <mergeCell ref="C299:E299"/>
-    <mergeCell ref="C300:E300"/>
-    <mergeCell ref="C301:E301"/>
-    <mergeCell ref="C302:E302"/>
-    <mergeCell ref="C303:E303"/>
-    <mergeCell ref="C304:E304"/>
-    <mergeCell ref="C287:E287"/>
-    <mergeCell ref="C288:E288"/>
-    <mergeCell ref="C289:E289"/>
-    <mergeCell ref="C290:E290"/>
-    <mergeCell ref="C278:E278"/>
-    <mergeCell ref="C279:E279"/>
-    <mergeCell ref="C280:E280"/>
-    <mergeCell ref="C281:E281"/>
-    <mergeCell ref="C282:E282"/>
-    <mergeCell ref="C283:E283"/>
-    <mergeCell ref="C284:E284"/>
-    <mergeCell ref="C285:E285"/>
-    <mergeCell ref="C286:E286"/>
-    <mergeCell ref="C269:E269"/>
-    <mergeCell ref="C270:E270"/>
-    <mergeCell ref="C271:E271"/>
-    <mergeCell ref="C272:E272"/>
-    <mergeCell ref="C273:E273"/>
-    <mergeCell ref="C274:E274"/>
-    <mergeCell ref="C275:E275"/>
-    <mergeCell ref="C276:E276"/>
-    <mergeCell ref="C277:E277"/>
-    <mergeCell ref="C260:E260"/>
-    <mergeCell ref="C261:E261"/>
-    <mergeCell ref="C262:E262"/>
-    <mergeCell ref="C263:E263"/>
-    <mergeCell ref="C264:E264"/>
-    <mergeCell ref="C265:E265"/>
-    <mergeCell ref="C266:E266"/>
-    <mergeCell ref="C267:E267"/>
-    <mergeCell ref="C268:E268"/>
-    <mergeCell ref="C251:E251"/>
-    <mergeCell ref="C252:E252"/>
-    <mergeCell ref="C253:E253"/>
-    <mergeCell ref="C254:E254"/>
-    <mergeCell ref="C255:E255"/>
-    <mergeCell ref="C256:E256"/>
-    <mergeCell ref="C257:E257"/>
-    <mergeCell ref="C258:E258"/>
-    <mergeCell ref="C259:E259"/>
-    <mergeCell ref="C242:E242"/>
-    <mergeCell ref="C243:E243"/>
-    <mergeCell ref="C244:E244"/>
-    <mergeCell ref="C245:E245"/>
-    <mergeCell ref="C246:E246"/>
-    <mergeCell ref="C247:E247"/>
-    <mergeCell ref="C248:E248"/>
-    <mergeCell ref="C249:E249"/>
-    <mergeCell ref="C250:E250"/>
-    <mergeCell ref="C233:E233"/>
-    <mergeCell ref="C234:E234"/>
-    <mergeCell ref="C235:E235"/>
-    <mergeCell ref="C236:E236"/>
-    <mergeCell ref="C237:E237"/>
-    <mergeCell ref="C238:E238"/>
-    <mergeCell ref="C239:E239"/>
-    <mergeCell ref="C240:E240"/>
-    <mergeCell ref="C241:E241"/>
-    <mergeCell ref="C224:E224"/>
-    <mergeCell ref="C225:E225"/>
-    <mergeCell ref="C226:E226"/>
-    <mergeCell ref="C227:E227"/>
-    <mergeCell ref="C228:E228"/>
-    <mergeCell ref="C229:E229"/>
-    <mergeCell ref="C230:E230"/>
-    <mergeCell ref="C231:E231"/>
-    <mergeCell ref="C232:E232"/>
-    <mergeCell ref="C215:E215"/>
-    <mergeCell ref="C216:E216"/>
-    <mergeCell ref="C217:E217"/>
-    <mergeCell ref="C218:E218"/>
-    <mergeCell ref="C219:E219"/>
-    <mergeCell ref="C220:E220"/>
-    <mergeCell ref="C221:E221"/>
-    <mergeCell ref="C222:E222"/>
-    <mergeCell ref="C223:E223"/>
-    <mergeCell ref="C206:E206"/>
-    <mergeCell ref="C207:E207"/>
-    <mergeCell ref="C208:E208"/>
-    <mergeCell ref="C209:E209"/>
-    <mergeCell ref="C210:E210"/>
-    <mergeCell ref="C211:E211"/>
-    <mergeCell ref="C212:E212"/>
-    <mergeCell ref="C213:E213"/>
-    <mergeCell ref="C214:E214"/>
-    <mergeCell ref="C197:E197"/>
-    <mergeCell ref="C198:E198"/>
-    <mergeCell ref="C199:E199"/>
-    <mergeCell ref="C200:E200"/>
-    <mergeCell ref="C201:E201"/>
-    <mergeCell ref="C202:E202"/>
-    <mergeCell ref="C203:E203"/>
-    <mergeCell ref="C204:E204"/>
-    <mergeCell ref="C205:E205"/>
-    <mergeCell ref="C188:E188"/>
-    <mergeCell ref="C189:E189"/>
-    <mergeCell ref="C190:E190"/>
-    <mergeCell ref="C191:E191"/>
-    <mergeCell ref="C192:E192"/>
-    <mergeCell ref="C193:E193"/>
-    <mergeCell ref="C194:E194"/>
-    <mergeCell ref="C195:E195"/>
-    <mergeCell ref="C196:E196"/>
-    <mergeCell ref="C179:E179"/>
-    <mergeCell ref="C180:E180"/>
-    <mergeCell ref="C181:E181"/>
-    <mergeCell ref="C182:E182"/>
-    <mergeCell ref="C183:E183"/>
-    <mergeCell ref="C184:E184"/>
-    <mergeCell ref="C185:E185"/>
-    <mergeCell ref="C186:E186"/>
-    <mergeCell ref="C187:E187"/>
-    <mergeCell ref="C170:E170"/>
-    <mergeCell ref="C171:E171"/>
-    <mergeCell ref="C172:E172"/>
-    <mergeCell ref="C173:E173"/>
-    <mergeCell ref="C174:E174"/>
-    <mergeCell ref="C175:E175"/>
-    <mergeCell ref="C176:E176"/>
-    <mergeCell ref="C177:E177"/>
-    <mergeCell ref="C178:E178"/>
-    <mergeCell ref="C161:E161"/>
-    <mergeCell ref="C162:E162"/>
-    <mergeCell ref="C163:E163"/>
-    <mergeCell ref="C164:E164"/>
-    <mergeCell ref="C165:E165"/>
-    <mergeCell ref="C166:E166"/>
-    <mergeCell ref="C167:E167"/>
-    <mergeCell ref="C168:E168"/>
-    <mergeCell ref="C169:E169"/>
-    <mergeCell ref="C152:E152"/>
-    <mergeCell ref="C153:E153"/>
-    <mergeCell ref="C154:E154"/>
-    <mergeCell ref="C155:E155"/>
-    <mergeCell ref="C156:E156"/>
-    <mergeCell ref="C157:E157"/>
-    <mergeCell ref="C158:E158"/>
-    <mergeCell ref="C159:E159"/>
-    <mergeCell ref="C160:E160"/>
-    <mergeCell ref="C143:E143"/>
-    <mergeCell ref="C144:E144"/>
-    <mergeCell ref="C145:E145"/>
-    <mergeCell ref="C146:E146"/>
-    <mergeCell ref="C147:E147"/>
-    <mergeCell ref="C148:E148"/>
-    <mergeCell ref="C149:E149"/>
-    <mergeCell ref="C150:E150"/>
-    <mergeCell ref="C151:E151"/>
-    <mergeCell ref="C122:E122"/>
-    <mergeCell ref="C123:E123"/>
-    <mergeCell ref="C117:E117"/>
-    <mergeCell ref="C118:E118"/>
-    <mergeCell ref="C119:E119"/>
-    <mergeCell ref="C120:E120"/>
-    <mergeCell ref="C121:E121"/>
-    <mergeCell ref="C112:E112"/>
-    <mergeCell ref="C113:E113"/>
-    <mergeCell ref="C114:E114"/>
-    <mergeCell ref="C115:E115"/>
-    <mergeCell ref="C116:E116"/>
-    <mergeCell ref="C107:E107"/>
-    <mergeCell ref="C108:E108"/>
-    <mergeCell ref="C109:E109"/>
-    <mergeCell ref="C110:E110"/>
-    <mergeCell ref="C111:E111"/>
-    <mergeCell ref="C102:E102"/>
-    <mergeCell ref="C103:E103"/>
-    <mergeCell ref="C104:E104"/>
-    <mergeCell ref="C105:E105"/>
-    <mergeCell ref="C106:E106"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="C98:E98"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="C100:E100"/>
-    <mergeCell ref="C101:E101"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="C88:E88"/>
-    <mergeCell ref="C89:E89"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="C94:E94"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C127:E127"/>
+    <mergeCell ref="C128:E128"/>
+    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="C130:E130"/>
+    <mergeCell ref="C131:E131"/>
+    <mergeCell ref="C132:E132"/>
+    <mergeCell ref="C142:E142"/>
+    <mergeCell ref="C133:E133"/>
+    <mergeCell ref="C134:E134"/>
+    <mergeCell ref="C135:E135"/>
+    <mergeCell ref="C136:E136"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="C138:E138"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="C141:E141"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="C13:E13"/>
@@ -13117,22 +13947,281 @@
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C127:E127"/>
-    <mergeCell ref="C128:E128"/>
-    <mergeCell ref="C129:E129"/>
-    <mergeCell ref="C130:E130"/>
-    <mergeCell ref="C131:E131"/>
-    <mergeCell ref="C132:E132"/>
-    <mergeCell ref="C142:E142"/>
-    <mergeCell ref="C133:E133"/>
-    <mergeCell ref="C134:E134"/>
-    <mergeCell ref="C135:E135"/>
-    <mergeCell ref="C136:E136"/>
-    <mergeCell ref="C137:E137"/>
-    <mergeCell ref="C138:E138"/>
-    <mergeCell ref="C139:E139"/>
-    <mergeCell ref="C140:E140"/>
-    <mergeCell ref="C141:E141"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="C100:E100"/>
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C107:E107"/>
+    <mergeCell ref="C108:E108"/>
+    <mergeCell ref="C109:E109"/>
+    <mergeCell ref="C110:E110"/>
+    <mergeCell ref="C111:E111"/>
+    <mergeCell ref="C102:E102"/>
+    <mergeCell ref="C103:E103"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="C105:E105"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="C122:E122"/>
+    <mergeCell ref="C123:E123"/>
+    <mergeCell ref="C117:E117"/>
+    <mergeCell ref="C118:E118"/>
+    <mergeCell ref="C119:E119"/>
+    <mergeCell ref="C120:E120"/>
+    <mergeCell ref="C121:E121"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="C113:E113"/>
+    <mergeCell ref="C114:E114"/>
+    <mergeCell ref="C115:E115"/>
+    <mergeCell ref="C116:E116"/>
+    <mergeCell ref="C143:E143"/>
+    <mergeCell ref="C144:E144"/>
+    <mergeCell ref="C145:E145"/>
+    <mergeCell ref="C146:E146"/>
+    <mergeCell ref="C147:E147"/>
+    <mergeCell ref="C148:E148"/>
+    <mergeCell ref="C149:E149"/>
+    <mergeCell ref="C150:E150"/>
+    <mergeCell ref="C151:E151"/>
+    <mergeCell ref="C152:E152"/>
+    <mergeCell ref="C153:E153"/>
+    <mergeCell ref="C154:E154"/>
+    <mergeCell ref="C155:E155"/>
+    <mergeCell ref="C156:E156"/>
+    <mergeCell ref="C157:E157"/>
+    <mergeCell ref="C158:E158"/>
+    <mergeCell ref="C159:E159"/>
+    <mergeCell ref="C160:E160"/>
+    <mergeCell ref="C161:E161"/>
+    <mergeCell ref="C162:E162"/>
+    <mergeCell ref="C163:E163"/>
+    <mergeCell ref="C164:E164"/>
+    <mergeCell ref="C165:E165"/>
+    <mergeCell ref="C166:E166"/>
+    <mergeCell ref="C167:E167"/>
+    <mergeCell ref="C168:E168"/>
+    <mergeCell ref="C169:E169"/>
+    <mergeCell ref="C170:E170"/>
+    <mergeCell ref="C171:E171"/>
+    <mergeCell ref="C172:E172"/>
+    <mergeCell ref="C173:E173"/>
+    <mergeCell ref="C174:E174"/>
+    <mergeCell ref="C175:E175"/>
+    <mergeCell ref="C176:E176"/>
+    <mergeCell ref="C177:E177"/>
+    <mergeCell ref="C178:E178"/>
+    <mergeCell ref="C179:E179"/>
+    <mergeCell ref="C180:E180"/>
+    <mergeCell ref="C181:E181"/>
+    <mergeCell ref="C182:E182"/>
+    <mergeCell ref="C183:E183"/>
+    <mergeCell ref="C184:E184"/>
+    <mergeCell ref="C185:E185"/>
+    <mergeCell ref="C186:E186"/>
+    <mergeCell ref="C187:E187"/>
+    <mergeCell ref="C188:E188"/>
+    <mergeCell ref="C189:E189"/>
+    <mergeCell ref="C190:E190"/>
+    <mergeCell ref="C191:E191"/>
+    <mergeCell ref="C192:E192"/>
+    <mergeCell ref="C193:E193"/>
+    <mergeCell ref="C194:E194"/>
+    <mergeCell ref="C195:E195"/>
+    <mergeCell ref="C196:E196"/>
+    <mergeCell ref="C197:E197"/>
+    <mergeCell ref="C198:E198"/>
+    <mergeCell ref="C199:E199"/>
+    <mergeCell ref="C200:E200"/>
+    <mergeCell ref="C201:E201"/>
+    <mergeCell ref="C202:E202"/>
+    <mergeCell ref="C203:E203"/>
+    <mergeCell ref="C204:E204"/>
+    <mergeCell ref="C205:E205"/>
+    <mergeCell ref="C206:E206"/>
+    <mergeCell ref="C207:E207"/>
+    <mergeCell ref="C208:E208"/>
+    <mergeCell ref="C209:E209"/>
+    <mergeCell ref="C210:E210"/>
+    <mergeCell ref="C211:E211"/>
+    <mergeCell ref="C212:E212"/>
+    <mergeCell ref="C213:E213"/>
+    <mergeCell ref="C214:E214"/>
+    <mergeCell ref="C215:E215"/>
+    <mergeCell ref="C216:E216"/>
+    <mergeCell ref="C217:E217"/>
+    <mergeCell ref="C218:E218"/>
+    <mergeCell ref="C219:E219"/>
+    <mergeCell ref="C220:E220"/>
+    <mergeCell ref="C221:E221"/>
+    <mergeCell ref="C222:E222"/>
+    <mergeCell ref="C223:E223"/>
+    <mergeCell ref="C224:E224"/>
+    <mergeCell ref="C225:E225"/>
+    <mergeCell ref="C226:E226"/>
+    <mergeCell ref="C227:E227"/>
+    <mergeCell ref="C228:E228"/>
+    <mergeCell ref="C229:E229"/>
+    <mergeCell ref="C230:E230"/>
+    <mergeCell ref="C231:E231"/>
+    <mergeCell ref="C232:E232"/>
+    <mergeCell ref="C233:E233"/>
+    <mergeCell ref="C234:E234"/>
+    <mergeCell ref="C235:E235"/>
+    <mergeCell ref="C236:E236"/>
+    <mergeCell ref="C237:E237"/>
+    <mergeCell ref="C238:E238"/>
+    <mergeCell ref="C239:E239"/>
+    <mergeCell ref="C240:E240"/>
+    <mergeCell ref="C241:E241"/>
+    <mergeCell ref="C242:E242"/>
+    <mergeCell ref="C243:E243"/>
+    <mergeCell ref="C244:E244"/>
+    <mergeCell ref="C245:E245"/>
+    <mergeCell ref="C246:E246"/>
+    <mergeCell ref="C247:E247"/>
+    <mergeCell ref="C248:E248"/>
+    <mergeCell ref="C249:E249"/>
+    <mergeCell ref="C250:E250"/>
+    <mergeCell ref="C251:E251"/>
+    <mergeCell ref="C252:E252"/>
+    <mergeCell ref="C253:E253"/>
+    <mergeCell ref="C254:E254"/>
+    <mergeCell ref="C255:E255"/>
+    <mergeCell ref="C256:E256"/>
+    <mergeCell ref="C257:E257"/>
+    <mergeCell ref="C258:E258"/>
+    <mergeCell ref="C259:E259"/>
+    <mergeCell ref="C260:E260"/>
+    <mergeCell ref="C261:E261"/>
+    <mergeCell ref="C262:E262"/>
+    <mergeCell ref="C263:E263"/>
+    <mergeCell ref="C264:E264"/>
+    <mergeCell ref="C265:E265"/>
+    <mergeCell ref="C266:E266"/>
+    <mergeCell ref="C267:E267"/>
+    <mergeCell ref="C268:E268"/>
+    <mergeCell ref="C269:E269"/>
+    <mergeCell ref="C270:E270"/>
+    <mergeCell ref="C271:E271"/>
+    <mergeCell ref="C272:E272"/>
+    <mergeCell ref="C273:E273"/>
+    <mergeCell ref="C274:E274"/>
+    <mergeCell ref="C275:E275"/>
+    <mergeCell ref="C276:E276"/>
+    <mergeCell ref="C277:E277"/>
+    <mergeCell ref="C287:E287"/>
+    <mergeCell ref="C288:E288"/>
+    <mergeCell ref="C289:E289"/>
+    <mergeCell ref="C290:E290"/>
+    <mergeCell ref="C278:E278"/>
+    <mergeCell ref="C279:E279"/>
+    <mergeCell ref="C280:E280"/>
+    <mergeCell ref="C281:E281"/>
+    <mergeCell ref="C282:E282"/>
+    <mergeCell ref="C283:E283"/>
+    <mergeCell ref="C284:E284"/>
+    <mergeCell ref="C285:E285"/>
+    <mergeCell ref="C286:E286"/>
+    <mergeCell ref="C305:E305"/>
+    <mergeCell ref="C306:E306"/>
+    <mergeCell ref="C307:E307"/>
+    <mergeCell ref="C308:E308"/>
+    <mergeCell ref="C309:E309"/>
+    <mergeCell ref="C310:E310"/>
+    <mergeCell ref="C311:E311"/>
+    <mergeCell ref="C312:E312"/>
+    <mergeCell ref="C313:E313"/>
+    <mergeCell ref="C291:E291"/>
+    <mergeCell ref="C292:E292"/>
+    <mergeCell ref="C293:E293"/>
+    <mergeCell ref="C294:E294"/>
+    <mergeCell ref="C295:E295"/>
+    <mergeCell ref="C314:E314"/>
+    <mergeCell ref="C315:E315"/>
+    <mergeCell ref="C296:E296"/>
+    <mergeCell ref="C297:E297"/>
+    <mergeCell ref="C298:E298"/>
+    <mergeCell ref="C299:E299"/>
+    <mergeCell ref="C300:E300"/>
+    <mergeCell ref="C301:E301"/>
+    <mergeCell ref="C302:E302"/>
+    <mergeCell ref="C303:E303"/>
+    <mergeCell ref="C304:E304"/>
   </mergeCells>
   <pageMargins left="0.52999994886203072" right="0.52999994886203072" top="0.52999994886203072" bottom="0.68999998212799307" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/data/vendas-inadimplentes.xlsx
+++ b/data/vendas-inadimplentes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B2307E-D3F8-4CAD-8301-522A51762F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC736CB6-4F90-4F10-BA6B-087E5EEE6AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="168">
   <si>
     <t>Data vecto</t>
   </si>
@@ -507,6 +507,36 @@
   </si>
   <si>
     <t>30/05/2026</t>
+  </si>
+  <si>
+    <t>01/05/2026</t>
+  </si>
+  <si>
+    <t>27/06/2026</t>
+  </si>
+  <si>
+    <t>DIOGO AUGUSTO DA SILVA NASCIMENTO (436)</t>
+  </si>
+  <si>
+    <t>20/06/2026</t>
+  </si>
+  <si>
+    <t>05/06/2026</t>
+  </si>
+  <si>
+    <t>21/06/2026</t>
+  </si>
+  <si>
+    <t>17/06/2026</t>
+  </si>
+  <si>
+    <t>15/06/2026</t>
+  </si>
+  <si>
+    <t>ROBSON MARINHO DA COSTA (404)</t>
+  </si>
+  <si>
+    <t>10/06/2026</t>
   </si>
 </sst>
 </file>
@@ -1050,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N369"/>
+  <dimension ref="A1:N371"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -13575,7 +13605,7 @@
         <v>909.19</v>
       </c>
     </row>
-    <row r="337" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="14">
         <v>46143</v>
       </c>
@@ -13612,7 +13642,7 @@
         <v>1148.3599999999999</v>
       </c>
     </row>
-    <row r="338" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="14">
         <v>46143</v>
       </c>
@@ -13649,7 +13679,7 @@
         <v>802.97</v>
       </c>
     </row>
-    <row r="339" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="14">
         <v>46143</v>
       </c>
@@ -13686,7 +13716,7 @@
         <v>750.46</v>
       </c>
     </row>
-    <row r="340" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="14">
         <v>46143</v>
       </c>
@@ -13723,7 +13753,7 @@
         <v>3825.61</v>
       </c>
     </row>
-    <row r="341" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="14">
         <v>46143</v>
       </c>
@@ -13760,7 +13790,7 @@
         <v>905.45</v>
       </c>
     </row>
-    <row r="342" spans="1:13" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="14">
         <v>46143</v>
       </c>
@@ -13797,132 +13827,1414 @@
         <v>798.71</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A343" s="14"/>
-    </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A344" s="14"/>
-    </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A345" s="14"/>
-    </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A346" s="14"/>
-    </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A347" s="14"/>
-    </row>
-    <row r="348" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A348" s="14"/>
-    </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A349" s="14"/>
-    </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A350" s="14"/>
-    </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A351" s="14"/>
-    </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A352" s="14"/>
-    </row>
-    <row r="353" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A353" s="14"/>
-    </row>
-    <row r="354" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A354" s="14"/>
-    </row>
-    <row r="355" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A355" s="14"/>
-    </row>
-    <row r="356" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A356" s="14"/>
-    </row>
-    <row r="357" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A357" s="14"/>
-    </row>
-    <row r="358" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A358" s="14"/>
-    </row>
-    <row r="359" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A359" s="14"/>
-    </row>
-    <row r="360" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A360" s="14"/>
-    </row>
-    <row r="361" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A361" s="14"/>
-    </row>
-    <row r="362" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A362" s="14"/>
-    </row>
-    <row r="363" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A363" s="14"/>
-    </row>
-    <row r="364" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A364" s="14"/>
-    </row>
-    <row r="365" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A365" s="14"/>
-    </row>
-    <row r="366" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A366" s="14"/>
-    </row>
-    <row r="367" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A367" s="14"/>
-    </row>
-    <row r="368" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A368" s="14"/>
-    </row>
-    <row r="369" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A369" s="14"/>
+    <row r="343" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A343" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B343" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C343" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D343" s="23"/>
+      <c r="E343" s="23"/>
+      <c r="F343" s="15">
+        <v>1450</v>
+      </c>
+      <c r="G343" s="16">
+        <v>508</v>
+      </c>
+      <c r="H343" s="5">
+        <v>3515.6</v>
+      </c>
+      <c r="I343" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J343" s="17">
+        <v>4105.4399999999996</v>
+      </c>
+      <c r="K343" s="9">
+        <v>186</v>
+      </c>
+      <c r="L343" s="4">
+        <v>336.65</v>
+      </c>
+      <c r="M343" s="5">
+        <v>4442.09</v>
+      </c>
+      <c r="N343" s="20"/>
+    </row>
+    <row r="344" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A344" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B344" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C344" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D344" s="23"/>
+      <c r="E344" s="23"/>
+      <c r="F344" s="15">
+        <v>1508</v>
+      </c>
+      <c r="G344" s="15">
+        <v>1306</v>
+      </c>
+      <c r="H344" s="4">
+        <v>565.54999999999995</v>
+      </c>
+      <c r="I344" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J344" s="18">
+        <v>599.20000000000005</v>
+      </c>
+      <c r="K344" s="9">
+        <v>137</v>
+      </c>
+      <c r="L344" s="7">
+        <v>39.340000000000003</v>
+      </c>
+      <c r="M344" s="4">
+        <v>638.54</v>
+      </c>
+      <c r="N344" s="20"/>
+    </row>
+    <row r="345" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A345" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B345" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C345" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="D345" s="23"/>
+      <c r="E345" s="23"/>
+      <c r="F345" s="15">
+        <v>1814</v>
+      </c>
+      <c r="G345" s="15">
+        <v>1502</v>
+      </c>
+      <c r="H345" s="5">
+        <v>1430</v>
+      </c>
+      <c r="I345" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J345" s="17">
+        <v>1468.98</v>
+      </c>
+      <c r="K345" s="19">
+        <v>5</v>
+      </c>
+      <c r="L345" s="7">
+        <v>31.83</v>
+      </c>
+      <c r="M345" s="5">
+        <v>1500.81</v>
+      </c>
+      <c r="N345" s="20"/>
+    </row>
+    <row r="346" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A346" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B346" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C346" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D346" s="23"/>
+      <c r="E346" s="23"/>
+      <c r="F346" s="15">
+        <v>1613</v>
+      </c>
+      <c r="G346" s="15">
+        <v>1402</v>
+      </c>
+      <c r="H346" s="4">
+        <v>793.9</v>
+      </c>
+      <c r="I346" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J346" s="18">
+        <v>895.4</v>
+      </c>
+      <c r="K346" s="6">
+        <v>73</v>
+      </c>
+      <c r="L346" s="7">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="M346" s="4">
+        <v>935.1</v>
+      </c>
+      <c r="N346" s="20"/>
+    </row>
+    <row r="347" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A347" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B347" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C347" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D347" s="23"/>
+      <c r="E347" s="23"/>
+      <c r="F347" s="15">
+        <v>1613</v>
+      </c>
+      <c r="G347" s="15">
+        <v>1402</v>
+      </c>
+      <c r="H347" s="4">
+        <v>793.9</v>
+      </c>
+      <c r="I347" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J347" s="18">
+        <v>895.4</v>
+      </c>
+      <c r="K347" s="6">
+        <v>12</v>
+      </c>
+      <c r="L347" s="7">
+        <v>21.49</v>
+      </c>
+      <c r="M347" s="4">
+        <v>916.89</v>
+      </c>
+      <c r="N347" s="20"/>
+    </row>
+    <row r="348" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A348" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B348" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C348" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D348" s="23"/>
+      <c r="E348" s="23"/>
+      <c r="F348" s="15">
+        <v>1572</v>
+      </c>
+      <c r="G348" s="16">
+        <v>204</v>
+      </c>
+      <c r="H348" s="5">
+        <v>1000</v>
+      </c>
+      <c r="I348" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J348" s="17">
+        <v>1144.04</v>
+      </c>
+      <c r="K348" s="6">
+        <v>27</v>
+      </c>
+      <c r="L348" s="7">
+        <v>33.18</v>
+      </c>
+      <c r="M348" s="5">
+        <v>1177.22</v>
+      </c>
+      <c r="N348" s="20"/>
+    </row>
+    <row r="349" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A349" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B349" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C349" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D349" s="23"/>
+      <c r="E349" s="23"/>
+      <c r="F349" s="15">
+        <v>1470</v>
+      </c>
+      <c r="G349" s="16">
+        <v>602</v>
+      </c>
+      <c r="H349" s="4">
+        <v>763.85</v>
+      </c>
+      <c r="I349" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J349" s="18">
+        <v>892.01</v>
+      </c>
+      <c r="K349" s="6">
+        <v>42</v>
+      </c>
+      <c r="L349" s="7">
+        <v>30.33</v>
+      </c>
+      <c r="M349" s="4">
+        <v>922.34</v>
+      </c>
+      <c r="N349" s="20"/>
+    </row>
+    <row r="350" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A350" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B350" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C350" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D350" s="23"/>
+      <c r="E350" s="23"/>
+      <c r="F350" s="15">
+        <v>1470</v>
+      </c>
+      <c r="G350" s="16">
+        <v>602</v>
+      </c>
+      <c r="H350" s="4">
+        <v>763.85</v>
+      </c>
+      <c r="I350" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J350" s="18">
+        <v>892.01</v>
+      </c>
+      <c r="K350" s="6">
+        <v>11</v>
+      </c>
+      <c r="L350" s="7">
+        <v>21.11</v>
+      </c>
+      <c r="M350" s="4">
+        <v>913.12</v>
+      </c>
+      <c r="N350" s="20"/>
+    </row>
+    <row r="351" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A351" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B351" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C351" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D351" s="23"/>
+      <c r="E351" s="23"/>
+      <c r="F351" s="15">
+        <v>1458</v>
+      </c>
+      <c r="G351" s="16">
+        <v>403</v>
+      </c>
+      <c r="H351" s="4">
+        <v>813.02</v>
+      </c>
+      <c r="I351" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J351" s="18">
+        <v>949.43</v>
+      </c>
+      <c r="K351" s="6">
+        <v>78</v>
+      </c>
+      <c r="L351" s="7">
+        <v>43.68</v>
+      </c>
+      <c r="M351" s="4">
+        <v>993.11</v>
+      </c>
+      <c r="N351" s="20"/>
+    </row>
+    <row r="352" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A352" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B352" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C352" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D352" s="23"/>
+      <c r="E352" s="23"/>
+      <c r="F352" s="15">
+        <v>1469</v>
+      </c>
+      <c r="G352" s="16">
+        <v>208</v>
+      </c>
+      <c r="H352" s="4">
+        <v>968.46</v>
+      </c>
+      <c r="I352" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J352" s="17">
+        <v>1130.95</v>
+      </c>
+      <c r="K352" s="6">
+        <v>43</v>
+      </c>
+      <c r="L352" s="7">
+        <v>38.83</v>
+      </c>
+      <c r="M352" s="5">
+        <v>1169.78</v>
+      </c>
+      <c r="N352" s="20"/>
+    </row>
+    <row r="353" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A353" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B353" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C353" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D353" s="23"/>
+      <c r="E353" s="23"/>
+      <c r="F353" s="15">
+        <v>1469</v>
+      </c>
+      <c r="G353" s="16">
+        <v>208</v>
+      </c>
+      <c r="H353" s="4">
+        <v>968.46</v>
+      </c>
+      <c r="I353" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J353" s="17">
+        <v>1130.95</v>
+      </c>
+      <c r="K353" s="6">
+        <v>12</v>
+      </c>
+      <c r="L353" s="7">
+        <v>27.14</v>
+      </c>
+      <c r="M353" s="5">
+        <v>1158.0899999999999</v>
+      </c>
+      <c r="N353" s="20"/>
+    </row>
+    <row r="354" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A354" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B354" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C354" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D354" s="23"/>
+      <c r="E354" s="23"/>
+      <c r="F354" s="15">
+        <v>1610</v>
+      </c>
+      <c r="G354" s="15">
+        <v>1003</v>
+      </c>
+      <c r="H354" s="5">
+        <v>1300</v>
+      </c>
+      <c r="I354" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J354" s="17">
+        <v>1275.72</v>
+      </c>
+      <c r="K354" s="9">
+        <v>135</v>
+      </c>
+      <c r="L354" s="7">
+        <v>82.92</v>
+      </c>
+      <c r="M354" s="5">
+        <v>1358.64</v>
+      </c>
+      <c r="N354" s="20"/>
+    </row>
+    <row r="355" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A355" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B355" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C355" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D355" s="23"/>
+      <c r="E355" s="23"/>
+      <c r="F355" s="15">
+        <v>1610</v>
+      </c>
+      <c r="G355" s="15">
+        <v>1003</v>
+      </c>
+      <c r="H355" s="5">
+        <v>1300</v>
+      </c>
+      <c r="I355" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J355" s="17">
+        <v>1466.2</v>
+      </c>
+      <c r="K355" s="9">
+        <v>107</v>
+      </c>
+      <c r="L355" s="7">
+        <v>81.61</v>
+      </c>
+      <c r="M355" s="5">
+        <v>1547.81</v>
+      </c>
+      <c r="N355" s="20"/>
+    </row>
+    <row r="356" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A356" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B356" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="C356" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D356" s="23"/>
+      <c r="E356" s="23"/>
+      <c r="F356" s="15">
+        <v>1610</v>
+      </c>
+      <c r="G356" s="15">
+        <v>1003</v>
+      </c>
+      <c r="H356" s="5">
+        <v>1300</v>
+      </c>
+      <c r="I356" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J356" s="17">
+        <v>1466.2</v>
+      </c>
+      <c r="K356" s="6">
+        <v>46</v>
+      </c>
+      <c r="L356" s="7">
+        <v>51.8</v>
+      </c>
+      <c r="M356" s="5">
+        <v>1518</v>
+      </c>
+      <c r="N356" s="20"/>
+    </row>
+    <row r="357" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A357" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B357" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C357" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D357" s="23"/>
+      <c r="E357" s="23"/>
+      <c r="F357" s="15">
+        <v>1610</v>
+      </c>
+      <c r="G357" s="15">
+        <v>1003</v>
+      </c>
+      <c r="H357" s="5">
+        <v>2830.4</v>
+      </c>
+      <c r="I357" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J357" s="17">
+        <v>3192.27</v>
+      </c>
+      <c r="K357" s="6">
+        <v>15</v>
+      </c>
+      <c r="L357" s="7">
+        <v>79.81</v>
+      </c>
+      <c r="M357" s="5">
+        <v>3272.08</v>
+      </c>
+      <c r="N357" s="20"/>
+    </row>
+    <row r="358" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A358" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B358" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C358" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D358" s="23"/>
+      <c r="E358" s="23"/>
+      <c r="F358" s="15">
+        <v>1610</v>
+      </c>
+      <c r="G358" s="15">
+        <v>1003</v>
+      </c>
+      <c r="H358" s="5">
+        <v>1300</v>
+      </c>
+      <c r="I358" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J358" s="17">
+        <v>1466.2</v>
+      </c>
+      <c r="K358" s="6">
+        <v>15</v>
+      </c>
+      <c r="L358" s="7">
+        <v>36.65</v>
+      </c>
+      <c r="M358" s="5">
+        <v>1502.85</v>
+      </c>
+      <c r="N358" s="20"/>
+    </row>
+    <row r="359" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A359" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B359" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C359" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="D359" s="23"/>
+      <c r="E359" s="23"/>
+      <c r="F359" s="15">
+        <v>1419</v>
+      </c>
+      <c r="G359" s="16">
+        <v>607</v>
+      </c>
+      <c r="H359" s="5">
+        <v>1116.46</v>
+      </c>
+      <c r="I359" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J359" s="17">
+        <v>1307.82</v>
+      </c>
+      <c r="K359" s="6">
+        <v>17</v>
+      </c>
+      <c r="L359" s="7">
+        <v>33.57</v>
+      </c>
+      <c r="M359" s="5">
+        <v>1341.39</v>
+      </c>
+      <c r="N359" s="20"/>
+    </row>
+    <row r="360" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A360" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B360" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C360" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D360" s="23"/>
+      <c r="E360" s="23"/>
+      <c r="F360" s="15">
+        <v>1499</v>
+      </c>
+      <c r="G360" s="16">
+        <v>606</v>
+      </c>
+      <c r="H360" s="5">
+        <v>1200</v>
+      </c>
+      <c r="I360" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J360" s="17">
+        <v>1397.56</v>
+      </c>
+      <c r="K360" s="6">
+        <v>58</v>
+      </c>
+      <c r="L360" s="7">
+        <v>54.97</v>
+      </c>
+      <c r="M360" s="5">
+        <v>1452.53</v>
+      </c>
+      <c r="N360" s="20"/>
+    </row>
+    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A361" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B361" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C361" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D361" s="23"/>
+      <c r="E361" s="23"/>
+      <c r="F361" s="15">
+        <v>1499</v>
+      </c>
+      <c r="G361" s="16">
+        <v>606</v>
+      </c>
+      <c r="H361" s="5">
+        <v>1200</v>
+      </c>
+      <c r="I361" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J361" s="17">
+        <v>1397.56</v>
+      </c>
+      <c r="K361" s="6">
+        <v>27</v>
+      </c>
+      <c r="L361" s="7">
+        <v>40.53</v>
+      </c>
+      <c r="M361" s="5">
+        <v>1438.09</v>
+      </c>
+      <c r="N361" s="20"/>
+    </row>
+    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A362" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B362" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C362" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="D362" s="23"/>
+      <c r="E362" s="23"/>
+      <c r="F362" s="15">
+        <v>1559</v>
+      </c>
+      <c r="G362" s="16">
+        <v>203</v>
+      </c>
+      <c r="H362" s="5">
+        <v>1500</v>
+      </c>
+      <c r="I362" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J362" s="17">
+        <v>1730.81</v>
+      </c>
+      <c r="K362" s="6">
+        <v>12</v>
+      </c>
+      <c r="L362" s="7">
+        <v>41.54</v>
+      </c>
+      <c r="M362" s="5">
+        <v>1772.35</v>
+      </c>
+      <c r="N362" s="20"/>
+    </row>
+    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A363" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B363" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C363" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D363" s="23"/>
+      <c r="E363" s="23"/>
+      <c r="F363" s="15">
+        <v>1457</v>
+      </c>
+      <c r="G363" s="16">
+        <v>507</v>
+      </c>
+      <c r="H363" s="4">
+        <v>632.9</v>
+      </c>
+      <c r="I363" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J363" s="18">
+        <v>739.09</v>
+      </c>
+      <c r="K363" s="6">
+        <v>12</v>
+      </c>
+      <c r="L363" s="7">
+        <v>17.739999999999998</v>
+      </c>
+      <c r="M363" s="4">
+        <v>756.83</v>
+      </c>
+      <c r="N363" s="20"/>
+    </row>
+    <row r="364" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A364" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B364" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C364" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D364" s="23"/>
+      <c r="E364" s="23"/>
+      <c r="F364" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G364" s="16">
+        <v>506</v>
+      </c>
+      <c r="H364" s="4">
+        <v>688.62</v>
+      </c>
+      <c r="I364" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J364" s="18">
+        <v>800.95</v>
+      </c>
+      <c r="K364" s="9">
+        <v>204</v>
+      </c>
+      <c r="L364" s="7">
+        <v>70.48</v>
+      </c>
+      <c r="M364" s="4">
+        <v>871.43</v>
+      </c>
+      <c r="N364" s="20"/>
+    </row>
+    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A365" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B365" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C365" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D365" s="23"/>
+      <c r="E365" s="23"/>
+      <c r="F365" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G365" s="16">
+        <v>506</v>
+      </c>
+      <c r="H365" s="5">
+        <v>4340.6400000000003</v>
+      </c>
+      <c r="I365" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J365" s="17">
+        <v>5048.6899999999996</v>
+      </c>
+      <c r="K365" s="9">
+        <v>184</v>
+      </c>
+      <c r="L365" s="4">
+        <v>410.62</v>
+      </c>
+      <c r="M365" s="5">
+        <v>5459.31</v>
+      </c>
+      <c r="N365" s="20"/>
+    </row>
+    <row r="366" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A366" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B366" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C366" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D366" s="23"/>
+      <c r="E366" s="23"/>
+      <c r="F366" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G366" s="16">
+        <v>506</v>
+      </c>
+      <c r="H366" s="4">
+        <v>688.62</v>
+      </c>
+      <c r="I366" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J366" s="18">
+        <v>800.95</v>
+      </c>
+      <c r="K366" s="9">
+        <v>173</v>
+      </c>
+      <c r="L366" s="7">
+        <v>62.21</v>
+      </c>
+      <c r="M366" s="4">
+        <v>863.16</v>
+      </c>
+      <c r="N366" s="20"/>
+    </row>
+    <row r="367" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A367" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B367" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C367" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D367" s="23"/>
+      <c r="E367" s="23"/>
+      <c r="F367" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G367" s="16">
+        <v>506</v>
+      </c>
+      <c r="H367" s="4">
+        <v>688.62</v>
+      </c>
+      <c r="I367" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J367" s="18">
+        <v>800.95</v>
+      </c>
+      <c r="K367" s="9">
+        <v>142</v>
+      </c>
+      <c r="L367" s="7">
+        <v>53.93</v>
+      </c>
+      <c r="M367" s="4">
+        <v>854.88</v>
+      </c>
+      <c r="N367" s="20"/>
+    </row>
+    <row r="368" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A368" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B368" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C368" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D368" s="23"/>
+      <c r="E368" s="23"/>
+      <c r="F368" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G368" s="16">
+        <v>506</v>
+      </c>
+      <c r="H368" s="4">
+        <v>688.62</v>
+      </c>
+      <c r="I368" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J368" s="18">
+        <v>800.95</v>
+      </c>
+      <c r="K368" s="9">
+        <v>114</v>
+      </c>
+      <c r="L368" s="7">
+        <v>46.46</v>
+      </c>
+      <c r="M368" s="4">
+        <v>847.41</v>
+      </c>
+      <c r="N368" s="20"/>
+    </row>
+    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A369" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B369" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C369" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D369" s="23"/>
+      <c r="E369" s="23"/>
+      <c r="F369" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G369" s="16">
+        <v>506</v>
+      </c>
+      <c r="H369" s="4">
+        <v>688.62</v>
+      </c>
+      <c r="I369" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J369" s="18">
+        <v>800.95</v>
+      </c>
+      <c r="K369" s="6">
+        <v>83</v>
+      </c>
+      <c r="L369" s="7">
+        <v>38.18</v>
+      </c>
+      <c r="M369" s="4">
+        <v>839.13</v>
+      </c>
+      <c r="N369" s="20"/>
+    </row>
+    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A370" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B370" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C370" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D370" s="23"/>
+      <c r="E370" s="23"/>
+      <c r="F370" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G370" s="16">
+        <v>506</v>
+      </c>
+      <c r="H370" s="4">
+        <v>688.62</v>
+      </c>
+      <c r="I370" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J370" s="18">
+        <v>800.95</v>
+      </c>
+      <c r="K370" s="6">
+        <v>53</v>
+      </c>
+      <c r="L370" s="7">
+        <v>30.17</v>
+      </c>
+      <c r="M370" s="4">
+        <v>831.12</v>
+      </c>
+      <c r="N370" s="20"/>
+    </row>
+    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A371" s="14">
+        <v>46174</v>
+      </c>
+      <c r="B371" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C371" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D371" s="23"/>
+      <c r="E371" s="23"/>
+      <c r="F371" s="15">
+        <v>1533</v>
+      </c>
+      <c r="G371" s="16">
+        <v>506</v>
+      </c>
+      <c r="H371" s="4">
+        <v>688.62</v>
+      </c>
+      <c r="I371" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J371" s="18">
+        <v>800.95</v>
+      </c>
+      <c r="K371" s="6">
+        <v>22</v>
+      </c>
+      <c r="L371" s="7">
+        <v>21.89</v>
+      </c>
+      <c r="M371" s="4">
+        <v>822.84</v>
+      </c>
+      <c r="N371" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="342">
-    <mergeCell ref="C340:E340"/>
-    <mergeCell ref="C341:E341"/>
-    <mergeCell ref="C342:E342"/>
-    <mergeCell ref="C337:E337"/>
-    <mergeCell ref="C338:E338"/>
-    <mergeCell ref="C339:E339"/>
-    <mergeCell ref="C334:E334"/>
-    <mergeCell ref="C335:E335"/>
-    <mergeCell ref="C336:E336"/>
-    <mergeCell ref="C331:E331"/>
-    <mergeCell ref="C332:E332"/>
-    <mergeCell ref="C333:E333"/>
-    <mergeCell ref="C328:E328"/>
-    <mergeCell ref="C329:E329"/>
-    <mergeCell ref="C330:E330"/>
-    <mergeCell ref="C325:E325"/>
-    <mergeCell ref="C326:E326"/>
-    <mergeCell ref="C327:E327"/>
-    <mergeCell ref="C322:E322"/>
-    <mergeCell ref="C323:E323"/>
-    <mergeCell ref="C324:E324"/>
-    <mergeCell ref="C319:E319"/>
-    <mergeCell ref="C320:E320"/>
-    <mergeCell ref="C321:E321"/>
-    <mergeCell ref="C316:E316"/>
-    <mergeCell ref="C317:E317"/>
-    <mergeCell ref="C318:E318"/>
-    <mergeCell ref="C127:E127"/>
-    <mergeCell ref="C128:E128"/>
-    <mergeCell ref="C129:E129"/>
-    <mergeCell ref="C130:E130"/>
-    <mergeCell ref="C131:E131"/>
-    <mergeCell ref="C132:E132"/>
-    <mergeCell ref="C142:E142"/>
-    <mergeCell ref="C133:E133"/>
-    <mergeCell ref="C134:E134"/>
-    <mergeCell ref="C135:E135"/>
-    <mergeCell ref="C136:E136"/>
-    <mergeCell ref="C137:E137"/>
-    <mergeCell ref="C138:E138"/>
-    <mergeCell ref="C139:E139"/>
-    <mergeCell ref="C140:E140"/>
-    <mergeCell ref="C141:E141"/>
+  <mergeCells count="371">
+    <mergeCell ref="C370:E370"/>
+    <mergeCell ref="C371:E371"/>
+    <mergeCell ref="C367:E367"/>
+    <mergeCell ref="C368:E368"/>
+    <mergeCell ref="C369:E369"/>
+    <mergeCell ref="C364:E364"/>
+    <mergeCell ref="C365:E365"/>
+    <mergeCell ref="C366:E366"/>
+    <mergeCell ref="C361:E361"/>
+    <mergeCell ref="C362:E362"/>
+    <mergeCell ref="C363:E363"/>
+    <mergeCell ref="C358:E358"/>
+    <mergeCell ref="C359:E359"/>
+    <mergeCell ref="C360:E360"/>
+    <mergeCell ref="C355:E355"/>
+    <mergeCell ref="C356:E356"/>
+    <mergeCell ref="C357:E357"/>
+    <mergeCell ref="C352:E352"/>
+    <mergeCell ref="C353:E353"/>
+    <mergeCell ref="C354:E354"/>
+    <mergeCell ref="C349:E349"/>
+    <mergeCell ref="C350:E350"/>
+    <mergeCell ref="C351:E351"/>
+    <mergeCell ref="C346:E346"/>
+    <mergeCell ref="C347:E347"/>
+    <mergeCell ref="C348:E348"/>
+    <mergeCell ref="C343:E343"/>
+    <mergeCell ref="C344:E344"/>
+    <mergeCell ref="C345:E345"/>
+    <mergeCell ref="C291:E291"/>
+    <mergeCell ref="C292:E292"/>
+    <mergeCell ref="C293:E293"/>
+    <mergeCell ref="C294:E294"/>
+    <mergeCell ref="C295:E295"/>
+    <mergeCell ref="C314:E314"/>
+    <mergeCell ref="C315:E315"/>
+    <mergeCell ref="C296:E296"/>
+    <mergeCell ref="C297:E297"/>
+    <mergeCell ref="C298:E298"/>
+    <mergeCell ref="C299:E299"/>
+    <mergeCell ref="C300:E300"/>
+    <mergeCell ref="C301:E301"/>
+    <mergeCell ref="C302:E302"/>
+    <mergeCell ref="C303:E303"/>
+    <mergeCell ref="C304:E304"/>
+    <mergeCell ref="C305:E305"/>
+    <mergeCell ref="C306:E306"/>
+    <mergeCell ref="C307:E307"/>
+    <mergeCell ref="C308:E308"/>
+    <mergeCell ref="C309:E309"/>
+    <mergeCell ref="C310:E310"/>
+    <mergeCell ref="C311:E311"/>
+    <mergeCell ref="C312:E312"/>
+    <mergeCell ref="C313:E313"/>
+    <mergeCell ref="C287:E287"/>
+    <mergeCell ref="C288:E288"/>
+    <mergeCell ref="C289:E289"/>
+    <mergeCell ref="C290:E290"/>
+    <mergeCell ref="C278:E278"/>
+    <mergeCell ref="C279:E279"/>
+    <mergeCell ref="C280:E280"/>
+    <mergeCell ref="C281:E281"/>
+    <mergeCell ref="C282:E282"/>
+    <mergeCell ref="C283:E283"/>
+    <mergeCell ref="C284:E284"/>
+    <mergeCell ref="C285:E285"/>
+    <mergeCell ref="C286:E286"/>
+    <mergeCell ref="C269:E269"/>
+    <mergeCell ref="C270:E270"/>
+    <mergeCell ref="C271:E271"/>
+    <mergeCell ref="C272:E272"/>
+    <mergeCell ref="C273:E273"/>
+    <mergeCell ref="C274:E274"/>
+    <mergeCell ref="C275:E275"/>
+    <mergeCell ref="C276:E276"/>
+    <mergeCell ref="C277:E277"/>
+    <mergeCell ref="C260:E260"/>
+    <mergeCell ref="C261:E261"/>
+    <mergeCell ref="C262:E262"/>
+    <mergeCell ref="C263:E263"/>
+    <mergeCell ref="C264:E264"/>
+    <mergeCell ref="C265:E265"/>
+    <mergeCell ref="C266:E266"/>
+    <mergeCell ref="C267:E267"/>
+    <mergeCell ref="C268:E268"/>
+    <mergeCell ref="C251:E251"/>
+    <mergeCell ref="C252:E252"/>
+    <mergeCell ref="C253:E253"/>
+    <mergeCell ref="C254:E254"/>
+    <mergeCell ref="C255:E255"/>
+    <mergeCell ref="C256:E256"/>
+    <mergeCell ref="C257:E257"/>
+    <mergeCell ref="C258:E258"/>
+    <mergeCell ref="C259:E259"/>
+    <mergeCell ref="C242:E242"/>
+    <mergeCell ref="C243:E243"/>
+    <mergeCell ref="C244:E244"/>
+    <mergeCell ref="C245:E245"/>
+    <mergeCell ref="C246:E246"/>
+    <mergeCell ref="C247:E247"/>
+    <mergeCell ref="C248:E248"/>
+    <mergeCell ref="C249:E249"/>
+    <mergeCell ref="C250:E250"/>
+    <mergeCell ref="C233:E233"/>
+    <mergeCell ref="C234:E234"/>
+    <mergeCell ref="C235:E235"/>
+    <mergeCell ref="C236:E236"/>
+    <mergeCell ref="C237:E237"/>
+    <mergeCell ref="C238:E238"/>
+    <mergeCell ref="C239:E239"/>
+    <mergeCell ref="C240:E240"/>
+    <mergeCell ref="C241:E241"/>
+    <mergeCell ref="C224:E224"/>
+    <mergeCell ref="C225:E225"/>
+    <mergeCell ref="C226:E226"/>
+    <mergeCell ref="C227:E227"/>
+    <mergeCell ref="C228:E228"/>
+    <mergeCell ref="C229:E229"/>
+    <mergeCell ref="C230:E230"/>
+    <mergeCell ref="C231:E231"/>
+    <mergeCell ref="C232:E232"/>
+    <mergeCell ref="C215:E215"/>
+    <mergeCell ref="C216:E216"/>
+    <mergeCell ref="C217:E217"/>
+    <mergeCell ref="C218:E218"/>
+    <mergeCell ref="C219:E219"/>
+    <mergeCell ref="C220:E220"/>
+    <mergeCell ref="C221:E221"/>
+    <mergeCell ref="C222:E222"/>
+    <mergeCell ref="C223:E223"/>
+    <mergeCell ref="C206:E206"/>
+    <mergeCell ref="C207:E207"/>
+    <mergeCell ref="C208:E208"/>
+    <mergeCell ref="C209:E209"/>
+    <mergeCell ref="C210:E210"/>
+    <mergeCell ref="C211:E211"/>
+    <mergeCell ref="C212:E212"/>
+    <mergeCell ref="C213:E213"/>
+    <mergeCell ref="C214:E214"/>
+    <mergeCell ref="C197:E197"/>
+    <mergeCell ref="C198:E198"/>
+    <mergeCell ref="C199:E199"/>
+    <mergeCell ref="C200:E200"/>
+    <mergeCell ref="C201:E201"/>
+    <mergeCell ref="C202:E202"/>
+    <mergeCell ref="C203:E203"/>
+    <mergeCell ref="C204:E204"/>
+    <mergeCell ref="C205:E205"/>
+    <mergeCell ref="C188:E188"/>
+    <mergeCell ref="C189:E189"/>
+    <mergeCell ref="C190:E190"/>
+    <mergeCell ref="C191:E191"/>
+    <mergeCell ref="C192:E192"/>
+    <mergeCell ref="C193:E193"/>
+    <mergeCell ref="C194:E194"/>
+    <mergeCell ref="C195:E195"/>
+    <mergeCell ref="C196:E196"/>
+    <mergeCell ref="C179:E179"/>
+    <mergeCell ref="C180:E180"/>
+    <mergeCell ref="C181:E181"/>
+    <mergeCell ref="C182:E182"/>
+    <mergeCell ref="C183:E183"/>
+    <mergeCell ref="C184:E184"/>
+    <mergeCell ref="C185:E185"/>
+    <mergeCell ref="C186:E186"/>
+    <mergeCell ref="C187:E187"/>
+    <mergeCell ref="C170:E170"/>
+    <mergeCell ref="C171:E171"/>
+    <mergeCell ref="C172:E172"/>
+    <mergeCell ref="C173:E173"/>
+    <mergeCell ref="C174:E174"/>
+    <mergeCell ref="C175:E175"/>
+    <mergeCell ref="C176:E176"/>
+    <mergeCell ref="C177:E177"/>
+    <mergeCell ref="C178:E178"/>
+    <mergeCell ref="C161:E161"/>
+    <mergeCell ref="C162:E162"/>
+    <mergeCell ref="C163:E163"/>
+    <mergeCell ref="C164:E164"/>
+    <mergeCell ref="C165:E165"/>
+    <mergeCell ref="C166:E166"/>
+    <mergeCell ref="C167:E167"/>
+    <mergeCell ref="C168:E168"/>
+    <mergeCell ref="C169:E169"/>
+    <mergeCell ref="C152:E152"/>
+    <mergeCell ref="C153:E153"/>
+    <mergeCell ref="C154:E154"/>
+    <mergeCell ref="C155:E155"/>
+    <mergeCell ref="C156:E156"/>
+    <mergeCell ref="C157:E157"/>
+    <mergeCell ref="C158:E158"/>
+    <mergeCell ref="C159:E159"/>
+    <mergeCell ref="C160:E160"/>
+    <mergeCell ref="C143:E143"/>
+    <mergeCell ref="C144:E144"/>
+    <mergeCell ref="C145:E145"/>
+    <mergeCell ref="C146:E146"/>
+    <mergeCell ref="C147:E147"/>
+    <mergeCell ref="C148:E148"/>
+    <mergeCell ref="C149:E149"/>
+    <mergeCell ref="C150:E150"/>
+    <mergeCell ref="C151:E151"/>
+    <mergeCell ref="C122:E122"/>
+    <mergeCell ref="C123:E123"/>
+    <mergeCell ref="C117:E117"/>
+    <mergeCell ref="C118:E118"/>
+    <mergeCell ref="C119:E119"/>
+    <mergeCell ref="C120:E120"/>
+    <mergeCell ref="C121:E121"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="C113:E113"/>
+    <mergeCell ref="C114:E114"/>
+    <mergeCell ref="C115:E115"/>
+    <mergeCell ref="C116:E116"/>
+    <mergeCell ref="C107:E107"/>
+    <mergeCell ref="C108:E108"/>
+    <mergeCell ref="C109:E109"/>
+    <mergeCell ref="C110:E110"/>
+    <mergeCell ref="C111:E111"/>
+    <mergeCell ref="C102:E102"/>
+    <mergeCell ref="C103:E103"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="C105:E105"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="C100:E100"/>
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="C13:E13"/>
@@ -13947,281 +15259,49 @@
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="C98:E98"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="C100:E100"/>
-    <mergeCell ref="C101:E101"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="C88:E88"/>
-    <mergeCell ref="C89:E89"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="C94:E94"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="C107:E107"/>
-    <mergeCell ref="C108:E108"/>
-    <mergeCell ref="C109:E109"/>
-    <mergeCell ref="C110:E110"/>
-    <mergeCell ref="C111:E111"/>
-    <mergeCell ref="C102:E102"/>
-    <mergeCell ref="C103:E103"/>
-    <mergeCell ref="C104:E104"/>
-    <mergeCell ref="C105:E105"/>
-    <mergeCell ref="C106:E106"/>
-    <mergeCell ref="C122:E122"/>
-    <mergeCell ref="C123:E123"/>
-    <mergeCell ref="C117:E117"/>
-    <mergeCell ref="C118:E118"/>
-    <mergeCell ref="C119:E119"/>
-    <mergeCell ref="C120:E120"/>
-    <mergeCell ref="C121:E121"/>
-    <mergeCell ref="C112:E112"/>
-    <mergeCell ref="C113:E113"/>
-    <mergeCell ref="C114:E114"/>
-    <mergeCell ref="C115:E115"/>
-    <mergeCell ref="C116:E116"/>
-    <mergeCell ref="C143:E143"/>
-    <mergeCell ref="C144:E144"/>
-    <mergeCell ref="C145:E145"/>
-    <mergeCell ref="C146:E146"/>
-    <mergeCell ref="C147:E147"/>
-    <mergeCell ref="C148:E148"/>
-    <mergeCell ref="C149:E149"/>
-    <mergeCell ref="C150:E150"/>
-    <mergeCell ref="C151:E151"/>
-    <mergeCell ref="C152:E152"/>
-    <mergeCell ref="C153:E153"/>
-    <mergeCell ref="C154:E154"/>
-    <mergeCell ref="C155:E155"/>
-    <mergeCell ref="C156:E156"/>
-    <mergeCell ref="C157:E157"/>
-    <mergeCell ref="C158:E158"/>
-    <mergeCell ref="C159:E159"/>
-    <mergeCell ref="C160:E160"/>
-    <mergeCell ref="C161:E161"/>
-    <mergeCell ref="C162:E162"/>
-    <mergeCell ref="C163:E163"/>
-    <mergeCell ref="C164:E164"/>
-    <mergeCell ref="C165:E165"/>
-    <mergeCell ref="C166:E166"/>
-    <mergeCell ref="C167:E167"/>
-    <mergeCell ref="C168:E168"/>
-    <mergeCell ref="C169:E169"/>
-    <mergeCell ref="C170:E170"/>
-    <mergeCell ref="C171:E171"/>
-    <mergeCell ref="C172:E172"/>
-    <mergeCell ref="C173:E173"/>
-    <mergeCell ref="C174:E174"/>
-    <mergeCell ref="C175:E175"/>
-    <mergeCell ref="C176:E176"/>
-    <mergeCell ref="C177:E177"/>
-    <mergeCell ref="C178:E178"/>
-    <mergeCell ref="C179:E179"/>
-    <mergeCell ref="C180:E180"/>
-    <mergeCell ref="C181:E181"/>
-    <mergeCell ref="C182:E182"/>
-    <mergeCell ref="C183:E183"/>
-    <mergeCell ref="C184:E184"/>
-    <mergeCell ref="C185:E185"/>
-    <mergeCell ref="C186:E186"/>
-    <mergeCell ref="C187:E187"/>
-    <mergeCell ref="C188:E188"/>
-    <mergeCell ref="C189:E189"/>
-    <mergeCell ref="C190:E190"/>
-    <mergeCell ref="C191:E191"/>
-    <mergeCell ref="C192:E192"/>
-    <mergeCell ref="C193:E193"/>
-    <mergeCell ref="C194:E194"/>
-    <mergeCell ref="C195:E195"/>
-    <mergeCell ref="C196:E196"/>
-    <mergeCell ref="C197:E197"/>
-    <mergeCell ref="C198:E198"/>
-    <mergeCell ref="C199:E199"/>
-    <mergeCell ref="C200:E200"/>
-    <mergeCell ref="C201:E201"/>
-    <mergeCell ref="C202:E202"/>
-    <mergeCell ref="C203:E203"/>
-    <mergeCell ref="C204:E204"/>
-    <mergeCell ref="C205:E205"/>
-    <mergeCell ref="C206:E206"/>
-    <mergeCell ref="C207:E207"/>
-    <mergeCell ref="C208:E208"/>
-    <mergeCell ref="C209:E209"/>
-    <mergeCell ref="C210:E210"/>
-    <mergeCell ref="C211:E211"/>
-    <mergeCell ref="C212:E212"/>
-    <mergeCell ref="C213:E213"/>
-    <mergeCell ref="C214:E214"/>
-    <mergeCell ref="C215:E215"/>
-    <mergeCell ref="C216:E216"/>
-    <mergeCell ref="C217:E217"/>
-    <mergeCell ref="C218:E218"/>
-    <mergeCell ref="C219:E219"/>
-    <mergeCell ref="C220:E220"/>
-    <mergeCell ref="C221:E221"/>
-    <mergeCell ref="C222:E222"/>
-    <mergeCell ref="C223:E223"/>
-    <mergeCell ref="C224:E224"/>
-    <mergeCell ref="C225:E225"/>
-    <mergeCell ref="C226:E226"/>
-    <mergeCell ref="C227:E227"/>
-    <mergeCell ref="C228:E228"/>
-    <mergeCell ref="C229:E229"/>
-    <mergeCell ref="C230:E230"/>
-    <mergeCell ref="C231:E231"/>
-    <mergeCell ref="C232:E232"/>
-    <mergeCell ref="C233:E233"/>
-    <mergeCell ref="C234:E234"/>
-    <mergeCell ref="C235:E235"/>
-    <mergeCell ref="C236:E236"/>
-    <mergeCell ref="C237:E237"/>
-    <mergeCell ref="C238:E238"/>
-    <mergeCell ref="C239:E239"/>
-    <mergeCell ref="C240:E240"/>
-    <mergeCell ref="C241:E241"/>
-    <mergeCell ref="C242:E242"/>
-    <mergeCell ref="C243:E243"/>
-    <mergeCell ref="C244:E244"/>
-    <mergeCell ref="C245:E245"/>
-    <mergeCell ref="C246:E246"/>
-    <mergeCell ref="C247:E247"/>
-    <mergeCell ref="C248:E248"/>
-    <mergeCell ref="C249:E249"/>
-    <mergeCell ref="C250:E250"/>
-    <mergeCell ref="C251:E251"/>
-    <mergeCell ref="C252:E252"/>
-    <mergeCell ref="C253:E253"/>
-    <mergeCell ref="C254:E254"/>
-    <mergeCell ref="C255:E255"/>
-    <mergeCell ref="C256:E256"/>
-    <mergeCell ref="C257:E257"/>
-    <mergeCell ref="C258:E258"/>
-    <mergeCell ref="C259:E259"/>
-    <mergeCell ref="C260:E260"/>
-    <mergeCell ref="C261:E261"/>
-    <mergeCell ref="C262:E262"/>
-    <mergeCell ref="C263:E263"/>
-    <mergeCell ref="C264:E264"/>
-    <mergeCell ref="C265:E265"/>
-    <mergeCell ref="C266:E266"/>
-    <mergeCell ref="C267:E267"/>
-    <mergeCell ref="C268:E268"/>
-    <mergeCell ref="C269:E269"/>
-    <mergeCell ref="C270:E270"/>
-    <mergeCell ref="C271:E271"/>
-    <mergeCell ref="C272:E272"/>
-    <mergeCell ref="C273:E273"/>
-    <mergeCell ref="C274:E274"/>
-    <mergeCell ref="C275:E275"/>
-    <mergeCell ref="C276:E276"/>
-    <mergeCell ref="C277:E277"/>
-    <mergeCell ref="C287:E287"/>
-    <mergeCell ref="C288:E288"/>
-    <mergeCell ref="C289:E289"/>
-    <mergeCell ref="C290:E290"/>
-    <mergeCell ref="C278:E278"/>
-    <mergeCell ref="C279:E279"/>
-    <mergeCell ref="C280:E280"/>
-    <mergeCell ref="C281:E281"/>
-    <mergeCell ref="C282:E282"/>
-    <mergeCell ref="C283:E283"/>
-    <mergeCell ref="C284:E284"/>
-    <mergeCell ref="C285:E285"/>
-    <mergeCell ref="C286:E286"/>
-    <mergeCell ref="C305:E305"/>
-    <mergeCell ref="C306:E306"/>
-    <mergeCell ref="C307:E307"/>
-    <mergeCell ref="C308:E308"/>
-    <mergeCell ref="C309:E309"/>
-    <mergeCell ref="C310:E310"/>
-    <mergeCell ref="C311:E311"/>
-    <mergeCell ref="C312:E312"/>
-    <mergeCell ref="C313:E313"/>
-    <mergeCell ref="C291:E291"/>
-    <mergeCell ref="C292:E292"/>
-    <mergeCell ref="C293:E293"/>
-    <mergeCell ref="C294:E294"/>
-    <mergeCell ref="C295:E295"/>
-    <mergeCell ref="C314:E314"/>
-    <mergeCell ref="C315:E315"/>
-    <mergeCell ref="C296:E296"/>
-    <mergeCell ref="C297:E297"/>
-    <mergeCell ref="C298:E298"/>
-    <mergeCell ref="C299:E299"/>
-    <mergeCell ref="C300:E300"/>
-    <mergeCell ref="C301:E301"/>
-    <mergeCell ref="C302:E302"/>
-    <mergeCell ref="C303:E303"/>
-    <mergeCell ref="C304:E304"/>
+    <mergeCell ref="C127:E127"/>
+    <mergeCell ref="C128:E128"/>
+    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="C130:E130"/>
+    <mergeCell ref="C131:E131"/>
+    <mergeCell ref="C132:E132"/>
+    <mergeCell ref="C142:E142"/>
+    <mergeCell ref="C133:E133"/>
+    <mergeCell ref="C134:E134"/>
+    <mergeCell ref="C135:E135"/>
+    <mergeCell ref="C136:E136"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="C138:E138"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="C141:E141"/>
+    <mergeCell ref="C322:E322"/>
+    <mergeCell ref="C323:E323"/>
+    <mergeCell ref="C324:E324"/>
+    <mergeCell ref="C319:E319"/>
+    <mergeCell ref="C320:E320"/>
+    <mergeCell ref="C321:E321"/>
+    <mergeCell ref="C316:E316"/>
+    <mergeCell ref="C317:E317"/>
+    <mergeCell ref="C318:E318"/>
+    <mergeCell ref="C331:E331"/>
+    <mergeCell ref="C332:E332"/>
+    <mergeCell ref="C333:E333"/>
+    <mergeCell ref="C328:E328"/>
+    <mergeCell ref="C329:E329"/>
+    <mergeCell ref="C330:E330"/>
+    <mergeCell ref="C325:E325"/>
+    <mergeCell ref="C326:E326"/>
+    <mergeCell ref="C327:E327"/>
+    <mergeCell ref="C340:E340"/>
+    <mergeCell ref="C341:E341"/>
+    <mergeCell ref="C342:E342"/>
+    <mergeCell ref="C337:E337"/>
+    <mergeCell ref="C338:E338"/>
+    <mergeCell ref="C339:E339"/>
+    <mergeCell ref="C334:E334"/>
+    <mergeCell ref="C335:E335"/>
+    <mergeCell ref="C336:E336"/>
   </mergeCells>
   <pageMargins left="0.52999994886203072" right="0.52999994886203072" top="0.52999994886203072" bottom="0.68999998212799307" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/data/vendas-inadimplentes.xlsx
+++ b/data/vendas-inadimplentes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC736CB6-4F90-4F10-BA6B-087E5EEE6AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233F33A0-1B6F-4A3C-B62B-BC80376C2C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="180">
   <si>
     <t>Data vecto</t>
   </si>
@@ -537,6 +537,42 @@
   </si>
   <si>
     <t>10/06/2026</t>
+  </si>
+  <si>
+    <t>01/06/2026</t>
+  </si>
+  <si>
+    <t>05/07/2026</t>
+  </si>
+  <si>
+    <t>10/07/2026</t>
+  </si>
+  <si>
+    <t>OZEIAS VIEIRA DOS SANTOS (444)</t>
+  </si>
+  <si>
+    <t>17/07/2026</t>
+  </si>
+  <si>
+    <t>20/07/2026</t>
+  </si>
+  <si>
+    <t>27/07/2026</t>
+  </si>
+  <si>
+    <t>30/07/2026</t>
+  </si>
+  <si>
+    <t>JOSE ALVES DE OLIVEIRA JUNIOR (431)</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO DE OLIVEIRA BARBOSA SOUZA (449)</t>
+  </si>
+  <si>
+    <t>01/08/2026</t>
+  </si>
+  <si>
+    <t>ZANDERSON LUCAS ROSA LINO (438)</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1116,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N371"/>
+  <dimension ref="A1:AE399"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -14815,7 +14851,7 @@
       </c>
       <c r="N368" s="20"/>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A369" s="14">
         <v>46174</v>
       </c>
@@ -14853,7 +14889,7 @@
       </c>
       <c r="N369" s="20"/>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A370" s="14">
         <v>46174</v>
       </c>
@@ -14891,7 +14927,7 @@
       </c>
       <c r="N370" s="20"/>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A371" s="14">
         <v>46174</v>
       </c>
@@ -14929,37 +14965,1394 @@
       </c>
       <c r="N371" s="20"/>
     </row>
+    <row r="372" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A372" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B372" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C372" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D372" s="23"/>
+      <c r="E372" s="23"/>
+      <c r="F372" s="15">
+        <v>1450</v>
+      </c>
+      <c r="G372" s="16">
+        <v>508</v>
+      </c>
+      <c r="H372" s="4">
+        <v>3515.6</v>
+      </c>
+      <c r="I372" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J372" s="18">
+        <v>4137.47</v>
+      </c>
+      <c r="K372" s="6">
+        <v>218</v>
+      </c>
+      <c r="L372" s="7">
+        <v>383.41</v>
+      </c>
+      <c r="M372" s="4">
+        <v>4520.88</v>
+      </c>
+      <c r="N372" s="20"/>
+    </row>
+    <row r="373" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A373" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B373" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C373" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D373" s="23"/>
+      <c r="E373" s="23"/>
+      <c r="F373" s="15">
+        <v>1508</v>
+      </c>
+      <c r="G373" s="16">
+        <v>1306</v>
+      </c>
+      <c r="H373" s="4">
+        <v>565.54999999999995</v>
+      </c>
+      <c r="I373" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J373" s="18">
+        <v>603.88</v>
+      </c>
+      <c r="K373" s="6">
+        <v>169</v>
+      </c>
+      <c r="L373" s="7">
+        <v>46.1</v>
+      </c>
+      <c r="M373" s="4">
+        <v>649.98</v>
+      </c>
+      <c r="N373" s="20"/>
+    </row>
+    <row r="374" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A374" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B374" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C374" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D374" s="23"/>
+      <c r="E374" s="23"/>
+      <c r="F374" s="15">
+        <v>1458</v>
+      </c>
+      <c r="G374" s="16">
+        <v>403</v>
+      </c>
+      <c r="H374" s="4">
+        <v>813.02</v>
+      </c>
+      <c r="I374" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J374" s="18">
+        <v>956.83</v>
+      </c>
+      <c r="K374" s="6">
+        <v>110</v>
+      </c>
+      <c r="L374" s="7">
+        <v>54.22</v>
+      </c>
+      <c r="M374" s="4">
+        <v>1011.05</v>
+      </c>
+      <c r="N374" s="20"/>
+    </row>
+    <row r="375" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A375" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B375" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C375" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D375" s="23"/>
+      <c r="E375" s="23"/>
+      <c r="F375" s="15">
+        <v>1613</v>
+      </c>
+      <c r="G375" s="16">
+        <v>1402</v>
+      </c>
+      <c r="H375" s="4">
+        <v>793.9</v>
+      </c>
+      <c r="I375" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J375" s="18">
+        <v>902.38</v>
+      </c>
+      <c r="K375" s="6">
+        <v>105</v>
+      </c>
+      <c r="L375" s="7">
+        <v>49.63</v>
+      </c>
+      <c r="M375" s="4">
+        <v>952.01</v>
+      </c>
+      <c r="N375" s="20"/>
+    </row>
+    <row r="376" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A376" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B376" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C376" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D376" s="23"/>
+      <c r="E376" s="23"/>
+      <c r="F376" s="15">
+        <v>1499</v>
+      </c>
+      <c r="G376" s="16">
+        <v>606</v>
+      </c>
+      <c r="H376" s="4">
+        <v>1200</v>
+      </c>
+      <c r="I376" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J376" s="18">
+        <v>1408.46</v>
+      </c>
+      <c r="K376" s="6">
+        <v>90</v>
+      </c>
+      <c r="L376" s="7">
+        <v>70.42</v>
+      </c>
+      <c r="M376" s="4">
+        <v>1478.88</v>
+      </c>
+      <c r="N376" s="20"/>
+    </row>
+    <row r="377" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A377" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B377" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="C377" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D377" s="23"/>
+      <c r="E377" s="23"/>
+      <c r="F377" s="15">
+        <v>1499</v>
+      </c>
+      <c r="G377" s="16">
+        <v>606</v>
+      </c>
+      <c r="H377" s="4">
+        <v>1200</v>
+      </c>
+      <c r="I377" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J377" s="18">
+        <v>1408.46</v>
+      </c>
+      <c r="K377" s="6">
+        <v>59</v>
+      </c>
+      <c r="L377" s="7">
+        <v>55.87</v>
+      </c>
+      <c r="M377" s="4">
+        <v>1464.33</v>
+      </c>
+      <c r="N377" s="20"/>
+    </row>
+    <row r="378" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A378" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B378" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C378" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D378" s="23"/>
+      <c r="E378" s="23"/>
+      <c r="F378" s="15">
+        <v>1610</v>
+      </c>
+      <c r="G378" s="16">
+        <v>1003</v>
+      </c>
+      <c r="H378" s="4">
+        <v>2830.4</v>
+      </c>
+      <c r="I378" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J378" s="18">
+        <v>2258.23</v>
+      </c>
+      <c r="K378" s="6">
+        <v>47</v>
+      </c>
+      <c r="L378" s="7">
+        <v>80.540000000000006</v>
+      </c>
+      <c r="M378" s="4">
+        <v>2338.77</v>
+      </c>
+      <c r="N378" s="20"/>
+      <c r="AC378">
+        <v>218</v>
+      </c>
+      <c r="AD378">
+        <v>383.41</v>
+      </c>
+      <c r="AE378">
+        <v>4520.88</v>
+      </c>
+    </row>
+    <row r="379" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A379" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B379" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C379" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D379" s="23"/>
+      <c r="E379" s="23"/>
+      <c r="F379" s="15">
+        <v>1613</v>
+      </c>
+      <c r="G379" s="16">
+        <v>1402</v>
+      </c>
+      <c r="H379" s="4">
+        <v>793.9</v>
+      </c>
+      <c r="I379" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J379" s="18">
+        <v>902.38</v>
+      </c>
+      <c r="K379" s="6">
+        <v>44</v>
+      </c>
+      <c r="L379" s="7">
+        <v>31.28</v>
+      </c>
+      <c r="M379" s="4">
+        <v>933.66</v>
+      </c>
+      <c r="N379" s="20"/>
+      <c r="AC379">
+        <v>169</v>
+      </c>
+      <c r="AD379">
+        <v>46.1</v>
+      </c>
+      <c r="AE379">
+        <v>649.98</v>
+      </c>
+    </row>
+    <row r="380" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A380" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B380" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C380" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D380" s="23"/>
+      <c r="E380" s="23"/>
+      <c r="F380" s="15">
+        <v>1469</v>
+      </c>
+      <c r="G380" s="16">
+        <v>208</v>
+      </c>
+      <c r="H380" s="4">
+        <v>968.46</v>
+      </c>
+      <c r="I380" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J380" s="18">
+        <v>1139.77</v>
+      </c>
+      <c r="K380" s="6">
+        <v>44</v>
+      </c>
+      <c r="L380" s="7">
+        <v>39.520000000000003</v>
+      </c>
+      <c r="M380" s="4">
+        <v>1179.29</v>
+      </c>
+      <c r="N380" s="20"/>
+      <c r="AC380">
+        <v>110</v>
+      </c>
+      <c r="AD380">
+        <v>54.22</v>
+      </c>
+      <c r="AE380">
+        <v>1011.05</v>
+      </c>
+    </row>
+    <row r="381" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A381" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B381" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C381" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="D381" s="23"/>
+      <c r="E381" s="23"/>
+      <c r="F381" s="15">
+        <v>1814</v>
+      </c>
+      <c r="G381" s="16">
+        <v>1502</v>
+      </c>
+      <c r="H381" s="4">
+        <v>1430</v>
+      </c>
+      <c r="I381" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J381" s="18">
+        <v>1480.44</v>
+      </c>
+      <c r="K381" s="6">
+        <v>37</v>
+      </c>
+      <c r="L381" s="7">
+        <v>47.87</v>
+      </c>
+      <c r="M381" s="4">
+        <v>1528.31</v>
+      </c>
+      <c r="N381" s="20"/>
+      <c r="AC381">
+        <v>105</v>
+      </c>
+      <c r="AD381">
+        <v>49.63</v>
+      </c>
+      <c r="AE381">
+        <v>952.01</v>
+      </c>
+    </row>
+    <row r="382" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A382" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B382" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C382" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D382" s="23"/>
+      <c r="E382" s="23"/>
+      <c r="F382" s="15">
+        <v>1572</v>
+      </c>
+      <c r="G382" s="16">
+        <v>204</v>
+      </c>
+      <c r="H382" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I382" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J382" s="18">
+        <v>1152.96</v>
+      </c>
+      <c r="K382" s="6">
+        <v>29</v>
+      </c>
+      <c r="L382" s="7">
+        <v>34.21</v>
+      </c>
+      <c r="M382" s="4">
+        <v>1187.17</v>
+      </c>
+      <c r="N382" s="20"/>
+      <c r="AC382">
+        <v>90</v>
+      </c>
+      <c r="AD382">
+        <v>70.42</v>
+      </c>
+      <c r="AE382">
+        <v>1478.88</v>
+      </c>
+    </row>
+    <row r="383" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A383" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B383" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C383" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D383" s="23"/>
+      <c r="E383" s="23"/>
+      <c r="F383" s="15">
+        <v>1499</v>
+      </c>
+      <c r="G383" s="16">
+        <v>606</v>
+      </c>
+      <c r="H383" s="4">
+        <v>1200</v>
+      </c>
+      <c r="I383" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J383" s="18">
+        <v>1408.46</v>
+      </c>
+      <c r="K383" s="6">
+        <v>29</v>
+      </c>
+      <c r="L383" s="7">
+        <v>41.79</v>
+      </c>
+      <c r="M383" s="4">
+        <v>1450.25</v>
+      </c>
+      <c r="N383" s="20"/>
+      <c r="AC383">
+        <v>59</v>
+      </c>
+      <c r="AD383">
+        <v>55.87</v>
+      </c>
+      <c r="AE383">
+        <v>1464.33</v>
+      </c>
+    </row>
+    <row r="384" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A384" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B384" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C384" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="D384" s="23"/>
+      <c r="E384" s="23"/>
+      <c r="F384" s="15">
+        <v>1853</v>
+      </c>
+      <c r="G384" s="16">
+        <v>702</v>
+      </c>
+      <c r="H384" s="4">
+        <v>1127.6500000000001</v>
+      </c>
+      <c r="I384" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J384" s="18">
+        <v>1146.45</v>
+      </c>
+      <c r="K384" s="6">
+        <v>24</v>
+      </c>
+      <c r="L384" s="7">
+        <v>32.1</v>
+      </c>
+      <c r="M384" s="4">
+        <v>1178.55</v>
+      </c>
+      <c r="N384" s="20"/>
+      <c r="AC384">
+        <v>47</v>
+      </c>
+      <c r="AD384">
+        <v>80.540000000000006</v>
+      </c>
+      <c r="AE384">
+        <v>2338.77</v>
+      </c>
+    </row>
+    <row r="385" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A385" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B385" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C385" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D385" s="23"/>
+      <c r="E385" s="23"/>
+      <c r="F385" s="15">
+        <v>1610</v>
+      </c>
+      <c r="G385" s="16">
+        <v>1003</v>
+      </c>
+      <c r="H385" s="4">
+        <v>1300</v>
+      </c>
+      <c r="I385" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J385" s="18">
+        <v>1477.64</v>
+      </c>
+      <c r="K385" s="6">
+        <v>17</v>
+      </c>
+      <c r="L385" s="7">
+        <v>37.92</v>
+      </c>
+      <c r="M385" s="4">
+        <v>1515.56</v>
+      </c>
+      <c r="N385" s="20"/>
+      <c r="AC385">
+        <v>44</v>
+      </c>
+      <c r="AD385">
+        <v>31.28</v>
+      </c>
+      <c r="AE385">
+        <v>933.66</v>
+      </c>
+    </row>
+    <row r="386" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A386" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B386" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C386" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D386" s="23"/>
+      <c r="E386" s="23"/>
+      <c r="F386" s="15">
+        <v>1613</v>
+      </c>
+      <c r="G386" s="16">
+        <v>1402</v>
+      </c>
+      <c r="H386" s="4">
+        <v>793.9</v>
+      </c>
+      <c r="I386" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J386" s="18">
+        <v>902.38</v>
+      </c>
+      <c r="K386" s="6">
+        <v>14</v>
+      </c>
+      <c r="L386" s="7">
+        <v>22.26</v>
+      </c>
+      <c r="M386" s="4">
+        <v>924.64</v>
+      </c>
+      <c r="N386" s="20"/>
+      <c r="AC386">
+        <v>44</v>
+      </c>
+      <c r="AD386">
+        <v>39.520000000000003</v>
+      </c>
+      <c r="AE386">
+        <v>1179.29</v>
+      </c>
+    </row>
+    <row r="387" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A387" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B387" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C387" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D387" s="23"/>
+      <c r="E387" s="23"/>
+      <c r="F387" s="15">
+        <v>1469</v>
+      </c>
+      <c r="G387" s="16">
+        <v>208</v>
+      </c>
+      <c r="H387" s="4">
+        <v>968.46</v>
+      </c>
+      <c r="I387" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J387" s="18">
+        <v>1139.77</v>
+      </c>
+      <c r="K387" s="6">
+        <v>14</v>
+      </c>
+      <c r="L387" s="7">
+        <v>28.12</v>
+      </c>
+      <c r="M387" s="4">
+        <v>1167.8900000000001</v>
+      </c>
+      <c r="N387" s="20"/>
+      <c r="AC387">
+        <v>37</v>
+      </c>
+      <c r="AD387">
+        <v>47.87</v>
+      </c>
+      <c r="AE387">
+        <v>1528.31</v>
+      </c>
+    </row>
+    <row r="388" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A388" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B388" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C388" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D388" s="23"/>
+      <c r="E388" s="23"/>
+      <c r="F388" s="15">
+        <v>1457</v>
+      </c>
+      <c r="G388" s="16">
+        <v>507</v>
+      </c>
+      <c r="H388" s="4">
+        <v>632.9</v>
+      </c>
+      <c r="I388" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J388" s="18">
+        <v>744.85</v>
+      </c>
+      <c r="K388" s="6">
+        <v>14</v>
+      </c>
+      <c r="L388" s="7">
+        <v>18.38</v>
+      </c>
+      <c r="M388" s="4">
+        <v>763.23</v>
+      </c>
+      <c r="N388" s="20"/>
+      <c r="AC388">
+        <v>29</v>
+      </c>
+      <c r="AD388">
+        <v>34.21</v>
+      </c>
+      <c r="AE388">
+        <v>1187.17</v>
+      </c>
+    </row>
+    <row r="389" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A389" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B389" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C389" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="D389" s="23"/>
+      <c r="E389" s="23"/>
+      <c r="F389" s="15">
+        <v>1814</v>
+      </c>
+      <c r="G389" s="16">
+        <v>1502</v>
+      </c>
+      <c r="H389" s="4">
+        <v>1430</v>
+      </c>
+      <c r="I389" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J389" s="18">
+        <v>1480.44</v>
+      </c>
+      <c r="K389" s="6">
+        <v>7</v>
+      </c>
+      <c r="L389" s="7">
+        <v>33.06</v>
+      </c>
+      <c r="M389" s="4">
+        <v>1513.5</v>
+      </c>
+      <c r="N389" s="20"/>
+      <c r="AC389">
+        <v>29</v>
+      </c>
+      <c r="AD389">
+        <v>41.79</v>
+      </c>
+      <c r="AE389">
+        <v>1450.25</v>
+      </c>
+    </row>
+    <row r="390" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A390" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B390" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C390" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D390" s="23"/>
+      <c r="E390" s="23"/>
+      <c r="F390" s="15">
+        <v>1467</v>
+      </c>
+      <c r="G390" s="16">
+        <v>207</v>
+      </c>
+      <c r="H390" s="4">
+        <v>675.78</v>
+      </c>
+      <c r="I390" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J390" s="18">
+        <v>795.32</v>
+      </c>
+      <c r="K390" s="6">
+        <v>4</v>
+      </c>
+      <c r="L390" s="7">
+        <v>16.97</v>
+      </c>
+      <c r="M390" s="4">
+        <v>812.29</v>
+      </c>
+      <c r="N390" s="20"/>
+      <c r="AC390">
+        <v>24</v>
+      </c>
+      <c r="AD390">
+        <v>32.1</v>
+      </c>
+      <c r="AE390">
+        <v>1178.55</v>
+      </c>
+    </row>
+    <row r="391" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A391" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B391" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C391" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="D391" s="23"/>
+      <c r="E391" s="23"/>
+      <c r="F391" s="15">
+        <v>1788</v>
+      </c>
+      <c r="G391" s="16">
+        <v>108</v>
+      </c>
+      <c r="H391" s="4">
+        <v>4147.3100000000004</v>
+      </c>
+      <c r="I391" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J391" s="18">
+        <v>4179.66</v>
+      </c>
+      <c r="K391" s="6">
+        <v>4</v>
+      </c>
+      <c r="L391" s="7">
+        <v>89.16</v>
+      </c>
+      <c r="M391" s="4">
+        <v>4268.82</v>
+      </c>
+      <c r="N391" s="20"/>
+      <c r="AC391">
+        <v>17</v>
+      </c>
+      <c r="AD391">
+        <v>37.92</v>
+      </c>
+      <c r="AE391">
+        <v>1515.56</v>
+      </c>
+    </row>
+    <row r="392" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A392" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B392" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C392" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D392" s="23"/>
+      <c r="E392" s="23"/>
+      <c r="F392" s="15">
+        <v>1871</v>
+      </c>
+      <c r="G392" s="16">
+        <v>602</v>
+      </c>
+      <c r="H392" s="4">
+        <v>3000</v>
+      </c>
+      <c r="I392" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="J392" s="18">
+        <v>3000</v>
+      </c>
+      <c r="K392" s="6">
+        <v>4</v>
+      </c>
+      <c r="L392" s="7">
+        <v>64</v>
+      </c>
+      <c r="M392" s="4">
+        <v>3064</v>
+      </c>
+      <c r="N392" s="20"/>
+      <c r="AC392">
+        <v>14</v>
+      </c>
+      <c r="AD392">
+        <v>22.26</v>
+      </c>
+      <c r="AE392">
+        <v>924.64</v>
+      </c>
+    </row>
+    <row r="393" spans="1:31" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A393" s="14">
+        <v>46204</v>
+      </c>
+      <c r="B393" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C393" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="D393" s="23"/>
+      <c r="E393" s="23"/>
+      <c r="F393" s="15">
+        <v>1815</v>
+      </c>
+      <c r="G393" s="16">
+        <v>1508</v>
+      </c>
+      <c r="H393" s="4">
+        <v>788</v>
+      </c>
+      <c r="I393" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J393" s="18">
+        <v>813.52</v>
+      </c>
+      <c r="K393" s="6">
+        <v>4</v>
+      </c>
+      <c r="L393" s="7">
+        <v>17.350000000000001</v>
+      </c>
+      <c r="M393" s="4">
+        <v>830.87</v>
+      </c>
+      <c r="N393" s="20"/>
+      <c r="AC393">
+        <v>14</v>
+      </c>
+      <c r="AD393">
+        <v>28.12</v>
+      </c>
+      <c r="AE393">
+        <v>1167.8900000000001</v>
+      </c>
+    </row>
+    <row r="394" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AC394">
+        <v>14</v>
+      </c>
+      <c r="AD394">
+        <v>18.38</v>
+      </c>
+      <c r="AE394">
+        <v>763.23</v>
+      </c>
+    </row>
+    <row r="395" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AC395">
+        <v>7</v>
+      </c>
+      <c r="AD395">
+        <v>33.06</v>
+      </c>
+      <c r="AE395">
+        <v>1513.5</v>
+      </c>
+    </row>
+    <row r="396" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AC396">
+        <v>4</v>
+      </c>
+      <c r="AD396">
+        <v>16.97</v>
+      </c>
+      <c r="AE396">
+        <v>812.29</v>
+      </c>
+    </row>
+    <row r="397" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AC397">
+        <v>4</v>
+      </c>
+      <c r="AD397">
+        <v>89.16</v>
+      </c>
+      <c r="AE397">
+        <v>4268.82</v>
+      </c>
+    </row>
+    <row r="398" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AC398">
+        <v>4</v>
+      </c>
+      <c r="AD398">
+        <v>64</v>
+      </c>
+      <c r="AE398">
+        <v>3064</v>
+      </c>
+    </row>
+    <row r="399" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AC399">
+        <v>4</v>
+      </c>
+      <c r="AD399">
+        <v>17.350000000000001</v>
+      </c>
+      <c r="AE399">
+        <v>830.87</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="371">
-    <mergeCell ref="C370:E370"/>
-    <mergeCell ref="C371:E371"/>
-    <mergeCell ref="C367:E367"/>
-    <mergeCell ref="C368:E368"/>
-    <mergeCell ref="C369:E369"/>
-    <mergeCell ref="C364:E364"/>
-    <mergeCell ref="C365:E365"/>
-    <mergeCell ref="C366:E366"/>
-    <mergeCell ref="C361:E361"/>
-    <mergeCell ref="C362:E362"/>
-    <mergeCell ref="C363:E363"/>
-    <mergeCell ref="C358:E358"/>
-    <mergeCell ref="C359:E359"/>
-    <mergeCell ref="C360:E360"/>
-    <mergeCell ref="C355:E355"/>
-    <mergeCell ref="C356:E356"/>
-    <mergeCell ref="C357:E357"/>
-    <mergeCell ref="C352:E352"/>
-    <mergeCell ref="C353:E353"/>
-    <mergeCell ref="C354:E354"/>
-    <mergeCell ref="C349:E349"/>
-    <mergeCell ref="C350:E350"/>
-    <mergeCell ref="C351:E351"/>
-    <mergeCell ref="C346:E346"/>
-    <mergeCell ref="C347:E347"/>
-    <mergeCell ref="C348:E348"/>
-    <mergeCell ref="C343:E343"/>
-    <mergeCell ref="C344:E344"/>
-    <mergeCell ref="C345:E345"/>
+  <mergeCells count="393">
+    <mergeCell ref="C390:E390"/>
+    <mergeCell ref="C391:E391"/>
+    <mergeCell ref="C392:E392"/>
+    <mergeCell ref="C393:E393"/>
+    <mergeCell ref="C381:E381"/>
+    <mergeCell ref="C382:E382"/>
+    <mergeCell ref="C383:E383"/>
+    <mergeCell ref="C384:E384"/>
+    <mergeCell ref="C385:E385"/>
+    <mergeCell ref="C386:E386"/>
+    <mergeCell ref="C387:E387"/>
+    <mergeCell ref="C388:E388"/>
+    <mergeCell ref="C389:E389"/>
+    <mergeCell ref="C372:E372"/>
+    <mergeCell ref="C373:E373"/>
+    <mergeCell ref="C374:E374"/>
+    <mergeCell ref="C375:E375"/>
+    <mergeCell ref="C376:E376"/>
+    <mergeCell ref="C377:E377"/>
+    <mergeCell ref="C378:E378"/>
+    <mergeCell ref="C379:E379"/>
+    <mergeCell ref="C380:E380"/>
+    <mergeCell ref="C340:E340"/>
+    <mergeCell ref="C341:E341"/>
+    <mergeCell ref="C342:E342"/>
+    <mergeCell ref="C337:E337"/>
+    <mergeCell ref="C338:E338"/>
+    <mergeCell ref="C339:E339"/>
+    <mergeCell ref="C334:E334"/>
+    <mergeCell ref="C335:E335"/>
+    <mergeCell ref="C336:E336"/>
+    <mergeCell ref="C331:E331"/>
+    <mergeCell ref="C332:E332"/>
+    <mergeCell ref="C333:E333"/>
+    <mergeCell ref="C328:E328"/>
+    <mergeCell ref="C329:E329"/>
+    <mergeCell ref="C330:E330"/>
+    <mergeCell ref="C325:E325"/>
+    <mergeCell ref="C326:E326"/>
+    <mergeCell ref="C327:E327"/>
+    <mergeCell ref="C322:E322"/>
+    <mergeCell ref="C323:E323"/>
+    <mergeCell ref="C324:E324"/>
+    <mergeCell ref="C319:E319"/>
+    <mergeCell ref="C320:E320"/>
+    <mergeCell ref="C321:E321"/>
+    <mergeCell ref="C316:E316"/>
+    <mergeCell ref="C317:E317"/>
+    <mergeCell ref="C318:E318"/>
+    <mergeCell ref="C127:E127"/>
+    <mergeCell ref="C128:E128"/>
+    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="C130:E130"/>
+    <mergeCell ref="C131:E131"/>
+    <mergeCell ref="C132:E132"/>
+    <mergeCell ref="C142:E142"/>
+    <mergeCell ref="C133:E133"/>
+    <mergeCell ref="C134:E134"/>
+    <mergeCell ref="C135:E135"/>
+    <mergeCell ref="C136:E136"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="C138:E138"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="C141:E141"/>
+    <mergeCell ref="C15:E15"/>
+    <mergeCell ref="C16:E16"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="C124:E124"/>
+    <mergeCell ref="C125:E125"/>
+    <mergeCell ref="C126:E126"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="C18:E18"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="C100:E100"/>
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C107:E107"/>
+    <mergeCell ref="C108:E108"/>
+    <mergeCell ref="C109:E109"/>
+    <mergeCell ref="C110:E110"/>
+    <mergeCell ref="C111:E111"/>
+    <mergeCell ref="C102:E102"/>
+    <mergeCell ref="C103:E103"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="C105:E105"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="C122:E122"/>
+    <mergeCell ref="C123:E123"/>
+    <mergeCell ref="C117:E117"/>
+    <mergeCell ref="C118:E118"/>
+    <mergeCell ref="C119:E119"/>
+    <mergeCell ref="C120:E120"/>
+    <mergeCell ref="C121:E121"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="C113:E113"/>
+    <mergeCell ref="C114:E114"/>
+    <mergeCell ref="C115:E115"/>
+    <mergeCell ref="C116:E116"/>
+    <mergeCell ref="C143:E143"/>
+    <mergeCell ref="C144:E144"/>
+    <mergeCell ref="C145:E145"/>
+    <mergeCell ref="C146:E146"/>
+    <mergeCell ref="C147:E147"/>
+    <mergeCell ref="C148:E148"/>
+    <mergeCell ref="C149:E149"/>
+    <mergeCell ref="C150:E150"/>
+    <mergeCell ref="C151:E151"/>
+    <mergeCell ref="C152:E152"/>
+    <mergeCell ref="C153:E153"/>
+    <mergeCell ref="C154:E154"/>
+    <mergeCell ref="C155:E155"/>
+    <mergeCell ref="C156:E156"/>
+    <mergeCell ref="C157:E157"/>
+    <mergeCell ref="C158:E158"/>
+    <mergeCell ref="C159:E159"/>
+    <mergeCell ref="C160:E160"/>
+    <mergeCell ref="C161:E161"/>
+    <mergeCell ref="C162:E162"/>
+    <mergeCell ref="C163:E163"/>
+    <mergeCell ref="C164:E164"/>
+    <mergeCell ref="C165:E165"/>
+    <mergeCell ref="C166:E166"/>
+    <mergeCell ref="C167:E167"/>
+    <mergeCell ref="C168:E168"/>
+    <mergeCell ref="C169:E169"/>
+    <mergeCell ref="C170:E170"/>
+    <mergeCell ref="C171:E171"/>
+    <mergeCell ref="C172:E172"/>
+    <mergeCell ref="C173:E173"/>
+    <mergeCell ref="C174:E174"/>
+    <mergeCell ref="C175:E175"/>
+    <mergeCell ref="C176:E176"/>
+    <mergeCell ref="C177:E177"/>
+    <mergeCell ref="C178:E178"/>
+    <mergeCell ref="C179:E179"/>
+    <mergeCell ref="C180:E180"/>
+    <mergeCell ref="C181:E181"/>
+    <mergeCell ref="C182:E182"/>
+    <mergeCell ref="C183:E183"/>
+    <mergeCell ref="C184:E184"/>
+    <mergeCell ref="C185:E185"/>
+    <mergeCell ref="C186:E186"/>
+    <mergeCell ref="C187:E187"/>
+    <mergeCell ref="C188:E188"/>
+    <mergeCell ref="C189:E189"/>
+    <mergeCell ref="C190:E190"/>
+    <mergeCell ref="C191:E191"/>
+    <mergeCell ref="C192:E192"/>
+    <mergeCell ref="C193:E193"/>
+    <mergeCell ref="C194:E194"/>
+    <mergeCell ref="C195:E195"/>
+    <mergeCell ref="C196:E196"/>
+    <mergeCell ref="C197:E197"/>
+    <mergeCell ref="C198:E198"/>
+    <mergeCell ref="C199:E199"/>
+    <mergeCell ref="C200:E200"/>
+    <mergeCell ref="C201:E201"/>
+    <mergeCell ref="C202:E202"/>
+    <mergeCell ref="C203:E203"/>
+    <mergeCell ref="C204:E204"/>
+    <mergeCell ref="C205:E205"/>
+    <mergeCell ref="C206:E206"/>
+    <mergeCell ref="C207:E207"/>
+    <mergeCell ref="C208:E208"/>
+    <mergeCell ref="C209:E209"/>
+    <mergeCell ref="C210:E210"/>
+    <mergeCell ref="C211:E211"/>
+    <mergeCell ref="C212:E212"/>
+    <mergeCell ref="C213:E213"/>
+    <mergeCell ref="C214:E214"/>
+    <mergeCell ref="C215:E215"/>
+    <mergeCell ref="C216:E216"/>
+    <mergeCell ref="C217:E217"/>
+    <mergeCell ref="C218:E218"/>
+    <mergeCell ref="C219:E219"/>
+    <mergeCell ref="C220:E220"/>
+    <mergeCell ref="C221:E221"/>
+    <mergeCell ref="C222:E222"/>
+    <mergeCell ref="C223:E223"/>
+    <mergeCell ref="C224:E224"/>
+    <mergeCell ref="C225:E225"/>
+    <mergeCell ref="C226:E226"/>
+    <mergeCell ref="C227:E227"/>
+    <mergeCell ref="C228:E228"/>
+    <mergeCell ref="C229:E229"/>
+    <mergeCell ref="C230:E230"/>
+    <mergeCell ref="C231:E231"/>
+    <mergeCell ref="C232:E232"/>
+    <mergeCell ref="C233:E233"/>
+    <mergeCell ref="C234:E234"/>
+    <mergeCell ref="C235:E235"/>
+    <mergeCell ref="C236:E236"/>
+    <mergeCell ref="C237:E237"/>
+    <mergeCell ref="C238:E238"/>
+    <mergeCell ref="C239:E239"/>
+    <mergeCell ref="C240:E240"/>
+    <mergeCell ref="C241:E241"/>
+    <mergeCell ref="C242:E242"/>
+    <mergeCell ref="C243:E243"/>
+    <mergeCell ref="C244:E244"/>
+    <mergeCell ref="C245:E245"/>
+    <mergeCell ref="C246:E246"/>
+    <mergeCell ref="C247:E247"/>
+    <mergeCell ref="C248:E248"/>
+    <mergeCell ref="C249:E249"/>
+    <mergeCell ref="C250:E250"/>
+    <mergeCell ref="C251:E251"/>
+    <mergeCell ref="C252:E252"/>
+    <mergeCell ref="C253:E253"/>
+    <mergeCell ref="C254:E254"/>
+    <mergeCell ref="C255:E255"/>
+    <mergeCell ref="C256:E256"/>
+    <mergeCell ref="C257:E257"/>
+    <mergeCell ref="C258:E258"/>
+    <mergeCell ref="C259:E259"/>
+    <mergeCell ref="C260:E260"/>
+    <mergeCell ref="C261:E261"/>
+    <mergeCell ref="C262:E262"/>
+    <mergeCell ref="C263:E263"/>
+    <mergeCell ref="C264:E264"/>
+    <mergeCell ref="C265:E265"/>
+    <mergeCell ref="C266:E266"/>
+    <mergeCell ref="C267:E267"/>
+    <mergeCell ref="C268:E268"/>
+    <mergeCell ref="C269:E269"/>
+    <mergeCell ref="C270:E270"/>
+    <mergeCell ref="C271:E271"/>
+    <mergeCell ref="C272:E272"/>
+    <mergeCell ref="C273:E273"/>
+    <mergeCell ref="C274:E274"/>
+    <mergeCell ref="C275:E275"/>
+    <mergeCell ref="C276:E276"/>
+    <mergeCell ref="C277:E277"/>
+    <mergeCell ref="C313:E313"/>
+    <mergeCell ref="C287:E287"/>
+    <mergeCell ref="C288:E288"/>
+    <mergeCell ref="C289:E289"/>
+    <mergeCell ref="C290:E290"/>
+    <mergeCell ref="C278:E278"/>
+    <mergeCell ref="C279:E279"/>
+    <mergeCell ref="C280:E280"/>
+    <mergeCell ref="C281:E281"/>
+    <mergeCell ref="C282:E282"/>
+    <mergeCell ref="C283:E283"/>
+    <mergeCell ref="C284:E284"/>
+    <mergeCell ref="C285:E285"/>
+    <mergeCell ref="C286:E286"/>
     <mergeCell ref="C291:E291"/>
     <mergeCell ref="C292:E292"/>
     <mergeCell ref="C293:E293"/>
@@ -14984,324 +16377,35 @@
     <mergeCell ref="C310:E310"/>
     <mergeCell ref="C311:E311"/>
     <mergeCell ref="C312:E312"/>
-    <mergeCell ref="C313:E313"/>
-    <mergeCell ref="C287:E287"/>
-    <mergeCell ref="C288:E288"/>
-    <mergeCell ref="C289:E289"/>
-    <mergeCell ref="C290:E290"/>
-    <mergeCell ref="C278:E278"/>
-    <mergeCell ref="C279:E279"/>
-    <mergeCell ref="C280:E280"/>
-    <mergeCell ref="C281:E281"/>
-    <mergeCell ref="C282:E282"/>
-    <mergeCell ref="C283:E283"/>
-    <mergeCell ref="C284:E284"/>
-    <mergeCell ref="C285:E285"/>
-    <mergeCell ref="C286:E286"/>
-    <mergeCell ref="C269:E269"/>
-    <mergeCell ref="C270:E270"/>
-    <mergeCell ref="C271:E271"/>
-    <mergeCell ref="C272:E272"/>
-    <mergeCell ref="C273:E273"/>
-    <mergeCell ref="C274:E274"/>
-    <mergeCell ref="C275:E275"/>
-    <mergeCell ref="C276:E276"/>
-    <mergeCell ref="C277:E277"/>
-    <mergeCell ref="C260:E260"/>
-    <mergeCell ref="C261:E261"/>
-    <mergeCell ref="C262:E262"/>
-    <mergeCell ref="C263:E263"/>
-    <mergeCell ref="C264:E264"/>
-    <mergeCell ref="C265:E265"/>
-    <mergeCell ref="C266:E266"/>
-    <mergeCell ref="C267:E267"/>
-    <mergeCell ref="C268:E268"/>
-    <mergeCell ref="C251:E251"/>
-    <mergeCell ref="C252:E252"/>
-    <mergeCell ref="C253:E253"/>
-    <mergeCell ref="C254:E254"/>
-    <mergeCell ref="C255:E255"/>
-    <mergeCell ref="C256:E256"/>
-    <mergeCell ref="C257:E257"/>
-    <mergeCell ref="C258:E258"/>
-    <mergeCell ref="C259:E259"/>
-    <mergeCell ref="C242:E242"/>
-    <mergeCell ref="C243:E243"/>
-    <mergeCell ref="C244:E244"/>
-    <mergeCell ref="C245:E245"/>
-    <mergeCell ref="C246:E246"/>
-    <mergeCell ref="C247:E247"/>
-    <mergeCell ref="C248:E248"/>
-    <mergeCell ref="C249:E249"/>
-    <mergeCell ref="C250:E250"/>
-    <mergeCell ref="C233:E233"/>
-    <mergeCell ref="C234:E234"/>
-    <mergeCell ref="C235:E235"/>
-    <mergeCell ref="C236:E236"/>
-    <mergeCell ref="C237:E237"/>
-    <mergeCell ref="C238:E238"/>
-    <mergeCell ref="C239:E239"/>
-    <mergeCell ref="C240:E240"/>
-    <mergeCell ref="C241:E241"/>
-    <mergeCell ref="C224:E224"/>
-    <mergeCell ref="C225:E225"/>
-    <mergeCell ref="C226:E226"/>
-    <mergeCell ref="C227:E227"/>
-    <mergeCell ref="C228:E228"/>
-    <mergeCell ref="C229:E229"/>
-    <mergeCell ref="C230:E230"/>
-    <mergeCell ref="C231:E231"/>
-    <mergeCell ref="C232:E232"/>
-    <mergeCell ref="C215:E215"/>
-    <mergeCell ref="C216:E216"/>
-    <mergeCell ref="C217:E217"/>
-    <mergeCell ref="C218:E218"/>
-    <mergeCell ref="C219:E219"/>
-    <mergeCell ref="C220:E220"/>
-    <mergeCell ref="C221:E221"/>
-    <mergeCell ref="C222:E222"/>
-    <mergeCell ref="C223:E223"/>
-    <mergeCell ref="C206:E206"/>
-    <mergeCell ref="C207:E207"/>
-    <mergeCell ref="C208:E208"/>
-    <mergeCell ref="C209:E209"/>
-    <mergeCell ref="C210:E210"/>
-    <mergeCell ref="C211:E211"/>
-    <mergeCell ref="C212:E212"/>
-    <mergeCell ref="C213:E213"/>
-    <mergeCell ref="C214:E214"/>
-    <mergeCell ref="C197:E197"/>
-    <mergeCell ref="C198:E198"/>
-    <mergeCell ref="C199:E199"/>
-    <mergeCell ref="C200:E200"/>
-    <mergeCell ref="C201:E201"/>
-    <mergeCell ref="C202:E202"/>
-    <mergeCell ref="C203:E203"/>
-    <mergeCell ref="C204:E204"/>
-    <mergeCell ref="C205:E205"/>
-    <mergeCell ref="C188:E188"/>
-    <mergeCell ref="C189:E189"/>
-    <mergeCell ref="C190:E190"/>
-    <mergeCell ref="C191:E191"/>
-    <mergeCell ref="C192:E192"/>
-    <mergeCell ref="C193:E193"/>
-    <mergeCell ref="C194:E194"/>
-    <mergeCell ref="C195:E195"/>
-    <mergeCell ref="C196:E196"/>
-    <mergeCell ref="C179:E179"/>
-    <mergeCell ref="C180:E180"/>
-    <mergeCell ref="C181:E181"/>
-    <mergeCell ref="C182:E182"/>
-    <mergeCell ref="C183:E183"/>
-    <mergeCell ref="C184:E184"/>
-    <mergeCell ref="C185:E185"/>
-    <mergeCell ref="C186:E186"/>
-    <mergeCell ref="C187:E187"/>
-    <mergeCell ref="C170:E170"/>
-    <mergeCell ref="C171:E171"/>
-    <mergeCell ref="C172:E172"/>
-    <mergeCell ref="C173:E173"/>
-    <mergeCell ref="C174:E174"/>
-    <mergeCell ref="C175:E175"/>
-    <mergeCell ref="C176:E176"/>
-    <mergeCell ref="C177:E177"/>
-    <mergeCell ref="C178:E178"/>
-    <mergeCell ref="C161:E161"/>
-    <mergeCell ref="C162:E162"/>
-    <mergeCell ref="C163:E163"/>
-    <mergeCell ref="C164:E164"/>
-    <mergeCell ref="C165:E165"/>
-    <mergeCell ref="C166:E166"/>
-    <mergeCell ref="C167:E167"/>
-    <mergeCell ref="C168:E168"/>
-    <mergeCell ref="C169:E169"/>
-    <mergeCell ref="C152:E152"/>
-    <mergeCell ref="C153:E153"/>
-    <mergeCell ref="C154:E154"/>
-    <mergeCell ref="C155:E155"/>
-    <mergeCell ref="C156:E156"/>
-    <mergeCell ref="C157:E157"/>
-    <mergeCell ref="C158:E158"/>
-    <mergeCell ref="C159:E159"/>
-    <mergeCell ref="C160:E160"/>
-    <mergeCell ref="C143:E143"/>
-    <mergeCell ref="C144:E144"/>
-    <mergeCell ref="C145:E145"/>
-    <mergeCell ref="C146:E146"/>
-    <mergeCell ref="C147:E147"/>
-    <mergeCell ref="C148:E148"/>
-    <mergeCell ref="C149:E149"/>
-    <mergeCell ref="C150:E150"/>
-    <mergeCell ref="C151:E151"/>
-    <mergeCell ref="C122:E122"/>
-    <mergeCell ref="C123:E123"/>
-    <mergeCell ref="C117:E117"/>
-    <mergeCell ref="C118:E118"/>
-    <mergeCell ref="C119:E119"/>
-    <mergeCell ref="C120:E120"/>
-    <mergeCell ref="C121:E121"/>
-    <mergeCell ref="C112:E112"/>
-    <mergeCell ref="C113:E113"/>
-    <mergeCell ref="C114:E114"/>
-    <mergeCell ref="C115:E115"/>
-    <mergeCell ref="C116:E116"/>
-    <mergeCell ref="C107:E107"/>
-    <mergeCell ref="C108:E108"/>
-    <mergeCell ref="C109:E109"/>
-    <mergeCell ref="C110:E110"/>
-    <mergeCell ref="C111:E111"/>
-    <mergeCell ref="C102:E102"/>
-    <mergeCell ref="C103:E103"/>
-    <mergeCell ref="C104:E104"/>
-    <mergeCell ref="C105:E105"/>
-    <mergeCell ref="C106:E106"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="C98:E98"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="C100:E100"/>
-    <mergeCell ref="C101:E101"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="C88:E88"/>
-    <mergeCell ref="C89:E89"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="C94:E94"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C15:E15"/>
-    <mergeCell ref="C16:E16"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="C124:E124"/>
-    <mergeCell ref="C125:E125"/>
-    <mergeCell ref="C126:E126"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C17:E17"/>
-    <mergeCell ref="C18:E18"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C127:E127"/>
-    <mergeCell ref="C128:E128"/>
-    <mergeCell ref="C129:E129"/>
-    <mergeCell ref="C130:E130"/>
-    <mergeCell ref="C131:E131"/>
-    <mergeCell ref="C132:E132"/>
-    <mergeCell ref="C142:E142"/>
-    <mergeCell ref="C133:E133"/>
-    <mergeCell ref="C134:E134"/>
-    <mergeCell ref="C135:E135"/>
-    <mergeCell ref="C136:E136"/>
-    <mergeCell ref="C137:E137"/>
-    <mergeCell ref="C138:E138"/>
-    <mergeCell ref="C139:E139"/>
-    <mergeCell ref="C140:E140"/>
-    <mergeCell ref="C141:E141"/>
-    <mergeCell ref="C322:E322"/>
-    <mergeCell ref="C323:E323"/>
-    <mergeCell ref="C324:E324"/>
-    <mergeCell ref="C319:E319"/>
-    <mergeCell ref="C320:E320"/>
-    <mergeCell ref="C321:E321"/>
-    <mergeCell ref="C316:E316"/>
-    <mergeCell ref="C317:E317"/>
-    <mergeCell ref="C318:E318"/>
-    <mergeCell ref="C331:E331"/>
-    <mergeCell ref="C332:E332"/>
-    <mergeCell ref="C333:E333"/>
-    <mergeCell ref="C328:E328"/>
-    <mergeCell ref="C329:E329"/>
-    <mergeCell ref="C330:E330"/>
-    <mergeCell ref="C325:E325"/>
-    <mergeCell ref="C326:E326"/>
-    <mergeCell ref="C327:E327"/>
-    <mergeCell ref="C340:E340"/>
-    <mergeCell ref="C341:E341"/>
-    <mergeCell ref="C342:E342"/>
-    <mergeCell ref="C337:E337"/>
-    <mergeCell ref="C338:E338"/>
-    <mergeCell ref="C339:E339"/>
-    <mergeCell ref="C334:E334"/>
-    <mergeCell ref="C335:E335"/>
-    <mergeCell ref="C336:E336"/>
+    <mergeCell ref="C349:E349"/>
+    <mergeCell ref="C350:E350"/>
+    <mergeCell ref="C351:E351"/>
+    <mergeCell ref="C346:E346"/>
+    <mergeCell ref="C347:E347"/>
+    <mergeCell ref="C348:E348"/>
+    <mergeCell ref="C343:E343"/>
+    <mergeCell ref="C344:E344"/>
+    <mergeCell ref="C345:E345"/>
+    <mergeCell ref="C358:E358"/>
+    <mergeCell ref="C359:E359"/>
+    <mergeCell ref="C360:E360"/>
+    <mergeCell ref="C355:E355"/>
+    <mergeCell ref="C356:E356"/>
+    <mergeCell ref="C357:E357"/>
+    <mergeCell ref="C352:E352"/>
+    <mergeCell ref="C353:E353"/>
+    <mergeCell ref="C354:E354"/>
+    <mergeCell ref="C370:E370"/>
+    <mergeCell ref="C371:E371"/>
+    <mergeCell ref="C367:E367"/>
+    <mergeCell ref="C368:E368"/>
+    <mergeCell ref="C369:E369"/>
+    <mergeCell ref="C364:E364"/>
+    <mergeCell ref="C365:E365"/>
+    <mergeCell ref="C366:E366"/>
+    <mergeCell ref="C361:E361"/>
+    <mergeCell ref="C362:E362"/>
+    <mergeCell ref="C363:E363"/>
   </mergeCells>
   <pageMargins left="0.52999994886203072" right="0.52999994886203072" top="0.52999994886203072" bottom="0.68999998212799307" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="landscape" r:id="rId1"/>

--- a/data/vendas-inadimplentes.xlsx
+++ b/data/vendas-inadimplentes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rssla\Desktop\SPE JARDIM LUZ\01. Relatorio Obra Ramon Gerenciamento\meu-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233F33A0-1B6F-4A3C-B62B-BC80376C2C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{233F33A0-1B6F-4A3C-B62B-BC80376C2C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E7646CF-4CFF-45BA-B8AE-221BC924329C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="192">
   <si>
     <t>Data vecto</t>
   </si>
@@ -573,6 +573,42 @@
   </si>
   <si>
     <t>ZANDERSON LUCAS ROSA LINO (438)</t>
+  </si>
+  <si>
+    <t>01/07/2026</t>
+  </si>
+  <si>
+    <t>05/08/2026</t>
+  </si>
+  <si>
+    <t>15/08/2026</t>
+  </si>
+  <si>
+    <t>KENENDY ANDERSON OLIVEIRA SILVA (447)</t>
+  </si>
+  <si>
+    <t>17/08/2026</t>
+  </si>
+  <si>
+    <t>20/08/2026</t>
+  </si>
+  <si>
+    <t>25/08/2026</t>
+  </si>
+  <si>
+    <t>PAULO ELIAS VILHALVA DANTAS (451)</t>
+  </si>
+  <si>
+    <t>01/09/2026</t>
+  </si>
+  <si>
+    <t>27/08/2026</t>
+  </si>
+  <si>
+    <t>30/08/2026</t>
+  </si>
+  <si>
+    <t>VINICIUS FARIA GONZAGA (426)</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AE399"/>
+  <dimension ref="A1:AE419"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -15946,6 +15982,41 @@
       </c>
     </row>
     <row r="394" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A394" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B394" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C394" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D394" s="23"/>
+      <c r="E394" s="23"/>
+      <c r="F394" s="15">
+        <v>1450</v>
+      </c>
+      <c r="G394" s="16">
+        <v>508</v>
+      </c>
+      <c r="H394" s="4">
+        <v>3515.6</v>
+      </c>
+      <c r="I394" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J394" s="18">
+        <v>4162.7</v>
+      </c>
+      <c r="K394" s="6">
+        <v>248</v>
+      </c>
+      <c r="L394" s="7">
+        <v>427.37</v>
+      </c>
+      <c r="M394" s="4">
+        <v>4590.07</v>
+      </c>
       <c r="AC394">
         <v>14</v>
       </c>
@@ -15957,6 +16028,41 @@
       </c>
     </row>
     <row r="395" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A395" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B395" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C395" s="23" t="s">
+        <v>10</v>
+      </c>
+      <c r="D395" s="23"/>
+      <c r="E395" s="23"/>
+      <c r="F395" s="15">
+        <v>1508</v>
+      </c>
+      <c r="G395" s="16">
+        <v>1306</v>
+      </c>
+      <c r="H395" s="4">
+        <v>565.54999999999995</v>
+      </c>
+      <c r="I395" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J395" s="18">
+        <v>607.55999999999995</v>
+      </c>
+      <c r="K395" s="6">
+        <v>199</v>
+      </c>
+      <c r="L395" s="7">
+        <v>52.45</v>
+      </c>
+      <c r="M395" s="4">
+        <v>660.01</v>
+      </c>
       <c r="AC395">
         <v>7</v>
       </c>
@@ -15968,6 +16074,41 @@
       </c>
     </row>
     <row r="396" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A396" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B396" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C396" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D396" s="23"/>
+      <c r="E396" s="23"/>
+      <c r="F396" s="15">
+        <v>1458</v>
+      </c>
+      <c r="G396" s="16">
+        <v>403</v>
+      </c>
+      <c r="H396" s="4">
+        <v>813.02</v>
+      </c>
+      <c r="I396" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J396" s="18">
+        <v>962.67</v>
+      </c>
+      <c r="K396" s="6">
+        <v>140</v>
+      </c>
+      <c r="L396" s="7">
+        <v>64.17</v>
+      </c>
+      <c r="M396" s="4">
+        <v>1026.8399999999999</v>
+      </c>
       <c r="AC396">
         <v>4</v>
       </c>
@@ -15979,6 +16120,41 @@
       </c>
     </row>
     <row r="397" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A397" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B397" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C397" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D397" s="23"/>
+      <c r="E397" s="23"/>
+      <c r="F397" s="15">
+        <v>1613</v>
+      </c>
+      <c r="G397" s="16">
+        <v>1402</v>
+      </c>
+      <c r="H397" s="4">
+        <v>793.9</v>
+      </c>
+      <c r="I397" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J397" s="18">
+        <v>907.89</v>
+      </c>
+      <c r="K397" s="6">
+        <v>135</v>
+      </c>
+      <c r="L397" s="7">
+        <v>59.02</v>
+      </c>
+      <c r="M397" s="4">
+        <v>966.91</v>
+      </c>
       <c r="AC397">
         <v>4</v>
       </c>
@@ -15990,6 +16166,41 @@
       </c>
     </row>
     <row r="398" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A398" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B398" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C398" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D398" s="23"/>
+      <c r="E398" s="23"/>
+      <c r="F398" s="15">
+        <v>1610</v>
+      </c>
+      <c r="G398" s="16">
+        <v>1003</v>
+      </c>
+      <c r="H398" s="4">
+        <v>2830.4</v>
+      </c>
+      <c r="I398" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J398" s="18">
+        <v>2272.0100000000002</v>
+      </c>
+      <c r="K398" s="6">
+        <v>77</v>
+      </c>
+      <c r="L398" s="7">
+        <v>103.75</v>
+      </c>
+      <c r="M398" s="4">
+        <v>2375.7600000000002</v>
+      </c>
       <c r="AC398">
         <v>4</v>
       </c>
@@ -16001,6 +16212,41 @@
       </c>
     </row>
     <row r="399" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A399" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B399" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C399" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D399" s="23"/>
+      <c r="E399" s="23"/>
+      <c r="F399" s="15">
+        <v>1613</v>
+      </c>
+      <c r="G399" s="16">
+        <v>1402</v>
+      </c>
+      <c r="H399" s="4">
+        <v>793.9</v>
+      </c>
+      <c r="I399" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J399" s="18">
+        <v>907.89</v>
+      </c>
+      <c r="K399" s="6">
+        <v>74</v>
+      </c>
+      <c r="L399" s="7">
+        <v>40.549999999999997</v>
+      </c>
+      <c r="M399" s="4">
+        <v>948.44</v>
+      </c>
       <c r="AC399">
         <v>4</v>
       </c>
@@ -16011,73 +16257,1033 @@
         <v>830.87</v>
       </c>
     </row>
+    <row r="400" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A400" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B400" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C400" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D400" s="23"/>
+      <c r="E400" s="23"/>
+      <c r="F400" s="15">
+        <v>1469</v>
+      </c>
+      <c r="G400" s="16">
+        <v>208</v>
+      </c>
+      <c r="H400" s="4">
+        <v>968.46</v>
+      </c>
+      <c r="I400" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J400" s="18">
+        <v>1146.72</v>
+      </c>
+      <c r="K400" s="6">
+        <v>74</v>
+      </c>
+      <c r="L400" s="7">
+        <v>51.22</v>
+      </c>
+      <c r="M400" s="4">
+        <v>1197.94</v>
+      </c>
+    </row>
+    <row r="401" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A401" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B401" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C401" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="D401" s="23"/>
+      <c r="E401" s="23"/>
+      <c r="F401" s="15">
+        <v>1814</v>
+      </c>
+      <c r="G401" s="16">
+        <v>1502</v>
+      </c>
+      <c r="H401" s="4">
+        <v>1430</v>
+      </c>
+      <c r="I401" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J401" s="18">
+        <v>1489.47</v>
+      </c>
+      <c r="K401" s="6">
+        <v>67</v>
+      </c>
+      <c r="L401" s="7">
+        <v>63.05</v>
+      </c>
+      <c r="M401" s="4">
+        <v>1552.52</v>
+      </c>
+    </row>
+    <row r="402" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A402" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B402" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="C402" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D402" s="23"/>
+      <c r="E402" s="23"/>
+      <c r="F402" s="15">
+        <v>1610</v>
+      </c>
+      <c r="G402" s="16">
+        <v>1003</v>
+      </c>
+      <c r="H402" s="4">
+        <v>1300</v>
+      </c>
+      <c r="I402" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J402" s="18">
+        <v>1486.65</v>
+      </c>
+      <c r="K402" s="6">
+        <v>47</v>
+      </c>
+      <c r="L402" s="7">
+        <v>53.02</v>
+      </c>
+      <c r="M402" s="4">
+        <v>1539.67</v>
+      </c>
+    </row>
+    <row r="403" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A403" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B403" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C403" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D403" s="23"/>
+      <c r="E403" s="23"/>
+      <c r="F403" s="15">
+        <v>1613</v>
+      </c>
+      <c r="G403" s="16">
+        <v>1402</v>
+      </c>
+      <c r="H403" s="4">
+        <v>793.9</v>
+      </c>
+      <c r="I403" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J403" s="18">
+        <v>907.89</v>
+      </c>
+      <c r="K403" s="6">
+        <v>44</v>
+      </c>
+      <c r="L403" s="7">
+        <v>31.48</v>
+      </c>
+      <c r="M403" s="4">
+        <v>939.37</v>
+      </c>
+    </row>
+    <row r="404" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A404" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B404" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C404" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D404" s="23"/>
+      <c r="E404" s="23"/>
+      <c r="F404" s="15">
+        <v>1469</v>
+      </c>
+      <c r="G404" s="16">
+        <v>208</v>
+      </c>
+      <c r="H404" s="4">
+        <v>968.46</v>
+      </c>
+      <c r="I404" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J404" s="18">
+        <v>1146.72</v>
+      </c>
+      <c r="K404" s="6">
+        <v>44</v>
+      </c>
+      <c r="L404" s="7">
+        <v>39.75</v>
+      </c>
+      <c r="M404" s="4">
+        <v>1186.47</v>
+      </c>
+    </row>
+    <row r="405" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A405" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B405" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C405" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D405" s="23"/>
+      <c r="E405" s="23"/>
+      <c r="F405" s="15">
+        <v>1457</v>
+      </c>
+      <c r="G405" s="16">
+        <v>507</v>
+      </c>
+      <c r="H405" s="4">
+        <v>632.9</v>
+      </c>
+      <c r="I405" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J405" s="18">
+        <v>749.4</v>
+      </c>
+      <c r="K405" s="6">
+        <v>44</v>
+      </c>
+      <c r="L405" s="7">
+        <v>25.98</v>
+      </c>
+      <c r="M405" s="4">
+        <v>775.38</v>
+      </c>
+    </row>
+    <row r="406" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A406" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B406" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="C406" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="D406" s="23"/>
+      <c r="E406" s="23"/>
+      <c r="F406" s="15">
+        <v>1814</v>
+      </c>
+      <c r="G406" s="16">
+        <v>1502</v>
+      </c>
+      <c r="H406" s="4">
+        <v>1430</v>
+      </c>
+      <c r="I406" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J406" s="18">
+        <v>1489.47</v>
+      </c>
+      <c r="K406" s="6">
+        <v>37</v>
+      </c>
+      <c r="L406" s="7">
+        <v>48.16</v>
+      </c>
+      <c r="M406" s="4">
+        <v>1537.63</v>
+      </c>
+    </row>
+    <row r="407" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A407" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B407" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C407" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D407" s="23"/>
+      <c r="E407" s="23"/>
+      <c r="F407" s="15">
+        <v>1572</v>
+      </c>
+      <c r="G407" s="16">
+        <v>204</v>
+      </c>
+      <c r="H407" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I407" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J407" s="18">
+        <v>1159.99</v>
+      </c>
+      <c r="K407" s="6">
+        <v>28</v>
+      </c>
+      <c r="L407" s="7">
+        <v>34.03</v>
+      </c>
+      <c r="M407" s="4">
+        <v>1194.02</v>
+      </c>
+    </row>
+    <row r="408" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A408" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B408" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C408" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="D408" s="23"/>
+      <c r="E408" s="23"/>
+      <c r="F408" s="15">
+        <v>1865</v>
+      </c>
+      <c r="G408" s="16">
+        <v>802</v>
+      </c>
+      <c r="H408" s="4">
+        <v>987.59</v>
+      </c>
+      <c r="I408" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J408" s="18">
+        <v>1001.36</v>
+      </c>
+      <c r="K408" s="6">
+        <v>18</v>
+      </c>
+      <c r="L408" s="7">
+        <v>26.04</v>
+      </c>
+      <c r="M408" s="4">
+        <v>1027.4000000000001</v>
+      </c>
+    </row>
+    <row r="409" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A409" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B409" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C409" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D409" s="23"/>
+      <c r="E409" s="23"/>
+      <c r="F409" s="15">
+        <v>1610</v>
+      </c>
+      <c r="G409" s="16">
+        <v>1003</v>
+      </c>
+      <c r="H409" s="4">
+        <v>1300</v>
+      </c>
+      <c r="I409" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J409" s="18">
+        <v>1486.65</v>
+      </c>
+      <c r="K409" s="6">
+        <v>16</v>
+      </c>
+      <c r="L409" s="7">
+        <v>37.659999999999997</v>
+      </c>
+      <c r="M409" s="4">
+        <v>1524.31</v>
+      </c>
+    </row>
+    <row r="410" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A410" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B410" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C410" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="D410" s="23"/>
+      <c r="E410" s="23"/>
+      <c r="F410" s="15">
+        <v>1613</v>
+      </c>
+      <c r="G410" s="16">
+        <v>1402</v>
+      </c>
+      <c r="H410" s="4">
+        <v>793.9</v>
+      </c>
+      <c r="I410" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J410" s="18">
+        <v>907.89</v>
+      </c>
+      <c r="K410" s="6">
+        <v>13</v>
+      </c>
+      <c r="L410" s="7">
+        <v>22.09</v>
+      </c>
+      <c r="M410" s="4">
+        <v>929.98</v>
+      </c>
+    </row>
+    <row r="411" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A411" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B411" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C411" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="D411" s="23"/>
+      <c r="E411" s="23"/>
+      <c r="F411" s="15">
+        <v>1416</v>
+      </c>
+      <c r="G411" s="16">
+        <v>1304</v>
+      </c>
+      <c r="H411" s="4">
+        <v>600</v>
+      </c>
+      <c r="I411" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J411" s="18">
+        <v>712.64</v>
+      </c>
+      <c r="K411" s="6">
+        <v>13</v>
+      </c>
+      <c r="L411" s="7">
+        <v>17.34</v>
+      </c>
+      <c r="M411" s="4">
+        <v>729.98</v>
+      </c>
+    </row>
+    <row r="412" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A412" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B412" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C412" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="D412" s="23"/>
+      <c r="E412" s="23"/>
+      <c r="F412" s="15">
+        <v>1469</v>
+      </c>
+      <c r="G412" s="16">
+        <v>208</v>
+      </c>
+      <c r="H412" s="4">
+        <v>968.46</v>
+      </c>
+      <c r="I412" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J412" s="18">
+        <v>1146.72</v>
+      </c>
+      <c r="K412" s="6">
+        <v>13</v>
+      </c>
+      <c r="L412" s="7">
+        <v>27.9</v>
+      </c>
+      <c r="M412" s="4">
+        <v>1174.6199999999999</v>
+      </c>
+    </row>
+    <row r="413" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A413" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B413" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C413" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D413" s="23"/>
+      <c r="E413" s="23"/>
+      <c r="F413" s="15">
+        <v>1457</v>
+      </c>
+      <c r="G413" s="16">
+        <v>507</v>
+      </c>
+      <c r="H413" s="4">
+        <v>632.9</v>
+      </c>
+      <c r="I413" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J413" s="18">
+        <v>749.4</v>
+      </c>
+      <c r="K413" s="6">
+        <v>13</v>
+      </c>
+      <c r="L413" s="7">
+        <v>18.239999999999998</v>
+      </c>
+      <c r="M413" s="4">
+        <v>767.64</v>
+      </c>
+    </row>
+    <row r="414" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A414" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B414" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="C414" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="D414" s="23"/>
+      <c r="E414" s="23"/>
+      <c r="F414" s="15">
+        <v>1883</v>
+      </c>
+      <c r="G414" s="16">
+        <v>1405</v>
+      </c>
+      <c r="H414" s="4">
+        <v>1000</v>
+      </c>
+      <c r="I414" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="J414" s="18">
+        <v>1000</v>
+      </c>
+      <c r="K414" s="6">
+        <v>8</v>
+      </c>
+      <c r="L414" s="7">
+        <v>22.67</v>
+      </c>
+      <c r="M414" s="4">
+        <v>1022.67</v>
+      </c>
+    </row>
+    <row r="415" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A415" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B415" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C415" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="D415" s="23"/>
+      <c r="E415" s="23"/>
+      <c r="F415" s="15">
+        <v>1814</v>
+      </c>
+      <c r="G415" s="16">
+        <v>1502</v>
+      </c>
+      <c r="H415" s="4">
+        <v>1430</v>
+      </c>
+      <c r="I415" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J415" s="18">
+        <v>1489.47</v>
+      </c>
+      <c r="K415" s="6">
+        <v>6</v>
+      </c>
+      <c r="L415" s="7">
+        <v>32.770000000000003</v>
+      </c>
+      <c r="M415" s="4">
+        <v>1522.24</v>
+      </c>
+    </row>
+    <row r="416" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A416" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B416" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C416" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D416" s="23"/>
+      <c r="E416" s="23"/>
+      <c r="F416" s="15">
+        <v>1467</v>
+      </c>
+      <c r="G416" s="16">
+        <v>207</v>
+      </c>
+      <c r="H416" s="4">
+        <v>675.78</v>
+      </c>
+      <c r="I416" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J416" s="18">
+        <v>800.17</v>
+      </c>
+      <c r="K416" s="6">
+        <v>3</v>
+      </c>
+      <c r="L416" s="7">
+        <v>16.8</v>
+      </c>
+      <c r="M416" s="4">
+        <v>816.97</v>
+      </c>
+    </row>
+    <row r="417" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A417" s="14">
+        <v>46235</v>
+      </c>
+      <c r="B417" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C417" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="D417" s="23"/>
+      <c r="E417" s="23"/>
+      <c r="F417" s="15">
+        <v>1772</v>
+      </c>
+      <c r="G417" s="16">
+        <v>1102</v>
+      </c>
+      <c r="H417" s="4">
+        <v>6000</v>
+      </c>
+      <c r="I417" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="J417" s="18">
+        <v>6343.74</v>
+      </c>
+      <c r="K417" s="6">
+        <v>3</v>
+      </c>
+      <c r="L417" s="7">
+        <v>133.21</v>
+      </c>
+      <c r="M417" s="4">
+        <v>6476.95</v>
+      </c>
+    </row>
+    <row r="418" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A418" s="14"/>
+      <c r="B418" s="3"/>
+      <c r="C418" s="23"/>
+      <c r="D418" s="23"/>
+      <c r="E418" s="23"/>
+      <c r="F418" s="15"/>
+      <c r="G418" s="16"/>
+      <c r="H418" s="4"/>
+      <c r="I418" s="3"/>
+      <c r="J418" s="18"/>
+      <c r="K418" s="6"/>
+      <c r="L418" s="7"/>
+      <c r="M418" s="4"/>
+    </row>
+    <row r="419" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B419" s="3"/>
+      <c r="C419" s="23"/>
+      <c r="D419" s="23"/>
+      <c r="E419" s="23"/>
+      <c r="F419" s="15"/>
+      <c r="G419" s="16"/>
+      <c r="H419" s="4"/>
+      <c r="I419" s="3"/>
+      <c r="J419" s="18"/>
+      <c r="K419" s="6"/>
+      <c r="L419" s="7"/>
+      <c r="M419" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="393">
-    <mergeCell ref="C390:E390"/>
-    <mergeCell ref="C391:E391"/>
-    <mergeCell ref="C392:E392"/>
-    <mergeCell ref="C393:E393"/>
-    <mergeCell ref="C381:E381"/>
-    <mergeCell ref="C382:E382"/>
-    <mergeCell ref="C383:E383"/>
-    <mergeCell ref="C384:E384"/>
-    <mergeCell ref="C385:E385"/>
-    <mergeCell ref="C386:E386"/>
-    <mergeCell ref="C387:E387"/>
-    <mergeCell ref="C388:E388"/>
-    <mergeCell ref="C389:E389"/>
-    <mergeCell ref="C372:E372"/>
-    <mergeCell ref="C373:E373"/>
-    <mergeCell ref="C374:E374"/>
-    <mergeCell ref="C375:E375"/>
-    <mergeCell ref="C376:E376"/>
-    <mergeCell ref="C377:E377"/>
-    <mergeCell ref="C378:E378"/>
-    <mergeCell ref="C379:E379"/>
-    <mergeCell ref="C380:E380"/>
-    <mergeCell ref="C340:E340"/>
-    <mergeCell ref="C341:E341"/>
-    <mergeCell ref="C342:E342"/>
-    <mergeCell ref="C337:E337"/>
-    <mergeCell ref="C338:E338"/>
-    <mergeCell ref="C339:E339"/>
-    <mergeCell ref="C334:E334"/>
-    <mergeCell ref="C335:E335"/>
-    <mergeCell ref="C336:E336"/>
-    <mergeCell ref="C331:E331"/>
-    <mergeCell ref="C332:E332"/>
-    <mergeCell ref="C333:E333"/>
-    <mergeCell ref="C328:E328"/>
-    <mergeCell ref="C329:E329"/>
-    <mergeCell ref="C330:E330"/>
-    <mergeCell ref="C325:E325"/>
-    <mergeCell ref="C326:E326"/>
-    <mergeCell ref="C327:E327"/>
-    <mergeCell ref="C322:E322"/>
-    <mergeCell ref="C323:E323"/>
-    <mergeCell ref="C324:E324"/>
-    <mergeCell ref="C319:E319"/>
-    <mergeCell ref="C320:E320"/>
-    <mergeCell ref="C321:E321"/>
-    <mergeCell ref="C316:E316"/>
-    <mergeCell ref="C317:E317"/>
-    <mergeCell ref="C318:E318"/>
-    <mergeCell ref="C127:E127"/>
-    <mergeCell ref="C128:E128"/>
-    <mergeCell ref="C129:E129"/>
-    <mergeCell ref="C130:E130"/>
-    <mergeCell ref="C131:E131"/>
-    <mergeCell ref="C132:E132"/>
-    <mergeCell ref="C142:E142"/>
-    <mergeCell ref="C133:E133"/>
-    <mergeCell ref="C134:E134"/>
-    <mergeCell ref="C135:E135"/>
-    <mergeCell ref="C136:E136"/>
-    <mergeCell ref="C137:E137"/>
-    <mergeCell ref="C138:E138"/>
-    <mergeCell ref="C139:E139"/>
-    <mergeCell ref="C140:E140"/>
-    <mergeCell ref="C141:E141"/>
+  <mergeCells count="419">
+    <mergeCell ref="C412:E412"/>
+    <mergeCell ref="C413:E413"/>
+    <mergeCell ref="C414:E414"/>
+    <mergeCell ref="C415:E415"/>
+    <mergeCell ref="C416:E416"/>
+    <mergeCell ref="C417:E417"/>
+    <mergeCell ref="C418:E418"/>
+    <mergeCell ref="C419:E419"/>
+    <mergeCell ref="C403:E403"/>
+    <mergeCell ref="C404:E404"/>
+    <mergeCell ref="C405:E405"/>
+    <mergeCell ref="C406:E406"/>
+    <mergeCell ref="C407:E407"/>
+    <mergeCell ref="C408:E408"/>
+    <mergeCell ref="C409:E409"/>
+    <mergeCell ref="C410:E410"/>
+    <mergeCell ref="C411:E411"/>
+    <mergeCell ref="C394:E394"/>
+    <mergeCell ref="C395:E395"/>
+    <mergeCell ref="C396:E396"/>
+    <mergeCell ref="C397:E397"/>
+    <mergeCell ref="C398:E398"/>
+    <mergeCell ref="C399:E399"/>
+    <mergeCell ref="C400:E400"/>
+    <mergeCell ref="C401:E401"/>
+    <mergeCell ref="C402:E402"/>
+    <mergeCell ref="C370:E370"/>
+    <mergeCell ref="C371:E371"/>
+    <mergeCell ref="C367:E367"/>
+    <mergeCell ref="C368:E368"/>
+    <mergeCell ref="C369:E369"/>
+    <mergeCell ref="C364:E364"/>
+    <mergeCell ref="C365:E365"/>
+    <mergeCell ref="C366:E366"/>
+    <mergeCell ref="C361:E361"/>
+    <mergeCell ref="C362:E362"/>
+    <mergeCell ref="C363:E363"/>
+    <mergeCell ref="C358:E358"/>
+    <mergeCell ref="C359:E359"/>
+    <mergeCell ref="C360:E360"/>
+    <mergeCell ref="C355:E355"/>
+    <mergeCell ref="C356:E356"/>
+    <mergeCell ref="C357:E357"/>
+    <mergeCell ref="C352:E352"/>
+    <mergeCell ref="C353:E353"/>
+    <mergeCell ref="C354:E354"/>
+    <mergeCell ref="C349:E349"/>
+    <mergeCell ref="C350:E350"/>
+    <mergeCell ref="C351:E351"/>
+    <mergeCell ref="C346:E346"/>
+    <mergeCell ref="C347:E347"/>
+    <mergeCell ref="C348:E348"/>
+    <mergeCell ref="C343:E343"/>
+    <mergeCell ref="C344:E344"/>
+    <mergeCell ref="C345:E345"/>
+    <mergeCell ref="C314:E314"/>
+    <mergeCell ref="C315:E315"/>
+    <mergeCell ref="C296:E296"/>
+    <mergeCell ref="C297:E297"/>
+    <mergeCell ref="C298:E298"/>
+    <mergeCell ref="C299:E299"/>
+    <mergeCell ref="C300:E300"/>
+    <mergeCell ref="C301:E301"/>
+    <mergeCell ref="C302:E302"/>
+    <mergeCell ref="C303:E303"/>
+    <mergeCell ref="C304:E304"/>
+    <mergeCell ref="C305:E305"/>
+    <mergeCell ref="C306:E306"/>
+    <mergeCell ref="C307:E307"/>
+    <mergeCell ref="C308:E308"/>
+    <mergeCell ref="C309:E309"/>
+    <mergeCell ref="C310:E310"/>
+    <mergeCell ref="C311:E311"/>
+    <mergeCell ref="C312:E312"/>
+    <mergeCell ref="C313:E313"/>
+    <mergeCell ref="C287:E287"/>
+    <mergeCell ref="C288:E288"/>
+    <mergeCell ref="C289:E289"/>
+    <mergeCell ref="C290:E290"/>
+    <mergeCell ref="C278:E278"/>
+    <mergeCell ref="C279:E279"/>
+    <mergeCell ref="C280:E280"/>
+    <mergeCell ref="C281:E281"/>
+    <mergeCell ref="C282:E282"/>
+    <mergeCell ref="C283:E283"/>
+    <mergeCell ref="C284:E284"/>
+    <mergeCell ref="C285:E285"/>
+    <mergeCell ref="C286:E286"/>
+    <mergeCell ref="C291:E291"/>
+    <mergeCell ref="C292:E292"/>
+    <mergeCell ref="C293:E293"/>
+    <mergeCell ref="C294:E294"/>
+    <mergeCell ref="C295:E295"/>
+    <mergeCell ref="C269:E269"/>
+    <mergeCell ref="C270:E270"/>
+    <mergeCell ref="C271:E271"/>
+    <mergeCell ref="C272:E272"/>
+    <mergeCell ref="C273:E273"/>
+    <mergeCell ref="C274:E274"/>
+    <mergeCell ref="C275:E275"/>
+    <mergeCell ref="C276:E276"/>
+    <mergeCell ref="C277:E277"/>
+    <mergeCell ref="C260:E260"/>
+    <mergeCell ref="C261:E261"/>
+    <mergeCell ref="C262:E262"/>
+    <mergeCell ref="C263:E263"/>
+    <mergeCell ref="C264:E264"/>
+    <mergeCell ref="C265:E265"/>
+    <mergeCell ref="C266:E266"/>
+    <mergeCell ref="C267:E267"/>
+    <mergeCell ref="C268:E268"/>
+    <mergeCell ref="C251:E251"/>
+    <mergeCell ref="C252:E252"/>
+    <mergeCell ref="C253:E253"/>
+    <mergeCell ref="C254:E254"/>
+    <mergeCell ref="C255:E255"/>
+    <mergeCell ref="C256:E256"/>
+    <mergeCell ref="C257:E257"/>
+    <mergeCell ref="C258:E258"/>
+    <mergeCell ref="C259:E259"/>
+    <mergeCell ref="C242:E242"/>
+    <mergeCell ref="C243:E243"/>
+    <mergeCell ref="C244:E244"/>
+    <mergeCell ref="C245:E245"/>
+    <mergeCell ref="C246:E246"/>
+    <mergeCell ref="C247:E247"/>
+    <mergeCell ref="C248:E248"/>
+    <mergeCell ref="C249:E249"/>
+    <mergeCell ref="C250:E250"/>
+    <mergeCell ref="C233:E233"/>
+    <mergeCell ref="C234:E234"/>
+    <mergeCell ref="C235:E235"/>
+    <mergeCell ref="C236:E236"/>
+    <mergeCell ref="C237:E237"/>
+    <mergeCell ref="C238:E238"/>
+    <mergeCell ref="C239:E239"/>
+    <mergeCell ref="C240:E240"/>
+    <mergeCell ref="C241:E241"/>
+    <mergeCell ref="C224:E224"/>
+    <mergeCell ref="C225:E225"/>
+    <mergeCell ref="C226:E226"/>
+    <mergeCell ref="C227:E227"/>
+    <mergeCell ref="C228:E228"/>
+    <mergeCell ref="C229:E229"/>
+    <mergeCell ref="C230:E230"/>
+    <mergeCell ref="C231:E231"/>
+    <mergeCell ref="C232:E232"/>
+    <mergeCell ref="C215:E215"/>
+    <mergeCell ref="C216:E216"/>
+    <mergeCell ref="C217:E217"/>
+    <mergeCell ref="C218:E218"/>
+    <mergeCell ref="C219:E219"/>
+    <mergeCell ref="C220:E220"/>
+    <mergeCell ref="C221:E221"/>
+    <mergeCell ref="C222:E222"/>
+    <mergeCell ref="C223:E223"/>
+    <mergeCell ref="C206:E206"/>
+    <mergeCell ref="C207:E207"/>
+    <mergeCell ref="C208:E208"/>
+    <mergeCell ref="C209:E209"/>
+    <mergeCell ref="C210:E210"/>
+    <mergeCell ref="C211:E211"/>
+    <mergeCell ref="C212:E212"/>
+    <mergeCell ref="C213:E213"/>
+    <mergeCell ref="C214:E214"/>
+    <mergeCell ref="C197:E197"/>
+    <mergeCell ref="C198:E198"/>
+    <mergeCell ref="C199:E199"/>
+    <mergeCell ref="C200:E200"/>
+    <mergeCell ref="C201:E201"/>
+    <mergeCell ref="C202:E202"/>
+    <mergeCell ref="C203:E203"/>
+    <mergeCell ref="C204:E204"/>
+    <mergeCell ref="C205:E205"/>
+    <mergeCell ref="C188:E188"/>
+    <mergeCell ref="C189:E189"/>
+    <mergeCell ref="C190:E190"/>
+    <mergeCell ref="C191:E191"/>
+    <mergeCell ref="C192:E192"/>
+    <mergeCell ref="C193:E193"/>
+    <mergeCell ref="C194:E194"/>
+    <mergeCell ref="C195:E195"/>
+    <mergeCell ref="C196:E196"/>
+    <mergeCell ref="C179:E179"/>
+    <mergeCell ref="C180:E180"/>
+    <mergeCell ref="C181:E181"/>
+    <mergeCell ref="C182:E182"/>
+    <mergeCell ref="C183:E183"/>
+    <mergeCell ref="C184:E184"/>
+    <mergeCell ref="C185:E185"/>
+    <mergeCell ref="C186:E186"/>
+    <mergeCell ref="C187:E187"/>
+    <mergeCell ref="C170:E170"/>
+    <mergeCell ref="C171:E171"/>
+    <mergeCell ref="C172:E172"/>
+    <mergeCell ref="C173:E173"/>
+    <mergeCell ref="C174:E174"/>
+    <mergeCell ref="C175:E175"/>
+    <mergeCell ref="C176:E176"/>
+    <mergeCell ref="C177:E177"/>
+    <mergeCell ref="C178:E178"/>
+    <mergeCell ref="C161:E161"/>
+    <mergeCell ref="C162:E162"/>
+    <mergeCell ref="C163:E163"/>
+    <mergeCell ref="C164:E164"/>
+    <mergeCell ref="C165:E165"/>
+    <mergeCell ref="C166:E166"/>
+    <mergeCell ref="C167:E167"/>
+    <mergeCell ref="C168:E168"/>
+    <mergeCell ref="C169:E169"/>
+    <mergeCell ref="C152:E152"/>
+    <mergeCell ref="C153:E153"/>
+    <mergeCell ref="C154:E154"/>
+    <mergeCell ref="C155:E155"/>
+    <mergeCell ref="C156:E156"/>
+    <mergeCell ref="C157:E157"/>
+    <mergeCell ref="C158:E158"/>
+    <mergeCell ref="C159:E159"/>
+    <mergeCell ref="C160:E160"/>
+    <mergeCell ref="C143:E143"/>
+    <mergeCell ref="C144:E144"/>
+    <mergeCell ref="C145:E145"/>
+    <mergeCell ref="C146:E146"/>
+    <mergeCell ref="C147:E147"/>
+    <mergeCell ref="C148:E148"/>
+    <mergeCell ref="C149:E149"/>
+    <mergeCell ref="C150:E150"/>
+    <mergeCell ref="C151:E151"/>
+    <mergeCell ref="C122:E122"/>
+    <mergeCell ref="C123:E123"/>
+    <mergeCell ref="C117:E117"/>
+    <mergeCell ref="C118:E118"/>
+    <mergeCell ref="C119:E119"/>
+    <mergeCell ref="C120:E120"/>
+    <mergeCell ref="C121:E121"/>
+    <mergeCell ref="C112:E112"/>
+    <mergeCell ref="C113:E113"/>
+    <mergeCell ref="C114:E114"/>
+    <mergeCell ref="C115:E115"/>
+    <mergeCell ref="C116:E116"/>
+    <mergeCell ref="C107:E107"/>
+    <mergeCell ref="C108:E108"/>
+    <mergeCell ref="C109:E109"/>
+    <mergeCell ref="C110:E110"/>
+    <mergeCell ref="C111:E111"/>
+    <mergeCell ref="C102:E102"/>
+    <mergeCell ref="C103:E103"/>
+    <mergeCell ref="C104:E104"/>
+    <mergeCell ref="C105:E105"/>
+    <mergeCell ref="C106:E106"/>
+    <mergeCell ref="C97:E97"/>
+    <mergeCell ref="C98:E98"/>
+    <mergeCell ref="C99:E99"/>
+    <mergeCell ref="C100:E100"/>
+    <mergeCell ref="C101:E101"/>
+    <mergeCell ref="C86:E86"/>
+    <mergeCell ref="C87:E87"/>
+    <mergeCell ref="C88:E88"/>
+    <mergeCell ref="C89:E89"/>
+    <mergeCell ref="C90:E90"/>
+    <mergeCell ref="C96:E96"/>
+    <mergeCell ref="C91:E91"/>
+    <mergeCell ref="C92:E92"/>
+    <mergeCell ref="C93:E93"/>
+    <mergeCell ref="C94:E94"/>
+    <mergeCell ref="C95:E95"/>
+    <mergeCell ref="C85:E85"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C67:E67"/>
+    <mergeCell ref="C68:E68"/>
+    <mergeCell ref="C69:E69"/>
+    <mergeCell ref="C70:E70"/>
+    <mergeCell ref="C71:E71"/>
+    <mergeCell ref="C72:E72"/>
+    <mergeCell ref="C73:E73"/>
+    <mergeCell ref="C74:E74"/>
+    <mergeCell ref="C75:E75"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="C79:E79"/>
+    <mergeCell ref="C80:E80"/>
+    <mergeCell ref="C81:E81"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="C83:E83"/>
+    <mergeCell ref="C84:E84"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="C13:E13"/>
@@ -16102,310 +17308,71 @@
     <mergeCell ref="C28:E28"/>
     <mergeCell ref="C25:E25"/>
     <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C85:E85"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C67:E67"/>
-    <mergeCell ref="C68:E68"/>
-    <mergeCell ref="C69:E69"/>
-    <mergeCell ref="C70:E70"/>
-    <mergeCell ref="C71:E71"/>
-    <mergeCell ref="C72:E72"/>
-    <mergeCell ref="C73:E73"/>
-    <mergeCell ref="C74:E74"/>
-    <mergeCell ref="C75:E75"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="C79:E79"/>
-    <mergeCell ref="C80:E80"/>
-    <mergeCell ref="C81:E81"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="C83:E83"/>
-    <mergeCell ref="C84:E84"/>
-    <mergeCell ref="C97:E97"/>
-    <mergeCell ref="C98:E98"/>
-    <mergeCell ref="C99:E99"/>
-    <mergeCell ref="C100:E100"/>
-    <mergeCell ref="C101:E101"/>
-    <mergeCell ref="C86:E86"/>
-    <mergeCell ref="C87:E87"/>
-    <mergeCell ref="C88:E88"/>
-    <mergeCell ref="C89:E89"/>
-    <mergeCell ref="C90:E90"/>
-    <mergeCell ref="C96:E96"/>
-    <mergeCell ref="C91:E91"/>
-    <mergeCell ref="C92:E92"/>
-    <mergeCell ref="C93:E93"/>
-    <mergeCell ref="C94:E94"/>
-    <mergeCell ref="C95:E95"/>
-    <mergeCell ref="C107:E107"/>
-    <mergeCell ref="C108:E108"/>
-    <mergeCell ref="C109:E109"/>
-    <mergeCell ref="C110:E110"/>
-    <mergeCell ref="C111:E111"/>
-    <mergeCell ref="C102:E102"/>
-    <mergeCell ref="C103:E103"/>
-    <mergeCell ref="C104:E104"/>
-    <mergeCell ref="C105:E105"/>
-    <mergeCell ref="C106:E106"/>
-    <mergeCell ref="C122:E122"/>
-    <mergeCell ref="C123:E123"/>
-    <mergeCell ref="C117:E117"/>
-    <mergeCell ref="C118:E118"/>
-    <mergeCell ref="C119:E119"/>
-    <mergeCell ref="C120:E120"/>
-    <mergeCell ref="C121:E121"/>
-    <mergeCell ref="C112:E112"/>
-    <mergeCell ref="C113:E113"/>
-    <mergeCell ref="C114:E114"/>
-    <mergeCell ref="C115:E115"/>
-    <mergeCell ref="C116:E116"/>
-    <mergeCell ref="C143:E143"/>
-    <mergeCell ref="C144:E144"/>
-    <mergeCell ref="C145:E145"/>
-    <mergeCell ref="C146:E146"/>
-    <mergeCell ref="C147:E147"/>
-    <mergeCell ref="C148:E148"/>
-    <mergeCell ref="C149:E149"/>
-    <mergeCell ref="C150:E150"/>
-    <mergeCell ref="C151:E151"/>
-    <mergeCell ref="C152:E152"/>
-    <mergeCell ref="C153:E153"/>
-    <mergeCell ref="C154:E154"/>
-    <mergeCell ref="C155:E155"/>
-    <mergeCell ref="C156:E156"/>
-    <mergeCell ref="C157:E157"/>
-    <mergeCell ref="C158:E158"/>
-    <mergeCell ref="C159:E159"/>
-    <mergeCell ref="C160:E160"/>
-    <mergeCell ref="C161:E161"/>
-    <mergeCell ref="C162:E162"/>
-    <mergeCell ref="C163:E163"/>
-    <mergeCell ref="C164:E164"/>
-    <mergeCell ref="C165:E165"/>
-    <mergeCell ref="C166:E166"/>
-    <mergeCell ref="C167:E167"/>
-    <mergeCell ref="C168:E168"/>
-    <mergeCell ref="C169:E169"/>
-    <mergeCell ref="C170:E170"/>
-    <mergeCell ref="C171:E171"/>
-    <mergeCell ref="C172:E172"/>
-    <mergeCell ref="C173:E173"/>
-    <mergeCell ref="C174:E174"/>
-    <mergeCell ref="C175:E175"/>
-    <mergeCell ref="C176:E176"/>
-    <mergeCell ref="C177:E177"/>
-    <mergeCell ref="C178:E178"/>
-    <mergeCell ref="C179:E179"/>
-    <mergeCell ref="C180:E180"/>
-    <mergeCell ref="C181:E181"/>
-    <mergeCell ref="C182:E182"/>
-    <mergeCell ref="C183:E183"/>
-    <mergeCell ref="C184:E184"/>
-    <mergeCell ref="C185:E185"/>
-    <mergeCell ref="C186:E186"/>
-    <mergeCell ref="C187:E187"/>
-    <mergeCell ref="C188:E188"/>
-    <mergeCell ref="C189:E189"/>
-    <mergeCell ref="C190:E190"/>
-    <mergeCell ref="C191:E191"/>
-    <mergeCell ref="C192:E192"/>
-    <mergeCell ref="C193:E193"/>
-    <mergeCell ref="C194:E194"/>
-    <mergeCell ref="C195:E195"/>
-    <mergeCell ref="C196:E196"/>
-    <mergeCell ref="C197:E197"/>
-    <mergeCell ref="C198:E198"/>
-    <mergeCell ref="C199:E199"/>
-    <mergeCell ref="C200:E200"/>
-    <mergeCell ref="C201:E201"/>
-    <mergeCell ref="C202:E202"/>
-    <mergeCell ref="C203:E203"/>
-    <mergeCell ref="C204:E204"/>
-    <mergeCell ref="C205:E205"/>
-    <mergeCell ref="C206:E206"/>
-    <mergeCell ref="C207:E207"/>
-    <mergeCell ref="C208:E208"/>
-    <mergeCell ref="C209:E209"/>
-    <mergeCell ref="C210:E210"/>
-    <mergeCell ref="C211:E211"/>
-    <mergeCell ref="C212:E212"/>
-    <mergeCell ref="C213:E213"/>
-    <mergeCell ref="C214:E214"/>
-    <mergeCell ref="C215:E215"/>
-    <mergeCell ref="C216:E216"/>
-    <mergeCell ref="C217:E217"/>
-    <mergeCell ref="C218:E218"/>
-    <mergeCell ref="C219:E219"/>
-    <mergeCell ref="C220:E220"/>
-    <mergeCell ref="C221:E221"/>
-    <mergeCell ref="C222:E222"/>
-    <mergeCell ref="C223:E223"/>
-    <mergeCell ref="C224:E224"/>
-    <mergeCell ref="C225:E225"/>
-    <mergeCell ref="C226:E226"/>
-    <mergeCell ref="C227:E227"/>
-    <mergeCell ref="C228:E228"/>
-    <mergeCell ref="C229:E229"/>
-    <mergeCell ref="C230:E230"/>
-    <mergeCell ref="C231:E231"/>
-    <mergeCell ref="C232:E232"/>
-    <mergeCell ref="C233:E233"/>
-    <mergeCell ref="C234:E234"/>
-    <mergeCell ref="C235:E235"/>
-    <mergeCell ref="C236:E236"/>
-    <mergeCell ref="C237:E237"/>
-    <mergeCell ref="C238:E238"/>
-    <mergeCell ref="C239:E239"/>
-    <mergeCell ref="C240:E240"/>
-    <mergeCell ref="C241:E241"/>
-    <mergeCell ref="C242:E242"/>
-    <mergeCell ref="C243:E243"/>
-    <mergeCell ref="C244:E244"/>
-    <mergeCell ref="C245:E245"/>
-    <mergeCell ref="C246:E246"/>
-    <mergeCell ref="C247:E247"/>
-    <mergeCell ref="C248:E248"/>
-    <mergeCell ref="C249:E249"/>
-    <mergeCell ref="C250:E250"/>
-    <mergeCell ref="C251:E251"/>
-    <mergeCell ref="C252:E252"/>
-    <mergeCell ref="C253:E253"/>
-    <mergeCell ref="C254:E254"/>
-    <mergeCell ref="C255:E255"/>
-    <mergeCell ref="C256:E256"/>
-    <mergeCell ref="C257:E257"/>
-    <mergeCell ref="C258:E258"/>
-    <mergeCell ref="C259:E259"/>
-    <mergeCell ref="C260:E260"/>
-    <mergeCell ref="C261:E261"/>
-    <mergeCell ref="C262:E262"/>
-    <mergeCell ref="C263:E263"/>
-    <mergeCell ref="C264:E264"/>
-    <mergeCell ref="C265:E265"/>
-    <mergeCell ref="C266:E266"/>
-    <mergeCell ref="C267:E267"/>
-    <mergeCell ref="C268:E268"/>
-    <mergeCell ref="C269:E269"/>
-    <mergeCell ref="C270:E270"/>
-    <mergeCell ref="C271:E271"/>
-    <mergeCell ref="C272:E272"/>
-    <mergeCell ref="C273:E273"/>
-    <mergeCell ref="C274:E274"/>
-    <mergeCell ref="C275:E275"/>
-    <mergeCell ref="C276:E276"/>
-    <mergeCell ref="C277:E277"/>
-    <mergeCell ref="C313:E313"/>
-    <mergeCell ref="C287:E287"/>
-    <mergeCell ref="C288:E288"/>
-    <mergeCell ref="C289:E289"/>
-    <mergeCell ref="C290:E290"/>
-    <mergeCell ref="C278:E278"/>
-    <mergeCell ref="C279:E279"/>
-    <mergeCell ref="C280:E280"/>
-    <mergeCell ref="C281:E281"/>
-    <mergeCell ref="C282:E282"/>
-    <mergeCell ref="C283:E283"/>
-    <mergeCell ref="C284:E284"/>
-    <mergeCell ref="C285:E285"/>
-    <mergeCell ref="C286:E286"/>
-    <mergeCell ref="C291:E291"/>
-    <mergeCell ref="C292:E292"/>
-    <mergeCell ref="C293:E293"/>
-    <mergeCell ref="C294:E294"/>
-    <mergeCell ref="C295:E295"/>
-    <mergeCell ref="C314:E314"/>
-    <mergeCell ref="C315:E315"/>
-    <mergeCell ref="C296:E296"/>
-    <mergeCell ref="C297:E297"/>
-    <mergeCell ref="C298:E298"/>
-    <mergeCell ref="C299:E299"/>
-    <mergeCell ref="C300:E300"/>
-    <mergeCell ref="C301:E301"/>
-    <mergeCell ref="C302:E302"/>
-    <mergeCell ref="C303:E303"/>
-    <mergeCell ref="C304:E304"/>
-    <mergeCell ref="C305:E305"/>
-    <mergeCell ref="C306:E306"/>
-    <mergeCell ref="C307:E307"/>
-    <mergeCell ref="C308:E308"/>
-    <mergeCell ref="C309:E309"/>
-    <mergeCell ref="C310:E310"/>
-    <mergeCell ref="C311:E311"/>
-    <mergeCell ref="C312:E312"/>
-    <mergeCell ref="C349:E349"/>
-    <mergeCell ref="C350:E350"/>
-    <mergeCell ref="C351:E351"/>
-    <mergeCell ref="C346:E346"/>
-    <mergeCell ref="C347:E347"/>
-    <mergeCell ref="C348:E348"/>
-    <mergeCell ref="C343:E343"/>
-    <mergeCell ref="C344:E344"/>
-    <mergeCell ref="C345:E345"/>
-    <mergeCell ref="C358:E358"/>
-    <mergeCell ref="C359:E359"/>
-    <mergeCell ref="C360:E360"/>
-    <mergeCell ref="C355:E355"/>
-    <mergeCell ref="C356:E356"/>
-    <mergeCell ref="C357:E357"/>
-    <mergeCell ref="C352:E352"/>
-    <mergeCell ref="C353:E353"/>
-    <mergeCell ref="C354:E354"/>
-    <mergeCell ref="C370:E370"/>
-    <mergeCell ref="C371:E371"/>
-    <mergeCell ref="C367:E367"/>
-    <mergeCell ref="C368:E368"/>
-    <mergeCell ref="C369:E369"/>
-    <mergeCell ref="C364:E364"/>
-    <mergeCell ref="C365:E365"/>
-    <mergeCell ref="C366:E366"/>
-    <mergeCell ref="C361:E361"/>
-    <mergeCell ref="C362:E362"/>
-    <mergeCell ref="C363:E363"/>
+    <mergeCell ref="C127:E127"/>
+    <mergeCell ref="C128:E128"/>
+    <mergeCell ref="C129:E129"/>
+    <mergeCell ref="C130:E130"/>
+    <mergeCell ref="C131:E131"/>
+    <mergeCell ref="C132:E132"/>
+    <mergeCell ref="C142:E142"/>
+    <mergeCell ref="C133:E133"/>
+    <mergeCell ref="C134:E134"/>
+    <mergeCell ref="C135:E135"/>
+    <mergeCell ref="C136:E136"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="C138:E138"/>
+    <mergeCell ref="C139:E139"/>
+    <mergeCell ref="C140:E140"/>
+    <mergeCell ref="C141:E141"/>
+    <mergeCell ref="C322:E322"/>
+    <mergeCell ref="C323:E323"/>
+    <mergeCell ref="C324:E324"/>
+    <mergeCell ref="C319:E319"/>
+    <mergeCell ref="C320:E320"/>
+    <mergeCell ref="C321:E321"/>
+    <mergeCell ref="C316:E316"/>
+    <mergeCell ref="C317:E317"/>
+    <mergeCell ref="C318:E318"/>
+    <mergeCell ref="C331:E331"/>
+    <mergeCell ref="C332:E332"/>
+    <mergeCell ref="C333:E333"/>
+    <mergeCell ref="C328:E328"/>
+    <mergeCell ref="C329:E329"/>
+    <mergeCell ref="C330:E330"/>
+    <mergeCell ref="C325:E325"/>
+    <mergeCell ref="C326:E326"/>
+    <mergeCell ref="C327:E327"/>
+    <mergeCell ref="C340:E340"/>
+    <mergeCell ref="C341:E341"/>
+    <mergeCell ref="C342:E342"/>
+    <mergeCell ref="C337:E337"/>
+    <mergeCell ref="C338:E338"/>
+    <mergeCell ref="C339:E339"/>
+    <mergeCell ref="C334:E334"/>
+    <mergeCell ref="C335:E335"/>
+    <mergeCell ref="C336:E336"/>
+    <mergeCell ref="C372:E372"/>
+    <mergeCell ref="C373:E373"/>
+    <mergeCell ref="C374:E374"/>
+    <mergeCell ref="C375:E375"/>
+    <mergeCell ref="C376:E376"/>
+    <mergeCell ref="C377:E377"/>
+    <mergeCell ref="C378:E378"/>
+    <mergeCell ref="C379:E379"/>
+    <mergeCell ref="C380:E380"/>
+    <mergeCell ref="C390:E390"/>
+    <mergeCell ref="C391:E391"/>
+    <mergeCell ref="C392:E392"/>
+    <mergeCell ref="C393:E393"/>
+    <mergeCell ref="C381:E381"/>
+    <mergeCell ref="C382:E382"/>
+    <mergeCell ref="C383:E383"/>
+    <mergeCell ref="C384:E384"/>
+    <mergeCell ref="C385:E385"/>
+    <mergeCell ref="C386:E386"/>
+    <mergeCell ref="C387:E387"/>
+    <mergeCell ref="C388:E388"/>
+    <mergeCell ref="C389:E389"/>
   </mergeCells>
   <pageMargins left="0.52999994886203072" right="0.52999994886203072" top="0.52999994886203072" bottom="0.68999998212799307" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToWidth="0" fitToHeight="0" orientation="landscape" r:id="rId1"/>
